--- a/InputData/land/BLAPE/BAU LULUCF Anthro Pollutant Emis.xlsx
+++ b/InputData/land/BLAPE/BAU LULUCF Anthro Pollutant Emis.xlsx
@@ -1,27 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10727"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-brazil-cpl/InputData/land/BLAPE/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saido\Documents\eps-brazil-cpl\InputData\land\BLAPE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C4D3418-731B-BA40-B7BA-6AFA98AEF6B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="765" windowWidth="34200" windowHeight="21375" firstSheet="3" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="Data" sheetId="6" r:id="rId2"/>
     <sheet name="data from RPEpUACE" sheetId="7" r:id="rId3"/>
     <sheet name="Share of Pollutants" sheetId="3" r:id="rId4"/>
-    <sheet name="MA-Smoothing" sheetId="10" r:id="rId5"/>
-    <sheet name="Government Data" sheetId="8" r:id="rId6"/>
+    <sheet name="EPE-Land use emissions" sheetId="10" r:id="rId5"/>
+    <sheet name="Emissions by Pollutants" sheetId="8" r:id="rId6"/>
     <sheet name="BLAPE" sheetId="9" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="76">
   <si>
     <t>Source:</t>
   </si>
@@ -211,15 +210,6 @@
     <t>Share of N2O (g)</t>
   </si>
   <si>
-    <t>LULUCF Emissions (kt CO2e)</t>
-  </si>
-  <si>
-    <t>kt CO2e to g CO2e</t>
-  </si>
-  <si>
-    <t>LULUCF Emissions (g CO2e)</t>
-  </si>
-  <si>
     <t>CO2 (g CO2e)</t>
   </si>
   <si>
@@ -244,29 +234,50 @@
     <t>N2O (g pollutant)</t>
   </si>
   <si>
-    <t>CGR</t>
-  </si>
-  <si>
     <t>LULUCF Emissions-Smoothing (g CO2e)</t>
   </si>
   <si>
-    <t>Smoothing</t>
+    <t>EPE</t>
   </si>
   <si>
-    <t>LUE1</t>
+    <t>Land use emissions (Mt CO2e)</t>
+  </si>
+  <si>
+    <t>MOSTI</t>
+  </si>
+  <si>
+    <t>Growth rate</t>
+  </si>
+  <si>
+    <t>Hypothèses</t>
+  </si>
+  <si>
+    <t>Alpha MMA (α)</t>
+  </si>
+  <si>
+    <t>EPE-smoothing</t>
+  </si>
+  <si>
+    <t>Land use emissions - smoothing (Mt CO2e)</t>
+  </si>
+  <si>
+    <t>Mt CO2e to g CO2e</t>
+  </si>
+  <si>
+    <t>Land use emissions - smoothing (g CO2e)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -321,13 +332,27 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF7F6000"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -352,8 +377,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFCE5CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -376,13 +413,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFC0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFC0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFC0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFC0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
@@ -421,23 +473,29 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="11" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="11" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Comma" xfId="2" builtinId="3"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
+    <cellStyle name="Milliers" xfId="2" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -454,9 +512,9 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="fr-FR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -468,6 +526,29 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Land-use emissions</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -483,10 +564,7 @@
           <a:pPr>
             <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -508,11 +586,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'MA-Smoothing'!$A$2</c:f>
+              <c:f>'EPE-Land use emissions'!$A$24</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>LUE1</c:v>
+                  <c:v>Land use emissions (Mt CO2e)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -531,191 +609,101 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'MA-Smoothing'!$B$1:$BJ$1</c:f>
+              <c:f>'EPE-Land use emissions'!$B$23:$AF$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>1990</c:v>
+                  <c:v>2020</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1991</c:v>
+                  <c:v>2021</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1992</c:v>
+                  <c:v>2022</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1993</c:v>
+                  <c:v>2023</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1994</c:v>
+                  <c:v>2024</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1995</c:v>
+                  <c:v>2025</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1996</c:v>
+                  <c:v>2026</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1997</c:v>
+                  <c:v>2027</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1998</c:v>
+                  <c:v>2028</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1999</c:v>
+                  <c:v>2029</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2000</c:v>
+                  <c:v>2030</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2001</c:v>
+                  <c:v>2031</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2002</c:v>
+                  <c:v>2032</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2003</c:v>
+                  <c:v>2033</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2004</c:v>
+                  <c:v>2034</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2005</c:v>
+                  <c:v>2035</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2006</c:v>
+                  <c:v>2036</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2007</c:v>
+                  <c:v>2037</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2008</c:v>
+                  <c:v>2038</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2009</c:v>
+                  <c:v>2039</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2010</c:v>
+                  <c:v>2040</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>2011</c:v>
+                  <c:v>2041</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2012</c:v>
+                  <c:v>2042</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>2013</c:v>
+                  <c:v>2043</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>2014</c:v>
+                  <c:v>2044</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>2015</c:v>
+                  <c:v>2045</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>2016</c:v>
+                  <c:v>2046</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>2017</c:v>
+                  <c:v>2047</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>2018</c:v>
+                  <c:v>2048</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>2019</c:v>
+                  <c:v>2049</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>2020</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>2021</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>2022</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>2023</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>2024</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>2025</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>2026</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>2027</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>2028</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>2029</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>2030</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>2031</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>2032</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>2033</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>2034</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>2035</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>2036</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>2037</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>2038</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>2039</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>2040</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>2041</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>2042</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>2043</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>2044</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>2045</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>2046</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>2047</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>2048</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>2049</c:v>
-                </c:pt>
-                <c:pt idx="60">
                   <c:v>2050</c:v>
                 </c:pt>
               </c:numCache>
@@ -723,213 +711,118 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'MA-Smoothing'!$B$2:$BJ$2</c:f>
+              <c:f>'EPE-Land use emissions'!$B$24:$AF$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>908066332363945.25</c:v>
+                  <c:v>665.08399999999995</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>726204322679458.5</c:v>
+                  <c:v>882.47799999999995</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>839121579035849.25</c:v>
+                  <c:v>805.69399999999996</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>874712069778537.62</c:v>
+                  <c:v>806.72664032959744</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>854112479205995.62</c:v>
+                  <c:v>807.75928065919481</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1973225015654828</c:v>
+                  <c:v>808.7919209887923</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1245646946790318.2</c:v>
+                  <c:v>810.70294745777267</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>915577409855144.38</c:v>
+                  <c:v>812.61397392675303</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1179953485182655.8</c:v>
+                  <c:v>814.52500039573329</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1132596244208690.5</c:v>
+                  <c:v>816.43602686471365</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1184463676030746</c:v>
+                  <c:v>818.34705333369402</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1129708865473567.2</c:v>
+                  <c:v>822.79303483134242</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1339596237688777</c:v>
+                  <c:v>827.23901632899072</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2427047908322861</c:v>
+                  <c:v>831.68499782663912</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2621326240834337</c:v>
+                  <c:v>836.13097932428741</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1573713706255844.2</c:v>
+                  <c:v>840.57696082193581</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1201775417449594.5</c:v>
+                  <c:v>846.18446970114098</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>852790016028065</c:v>
+                  <c:v>851.79197858034615</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>963933618742378.88</c:v>
+                  <c:v>857.39948745955144</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>342440028055332.06</c:v>
+                  <c:v>863.00699633875661</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>277144032250903.78</c:v>
+                  <c:v>868.61450521796178</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>324149965481829.88</c:v>
+                  <c:v>868.77931653561507</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>172897475778987.47</c:v>
+                  <c:v>868.94412785326847</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>411276025337924.81</c:v>
+                  <c:v>869.10893917092176</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>259775337434062.5</c:v>
+                  <c:v>869.27375048857516</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>373263852526950.88</c:v>
+                  <c:v>869.43856180622845</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>436546377161111.81</c:v>
+                  <c:v>873.42542606184247</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>313282465310611.69</c:v>
+                  <c:v>877.41229031745661</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>362155719578151.5</c:v>
+                  <c:v>881.39915457307063</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>567067303185964</c:v>
+                  <c:v>885.38601882868477</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>665083900964468</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>882477987272240.88</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>805693940844518</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>737554850928654.75</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>675178415215819.88</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>618077274929946.75</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>565805288166264.88</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>517954044101029.88</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>474149672001257.69</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>434049920102657.31</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>397341481532488.56</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>363737546384279.06</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>332975560818302.44</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>304815175679249.12</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>279036368603255.31</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>255437724941961.66</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>233834864072138.25</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>214058998795338.44</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>195955616571901.84</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>179383272285539.69</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>164212483106147.12</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>150324716816197.78</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>137611465696325.88</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>125973398734189.95</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>115319585532667.64</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>105566785853630.58</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>96638799246372.031</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>88465869679212.312</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>80984140522557.078</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>74135155625089.281</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>67865402584909.328</c:v>
+                  <c:v>889.37288308429879</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5389-BF46-AD5E-07B14D214D66}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'MA-Smoothing'!$A$3</c:f>
+              <c:f>'EPE-Land use emissions'!$A$25</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Smoothing</c:v>
+                  <c:v>Land use emissions - smoothing (Mt CO2e)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -948,191 +841,101 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'MA-Smoothing'!$B$1:$BJ$1</c:f>
+              <c:f>'EPE-Land use emissions'!$B$23:$AF$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>1990</c:v>
+                  <c:v>2020</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1991</c:v>
+                  <c:v>2021</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1992</c:v>
+                  <c:v>2022</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1993</c:v>
+                  <c:v>2023</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1994</c:v>
+                  <c:v>2024</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1995</c:v>
+                  <c:v>2025</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1996</c:v>
+                  <c:v>2026</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1997</c:v>
+                  <c:v>2027</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1998</c:v>
+                  <c:v>2028</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1999</c:v>
+                  <c:v>2029</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2000</c:v>
+                  <c:v>2030</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2001</c:v>
+                  <c:v>2031</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2002</c:v>
+                  <c:v>2032</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2003</c:v>
+                  <c:v>2033</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2004</c:v>
+                  <c:v>2034</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2005</c:v>
+                  <c:v>2035</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2006</c:v>
+                  <c:v>2036</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2007</c:v>
+                  <c:v>2037</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2008</c:v>
+                  <c:v>2038</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2009</c:v>
+                  <c:v>2039</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2010</c:v>
+                  <c:v>2040</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>2011</c:v>
+                  <c:v>2041</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2012</c:v>
+                  <c:v>2042</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>2013</c:v>
+                  <c:v>2043</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>2014</c:v>
+                  <c:v>2044</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>2015</c:v>
+                  <c:v>2045</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>2016</c:v>
+                  <c:v>2046</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>2017</c:v>
+                  <c:v>2047</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>2018</c:v>
+                  <c:v>2048</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>2019</c:v>
+                  <c:v>2049</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>2020</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>2021</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>2022</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>2023</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>2024</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>2025</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>2026</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>2027</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>2028</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>2029</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>2030</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>2031</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>2032</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>2033</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>2034</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>2035</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>2036</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>2037</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>2038</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>2039</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>2040</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>2041</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>2042</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>2043</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>2044</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>2045</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>2046</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>2047</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>2048</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>2049</c:v>
-                </c:pt>
-                <c:pt idx="60">
                   <c:v>2050</c:v>
                 </c:pt>
               </c:numCache>
@@ -1140,202 +943,107 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'MA-Smoothing'!$B$3:$BJ$3</c:f>
+              <c:f>'EPE-Land use emissions'!$B$25:$AF$25</c:f>
               <c:numCache>
-                <c:formatCode>0.00E+00</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>837000000000000</c:v>
+                  <c:v>665.08399999999995</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>840000000000000</c:v>
+                  <c:v>730.30219999999986</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1050000000000000</c:v>
+                  <c:v>752.91973999999982</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1160000000000000</c:v>
+                  <c:v>769.06181009887905</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1170000000000000</c:v>
+                  <c:v>780.67105126697368</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1230000000000000</c:v>
+                  <c:v>789.10731218351918</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1290000000000000</c:v>
+                  <c:v>795.58600276579523</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1130000000000000</c:v>
+                  <c:v>800.69439411408257</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1110000000000000</c:v>
+                  <c:v>804.84357599857765</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1190000000000000</c:v>
+                  <c:v>808.3213112584184</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1440000000000000</c:v>
+                  <c:v>811.32903388100101</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1740000000000000</c:v>
+                  <c:v>814.76823416610341</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1820000000000000</c:v>
+                  <c:v>818.50946881496952</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1830000000000000</c:v>
+                  <c:v>822.46212751847042</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1740000000000000</c:v>
+                  <c:v>826.56278306021545</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1440000000000000</c:v>
+                  <c:v>830.76703638873153</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>987000000000000</c:v>
+                  <c:v>835.3922663824543</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>728000000000000</c:v>
+                  <c:v>840.31218004182188</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>552000000000000</c:v>
+                  <c:v>845.43837226714072</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>416000000000000</c:v>
+                  <c:v>850.7089594886254</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>306000000000000</c:v>
+                  <c:v>856.08062320742624</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>289000000000000</c:v>
+                  <c:v>859.89023120588286</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>308000000000000</c:v>
+                  <c:v>862.60640020009851</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>331000000000000</c:v>
+                  <c:v>864.55716189134546</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>359000000000000</c:v>
+                  <c:v>865.97213847051432</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>349000000000000</c:v>
+                  <c:v>867.01206547122842</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>410000000000000</c:v>
+                  <c:v>868.9360736484125</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>469000000000000</c:v>
+                  <c:v>871.47893864912567</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>558000000000000</c:v>
+                  <c:v>874.45500342630908</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>556000000000000</c:v>
+                  <c:v>877.73430804702184</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>632000000000000</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>853000000000000</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>844000000000000</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>780000000000000</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>623000000000000</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>570000000000000</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>522000000000000</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>478000000000000</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>437000000000000</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>400000000000000</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>367000000000000</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>336000000000000</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>307000000000000</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>281000000000000</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>257000000000000</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>236000000000000</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>216000000000000</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>197000000000000</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>181000000000000</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>165000000000000</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>152000000000000</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>139000000000000</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>127000000000000</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>116000000000000</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>106000000000000</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>97400000000000</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>89200000000000</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>81600000000000</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>77900000000000</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>74300000000000</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>71000000000000</c:v>
+                  <c:v>881.22588055820484</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-5389-BF46-AD5E-07B14D214D66}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -1346,11 +1054,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="601439488"/>
-        <c:axId val="601441200"/>
+        <c:axId val="-690525136"/>
+        <c:axId val="-690522960"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="601439488"/>
+        <c:axId val="-690525136"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1380,10 +1088,7 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -1393,7 +1098,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="601441200"/>
+        <c:crossAx val="-690522960"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1401,7 +1106,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="601441200"/>
+        <c:axId val="-690522960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1439,10 +1144,7 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -1452,7 +1154,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="601439488"/>
+        <c:crossAx val="-690525136"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1466,6 +1168,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1481,10 +1184,7 @@
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -1519,7 +1219,11 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -2093,25 +1797,19 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>25400</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:colOff>742950</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>14287</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>203200</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>50800</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>742950</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A00FB2B0-28B0-AC5A-9CF3-008A7F336A48}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="4" name="Graphique 3"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -2147,9 +1845,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2187,9 +1885,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2224,7 +1922,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2259,7 +1957,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2432,20 +2130,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" customWidth="1"/>
-    <col min="2" max="2" width="51.6640625" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" customWidth="1"/>
+    <col min="2" max="2" width="51.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -2453,42 +2151,42 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="4">
         <v>2020</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -2496,7 +2194,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -2504,29 +2202,29 @@
         <v>265</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>30</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B8" r:id="rId1" xr:uid="{28E45434-BF4A-40CF-BA05-2BB4327A7C6D}"/>
+    <hyperlink ref="B8" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
@@ -2534,27 +2232,27 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66C63694-8548-4798-9876-F1B5EF923EAF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.5" customWidth="1"/>
-    <col min="2" max="6" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="29.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" customWidth="1"/>
+    <col min="2" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -2564,12 +2262,12 @@
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -2579,22 +2277,22 @@
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B12" s="9" t="s">
         <v>38</v>
       </c>
@@ -2623,7 +2321,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13" s="11" t="s">
         <v>40</v>
       </c>
@@ -2653,16 +2351,16 @@
         <v>652321.40993903182</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I16" t="s">
         <v>41</v>
       </c>
       <c r="J16">
         <f>J13*10^9</f>
-        <v>652321409939031.88</v>
-      </c>
-    </row>
-    <row r="18" spans="10:10" x14ac:dyDescent="0.2">
+        <v>652321409939031.87</v>
+      </c>
+    </row>
+    <row r="18" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J18" s="12"/>
     </row>
   </sheetData>
@@ -2672,20 +2370,20 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA2398E0-C79E-4926-91C2-517BD5042907}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23" customWidth="1"/>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -2693,7 +2391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>43</v>
       </c>
@@ -2701,7 +2399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -2709,7 +2407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>45</v>
       </c>
@@ -2717,7 +2415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>46</v>
       </c>
@@ -2725,7 +2423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>47</v>
       </c>
@@ -2733,7 +2431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>48</v>
       </c>
@@ -2741,7 +2439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>49</v>
       </c>
@@ -2749,7 +2447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>50</v>
       </c>
@@ -2757,7 +2455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -2765,7 +2463,7 @@
         <v>4.3636084384378205E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -2773,7 +2471,7 @@
         <v>1.335357177073511E-4</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>51</v>
       </c>
@@ -2787,18 +2485,18 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
   <dimension ref="A1:AF19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="17" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.85546875" customWidth="1"/>
+    <col min="2" max="17" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -2896,136 +2594,136 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="3">
         <f>Data!$J$16</f>
-        <v>652321409939031.88</v>
+        <v>652321409939031.87</v>
       </c>
       <c r="C2" s="3">
         <f>Data!$J$16</f>
-        <v>652321409939031.88</v>
+        <v>652321409939031.87</v>
       </c>
       <c r="D2" s="3">
         <f>Data!$J$16</f>
-        <v>652321409939031.88</v>
+        <v>652321409939031.87</v>
       </c>
       <c r="E2" s="3">
         <f>Data!$J$16</f>
-        <v>652321409939031.88</v>
+        <v>652321409939031.87</v>
       </c>
       <c r="F2" s="3">
         <f>Data!$J$16</f>
-        <v>652321409939031.88</v>
+        <v>652321409939031.87</v>
       </c>
       <c r="G2" s="3">
         <f>Data!$J$16</f>
-        <v>652321409939031.88</v>
+        <v>652321409939031.87</v>
       </c>
       <c r="H2" s="3">
         <f>Data!$J$16</f>
-        <v>652321409939031.88</v>
+        <v>652321409939031.87</v>
       </c>
       <c r="I2" s="3">
         <f>Data!$J$16</f>
-        <v>652321409939031.88</v>
+        <v>652321409939031.87</v>
       </c>
       <c r="J2" s="3">
         <f>Data!$J$16</f>
-        <v>652321409939031.88</v>
+        <v>652321409939031.87</v>
       </c>
       <c r="K2" s="3">
         <f>Data!$J$16</f>
-        <v>652321409939031.88</v>
+        <v>652321409939031.87</v>
       </c>
       <c r="L2" s="3">
         <f>Data!$J$16</f>
-        <v>652321409939031.88</v>
+        <v>652321409939031.87</v>
       </c>
       <c r="M2" s="3">
         <f>Data!$J$16</f>
-        <v>652321409939031.88</v>
+        <v>652321409939031.87</v>
       </c>
       <c r="N2" s="3">
         <f>Data!$J$16</f>
-        <v>652321409939031.88</v>
+        <v>652321409939031.87</v>
       </c>
       <c r="O2" s="3">
         <f>Data!$J$16</f>
-        <v>652321409939031.88</v>
+        <v>652321409939031.87</v>
       </c>
       <c r="P2" s="3">
         <f>Data!$J$16</f>
-        <v>652321409939031.88</v>
+        <v>652321409939031.87</v>
       </c>
       <c r="Q2" s="3">
         <f>Data!$J$16</f>
-        <v>652321409939031.88</v>
+        <v>652321409939031.87</v>
       </c>
       <c r="R2" s="3">
         <f>Data!$J$16</f>
-        <v>652321409939031.88</v>
+        <v>652321409939031.87</v>
       </c>
       <c r="S2" s="3">
         <f>Data!$J$16</f>
-        <v>652321409939031.88</v>
+        <v>652321409939031.87</v>
       </c>
       <c r="T2" s="3">
         <f>Data!$J$16</f>
-        <v>652321409939031.88</v>
+        <v>652321409939031.87</v>
       </c>
       <c r="U2" s="3">
         <f>Data!$J$16</f>
-        <v>652321409939031.88</v>
+        <v>652321409939031.87</v>
       </c>
       <c r="V2" s="3">
         <f>Data!$J$16</f>
-        <v>652321409939031.88</v>
+        <v>652321409939031.87</v>
       </c>
       <c r="W2" s="3">
         <f>Data!$J$16</f>
-        <v>652321409939031.88</v>
+        <v>652321409939031.87</v>
       </c>
       <c r="X2" s="3">
         <f>Data!$J$16</f>
-        <v>652321409939031.88</v>
+        <v>652321409939031.87</v>
       </c>
       <c r="Y2" s="3">
         <f>Data!$J$16</f>
-        <v>652321409939031.88</v>
+        <v>652321409939031.87</v>
       </c>
       <c r="Z2" s="3">
         <f>Data!$J$16</f>
-        <v>652321409939031.88</v>
+        <v>652321409939031.87</v>
       </c>
       <c r="AA2" s="3">
         <f>Data!$J$16</f>
-        <v>652321409939031.88</v>
+        <v>652321409939031.87</v>
       </c>
       <c r="AB2" s="3">
         <f>Data!$J$16</f>
-        <v>652321409939031.88</v>
+        <v>652321409939031.87</v>
       </c>
       <c r="AC2" s="3">
         <f>Data!$J$16</f>
-        <v>652321409939031.88</v>
+        <v>652321409939031.87</v>
       </c>
       <c r="AD2" s="3">
         <f>Data!$J$16</f>
-        <v>652321409939031.88</v>
+        <v>652321409939031.87</v>
       </c>
       <c r="AE2" s="3">
         <f>Data!$J$16</f>
-        <v>652321409939031.88</v>
+        <v>652321409939031.87</v>
       </c>
       <c r="AF2" s="3">
         <f>Data!$J$16</f>
-        <v>652321409939031.88</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+        <v>652321409939031.87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -3123,7 +2821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -3221,7 +2919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -3319,7 +3017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -3417,7 +3115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -3515,7 +3213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -3613,7 +3311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -3711,7 +3409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -3809,7 +3507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -3938,7 +3636,7 @@
         <v>2846475208983.6162</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -4067,7 +3765,7 @@
         <v>87108207652.079819</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -4165,7 +3863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>53</v>
       </c>
@@ -4294,7 +3992,7 @@
         <v>655254993355667.62</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>52</v>
       </c>
@@ -4423,7 +4121,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>54</v>
       </c>
@@ -4552,7 +4250,7 @@
         <v>0.99552298960498964</v>
       </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>55</v>
       </c>
@@ -4681,7 +4379,7 @@
         <v>4.3440725180991799E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>56</v>
       </c>
@@ -4816,3089 +4514,2603 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EFC772B-9942-6049-8D64-C5B578D545E8}">
-  <dimension ref="A1:BJ36"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AF31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="A1" s="23" t="s">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="13">
-        <v>1990</v>
-      </c>
-      <c r="C1" s="13">
-        <v>1991</v>
-      </c>
-      <c r="D1" s="13">
-        <v>1992</v>
-      </c>
-      <c r="E1" s="13">
-        <v>1993</v>
-      </c>
-      <c r="F1" s="13">
-        <v>1994</v>
-      </c>
-      <c r="G1" s="13">
-        <v>1995</v>
-      </c>
-      <c r="H1" s="13">
-        <v>1996</v>
-      </c>
-      <c r="I1" s="13">
-        <v>1997</v>
-      </c>
-      <c r="J1" s="13">
-        <v>1998</v>
-      </c>
-      <c r="K1" s="13">
-        <v>1999</v>
-      </c>
-      <c r="L1" s="13">
-        <v>2000</v>
-      </c>
-      <c r="M1" s="13">
-        <v>2001</v>
-      </c>
-      <c r="N1" s="13">
-        <v>2002</v>
-      </c>
-      <c r="O1" s="13">
-        <v>2003</v>
-      </c>
-      <c r="P1" s="13">
-        <v>2004</v>
-      </c>
-      <c r="Q1" s="13">
-        <v>2005</v>
-      </c>
-      <c r="R1" s="13">
-        <v>2006</v>
-      </c>
-      <c r="S1" s="13">
-        <v>2007</v>
-      </c>
-      <c r="T1" s="13">
-        <v>2008</v>
-      </c>
-      <c r="U1" s="13">
-        <v>2009</v>
-      </c>
-      <c r="V1" s="13">
-        <v>2010</v>
-      </c>
-      <c r="W1" s="13">
-        <v>2011</v>
-      </c>
-      <c r="X1" s="13">
-        <v>2012</v>
-      </c>
-      <c r="Y1" s="13">
-        <v>2013</v>
-      </c>
-      <c r="Z1" s="13">
-        <v>2014</v>
-      </c>
-      <c r="AA1" s="13">
-        <v>2015</v>
-      </c>
-      <c r="AB1" s="13">
-        <v>2016</v>
-      </c>
-      <c r="AC1" s="13">
-        <v>2017</v>
-      </c>
-      <c r="AD1" s="13">
-        <v>2018</v>
-      </c>
-      <c r="AE1" s="13">
-        <v>2019</v>
-      </c>
-      <c r="AF1" s="13">
+      <c r="B2" s="1">
         <v>2020</v>
       </c>
-      <c r="AG1" s="13">
+      <c r="C2" s="1">
         <v>2021</v>
       </c>
-      <c r="AH1" s="13">
+      <c r="D2" s="1">
         <v>2022</v>
       </c>
-      <c r="AI1" s="13">
+      <c r="E2" s="1">
         <v>2023</v>
       </c>
-      <c r="AJ1" s="13">
+      <c r="F2" s="1">
         <v>2024</v>
       </c>
-      <c r="AK1" s="13">
+      <c r="G2" s="1">
         <v>2025</v>
       </c>
-      <c r="AL1" s="13">
+      <c r="H2" s="1">
         <v>2026</v>
       </c>
-      <c r="AM1" s="13">
+      <c r="I2" s="1">
         <v>2027</v>
       </c>
-      <c r="AN1" s="13">
+      <c r="J2" s="1">
         <v>2028</v>
       </c>
-      <c r="AO1" s="13">
+      <c r="K2" s="1">
         <v>2029</v>
       </c>
-      <c r="AP1" s="13">
+      <c r="L2" s="1">
         <v>2030</v>
       </c>
-      <c r="AQ1" s="13">
+      <c r="M2" s="1">
         <v>2031</v>
       </c>
-      <c r="AR1" s="13">
+      <c r="N2" s="1">
         <v>2032</v>
       </c>
-      <c r="AS1" s="13">
+      <c r="O2" s="1">
         <v>2033</v>
       </c>
-      <c r="AT1" s="13">
+      <c r="P2" s="1">
         <v>2034</v>
       </c>
-      <c r="AU1" s="13">
+      <c r="Q2" s="1">
         <v>2035</v>
       </c>
-      <c r="AV1" s="13">
+      <c r="R2" s="1">
         <v>2036</v>
       </c>
-      <c r="AW1" s="13">
+      <c r="S2" s="1">
         <v>2037</v>
       </c>
-      <c r="AX1" s="13">
+      <c r="T2" s="1">
         <v>2038</v>
       </c>
-      <c r="AY1" s="13">
+      <c r="U2" s="1">
         <v>2039</v>
       </c>
-      <c r="AZ1" s="13">
+      <c r="V2" s="1">
         <v>2040</v>
       </c>
-      <c r="BA1" s="13">
+      <c r="W2" s="1">
         <v>2041</v>
       </c>
-      <c r="BB1" s="13">
+      <c r="X2" s="1">
         <v>2042</v>
       </c>
-      <c r="BC1" s="13">
+      <c r="Y2" s="1">
         <v>2043</v>
       </c>
-      <c r="BD1" s="13">
+      <c r="Z2" s="1">
         <v>2044</v>
       </c>
-      <c r="BE1" s="13">
+      <c r="AA2" s="1">
         <v>2045</v>
       </c>
-      <c r="BF1" s="13">
+      <c r="AB2" s="1">
         <v>2046</v>
       </c>
-      <c r="BG1" s="13">
+      <c r="AC2" s="1">
         <v>2047</v>
       </c>
-      <c r="BH1" s="13">
+      <c r="AD2" s="1">
         <v>2048</v>
       </c>
-      <c r="BI1" s="13">
+      <c r="AE2" s="1">
         <v>2049</v>
       </c>
-      <c r="BJ1" s="13">
+      <c r="AF2" s="1">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3">
+        <v>665.08399999999995</v>
+      </c>
+      <c r="C3">
+        <v>882.47799999999995</v>
+      </c>
+      <c r="D3">
+        <v>805.69399999999996</v>
+      </c>
+      <c r="E3">
+        <f>FORECAST(E2,$C$3:$D$3,$C$2:$D$2)</f>
+        <v>728.91000000000349</v>
+      </c>
+      <c r="F3">
+        <f>FORECAST(F2,$B$3:$D$3,$B$2:$D$2)</f>
+        <v>995.33366666664369</v>
+      </c>
+      <c r="G3">
+        <f t="shared" ref="G3:AF3" si="0">FORECAST(G2,$B$3:$D$3,$B$2:$D$2)</f>
+        <v>1065.6386666666367</v>
+      </c>
+      <c r="H3">
+        <f t="shared" si="0"/>
+        <v>1135.9436666666588</v>
+      </c>
+      <c r="I3">
+        <f t="shared" si="0"/>
+        <v>1206.2486666666518</v>
+      </c>
+      <c r="J3">
+        <f t="shared" si="0"/>
+        <v>1276.5536666666449</v>
+      </c>
+      <c r="K3">
+        <f t="shared" si="0"/>
+        <v>1346.8586666666379</v>
+      </c>
+      <c r="L3">
+        <f t="shared" si="0"/>
+        <v>1417.16366666666</v>
+      </c>
+      <c r="M3">
+        <f t="shared" si="0"/>
+        <v>1487.468666666653</v>
+      </c>
+      <c r="N3">
+        <f t="shared" si="0"/>
+        <v>1557.773666666646</v>
+      </c>
+      <c r="O3">
+        <f t="shared" si="0"/>
+        <v>1628.078666666639</v>
+      </c>
+      <c r="P3">
+        <f t="shared" si="0"/>
+        <v>1698.3836666666612</v>
+      </c>
+      <c r="Q3">
+        <f t="shared" si="0"/>
+        <v>1768.6886666666542</v>
+      </c>
+      <c r="R3">
+        <f t="shared" si="0"/>
+        <v>1838.9936666666472</v>
+      </c>
+      <c r="S3">
+        <f t="shared" si="0"/>
+        <v>1909.2986666666402</v>
+      </c>
+      <c r="T3">
+        <f t="shared" si="0"/>
+        <v>1979.6036666666623</v>
+      </c>
+      <c r="U3">
+        <f t="shared" si="0"/>
+        <v>2049.9086666666553</v>
+      </c>
+      <c r="V3">
+        <f t="shared" si="0"/>
+        <v>2120.2136666666484</v>
+      </c>
+      <c r="W3">
+        <f t="shared" si="0"/>
+        <v>2190.5186666666414</v>
+      </c>
+      <c r="X3">
+        <f t="shared" si="0"/>
+        <v>2260.8236666666635</v>
+      </c>
+      <c r="Y3">
+        <f t="shared" si="0"/>
+        <v>2331.1286666666565</v>
+      </c>
+      <c r="Z3">
+        <f t="shared" si="0"/>
+        <v>2401.4336666666495</v>
+      </c>
+      <c r="AA3">
+        <f t="shared" si="0"/>
+        <v>2471.7386666666425</v>
+      </c>
+      <c r="AB3">
+        <f t="shared" si="0"/>
+        <v>2542.0436666666646</v>
+      </c>
+      <c r="AC3">
+        <f t="shared" si="0"/>
+        <v>2612.3486666666577</v>
+      </c>
+      <c r="AD3">
+        <f t="shared" si="0"/>
+        <v>2682.6536666666507</v>
+      </c>
+      <c r="AE3">
+        <f t="shared" si="0"/>
+        <v>2752.9586666666437</v>
+      </c>
+      <c r="AF3">
+        <f t="shared" si="0"/>
+        <v>2823.2636666666367</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A5" s="21" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="1">
+        <v>2020</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2025</v>
+      </c>
+      <c r="D6" s="1">
+        <v>2030</v>
+      </c>
+      <c r="E6" s="1">
+        <v>2035</v>
+      </c>
+      <c r="F6" s="1">
+        <v>2040</v>
+      </c>
+      <c r="G6" s="1">
+        <v>2045</v>
+      </c>
+      <c r="H6" s="1">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7">
+        <v>824.44</v>
+      </c>
+      <c r="C7">
+        <v>827.61</v>
+      </c>
+      <c r="D7">
+        <v>834.18</v>
+      </c>
+      <c r="E7">
+        <v>856.84</v>
+      </c>
+      <c r="F7">
+        <v>885.42</v>
+      </c>
+      <c r="G7">
+        <v>886.26</v>
+      </c>
+      <c r="H7">
+        <v>906.58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <f>(C7-$B$7)/$B$7</f>
+        <v>3.845034205036096E-3</v>
+      </c>
+      <c r="D8">
+        <f t="shared" ref="D8:H8" si="1">(D7-$B$7)/$B$7</f>
+        <v>1.181407986026866E-2</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="1"/>
+        <v>3.9299403231284238E-2</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="1"/>
+        <v>7.3965358303818229E-2</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="1"/>
+        <v>7.4984231720925637E-2</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="1"/>
+        <v>9.9631264858570642E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A11" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="1">
+        <v>2020</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2025</v>
+      </c>
+      <c r="D11" s="1">
+        <v>2030</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2035</v>
+      </c>
+      <c r="F11" s="1">
+        <v>2040</v>
+      </c>
+      <c r="G11" s="1">
+        <v>2045</v>
+      </c>
+      <c r="H11" s="1">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12">
+        <f>B3</f>
+        <v>665.08399999999995</v>
+      </c>
+      <c r="C12">
+        <f>(D3+D3*C8)</f>
+        <v>808.7919209887923</v>
+      </c>
+      <c r="D12">
+        <f>($C$12+$C$12*D8)</f>
+        <v>818.34705333369402</v>
+      </c>
+      <c r="E12">
+        <f t="shared" ref="E12:H12" si="2">($C$12+$C$12*E8)</f>
+        <v>840.57696082193581</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="2"/>
+        <v>868.61450521796178</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="2"/>
+        <v>869.43856180622845</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="2"/>
+        <v>889.37288308429879</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A15" s="21" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="1">
+        <v>2020</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2021</v>
+      </c>
+      <c r="D16" s="1">
+        <v>2022</v>
+      </c>
+      <c r="E16" s="1">
+        <v>2023</v>
+      </c>
+      <c r="F16" s="1">
+        <v>2024</v>
+      </c>
+      <c r="G16" s="1">
+        <v>2025</v>
+      </c>
+      <c r="H16" s="1">
+        <v>2026</v>
+      </c>
+      <c r="I16" s="1">
+        <v>2027</v>
+      </c>
+      <c r="J16" s="1">
+        <v>2028</v>
+      </c>
+      <c r="K16" s="1">
+        <v>2029</v>
+      </c>
+      <c r="L16" s="1">
+        <v>2030</v>
+      </c>
+      <c r="M16" s="1">
+        <v>2031</v>
+      </c>
+      <c r="N16" s="1">
+        <v>2032</v>
+      </c>
+      <c r="O16" s="1">
+        <v>2033</v>
+      </c>
+      <c r="P16" s="1">
+        <v>2034</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>2035</v>
+      </c>
+      <c r="R16" s="1">
+        <v>2036</v>
+      </c>
+      <c r="S16" s="1">
+        <v>2037</v>
+      </c>
+      <c r="T16" s="1">
+        <v>2038</v>
+      </c>
+      <c r="U16" s="1">
+        <v>2039</v>
+      </c>
+      <c r="V16" s="1">
+        <v>2040</v>
+      </c>
+      <c r="W16" s="1">
+        <v>2041</v>
+      </c>
+      <c r="X16" s="1">
+        <v>2042</v>
+      </c>
+      <c r="Y16" s="1">
+        <v>2043</v>
+      </c>
+      <c r="Z16" s="1">
+        <v>2044</v>
+      </c>
+      <c r="AA16" s="1">
+        <v>2045</v>
+      </c>
+      <c r="AB16" s="1">
+        <v>2046</v>
+      </c>
+      <c r="AC16" s="1">
+        <v>2047</v>
+      </c>
+      <c r="AD16" s="1">
+        <v>2048</v>
+      </c>
+      <c r="AE16" s="1">
+        <v>2049</v>
+      </c>
+      <c r="AF16" s="1">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17">
+        <f>B3</f>
+        <v>665.08399999999995</v>
+      </c>
+      <c r="C17">
+        <f t="shared" ref="C17:D17" si="3">C3</f>
+        <v>882.47799999999995</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="3"/>
+        <v>805.69399999999996</v>
+      </c>
+      <c r="E17">
+        <f>($D$17+($G$17-$D$17)*((E16-$D$16)/($G$16-$D$16)))</f>
+        <v>806.72664032959744</v>
+      </c>
+      <c r="F17">
+        <f>($D$17+($G$17-$D$17)*((F16-$D$16)/($G$16-$D$16)))</f>
+        <v>807.75928065919481</v>
+      </c>
+      <c r="G17">
+        <f>C12</f>
+        <v>808.7919209887923</v>
+      </c>
+      <c r="H17">
+        <f>($G$17+($L$17-$G$17)*((H16-$G$16)/($L$16-$G$16)))</f>
+        <v>810.70294745777267</v>
+      </c>
+      <c r="I17">
+        <f t="shared" ref="I17:K17" si="4">($G$17+($L$17-$G$17)*((I16-$G$16)/($L$16-$G$16)))</f>
+        <v>812.61397392675303</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="4"/>
+        <v>814.52500039573329</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="4"/>
+        <v>816.43602686471365</v>
+      </c>
+      <c r="L17">
+        <f>D12</f>
+        <v>818.34705333369402</v>
+      </c>
+      <c r="M17">
+        <f>($L$17+($Q$17-$L$17)*((M16-$L$16)/($Q$16-$L$16)))</f>
+        <v>822.79303483134242</v>
+      </c>
+      <c r="N17">
+        <f>($L$17+($Q$17-$L$17)*((N16-$L$16)/($Q$16-$L$16)))</f>
+        <v>827.23901632899072</v>
+      </c>
+      <c r="O17">
+        <f>($L$17+($Q$17-$L$17)*((O16-$L$16)/($Q$16-$L$16)))</f>
+        <v>831.68499782663912</v>
+      </c>
+      <c r="P17">
+        <f>($L$17+($Q$17-$L$17)*((P16-$L$16)/($Q$16-$L$16)))</f>
+        <v>836.13097932428741</v>
+      </c>
+      <c r="Q17">
+        <f>E12</f>
+        <v>840.57696082193581</v>
+      </c>
+      <c r="R17">
+        <f>($Q$17+($V$17-$Q$17)*((R16-$Q$16)/($V$16-$Q$16)))</f>
+        <v>846.18446970114098</v>
+      </c>
+      <c r="S17">
+        <f>($Q$17+($V$17-$Q$17)*((S16-$Q$16)/($V$16-$Q$16)))</f>
+        <v>851.79197858034615</v>
+      </c>
+      <c r="T17">
+        <f>($Q$17+($V$17-$Q$17)*((T16-$Q$16)/($V$16-$Q$16)))</f>
+        <v>857.39948745955144</v>
+      </c>
+      <c r="U17">
+        <f>($Q$17+($V$17-$Q$17)*((U16-$Q$16)/($V$16-$Q$16)))</f>
+        <v>863.00699633875661</v>
+      </c>
+      <c r="V17">
+        <f>F12</f>
+        <v>868.61450521796178</v>
+      </c>
+      <c r="W17">
+        <f>($V$17+($AA$17-$V$17)*((W16-$V$16)/($AA$16-$V$16)))</f>
+        <v>868.77931653561507</v>
+      </c>
+      <c r="X17">
+        <f t="shared" ref="X17:Z17" si="5">($V$17+($AA$17-$V$17)*((X16-$V$16)/($AA$16-$V$16)))</f>
+        <v>868.94412785326847</v>
+      </c>
+      <c r="Y17">
+        <f t="shared" si="5"/>
+        <v>869.10893917092176</v>
+      </c>
+      <c r="Z17">
+        <f t="shared" si="5"/>
+        <v>869.27375048857516</v>
+      </c>
+      <c r="AA17">
+        <f>G12</f>
+        <v>869.43856180622845</v>
+      </c>
+      <c r="AB17">
+        <f>($AA$17+($AF$17-$AA$17)*((AB16-$AA$16)/($AF$16-$AA$16)))</f>
+        <v>873.42542606184247</v>
+      </c>
+      <c r="AC17">
+        <f t="shared" ref="AC17:AE17" si="6">($AA$17+($AF$17-$AA$17)*((AC16-$AA$16)/($AF$16-$AA$16)))</f>
+        <v>877.41229031745661</v>
+      </c>
+      <c r="AD17">
+        <f t="shared" si="6"/>
+        <v>881.39915457307063</v>
+      </c>
+      <c r="AE17">
+        <f t="shared" si="6"/>
+        <v>885.38601882868477</v>
+      </c>
+      <c r="AF17">
+        <f>H12</f>
+        <v>889.37288308429879</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A18" s="4"/>
+    </row>
+    <row r="19" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A19" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="26"/>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A20" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="13">
-        <v>908066332363945.25</v>
-      </c>
-      <c r="C2" s="13">
-        <v>726204322679458.5</v>
-      </c>
-      <c r="D2" s="13">
-        <v>839121579035849.25</v>
-      </c>
-      <c r="E2" s="13">
-        <v>874712069778537.62</v>
-      </c>
-      <c r="F2" s="13">
-        <v>854112479205995.62</v>
-      </c>
-      <c r="G2" s="13">
-        <v>1973225015654828</v>
-      </c>
-      <c r="H2" s="13">
-        <v>1245646946790318.2</v>
-      </c>
-      <c r="I2" s="13">
-        <v>915577409855144.38</v>
-      </c>
-      <c r="J2" s="13">
-        <v>1179953485182655.8</v>
-      </c>
-      <c r="K2" s="13">
-        <v>1132596244208690.5</v>
-      </c>
-      <c r="L2" s="13">
-        <v>1184463676030746</v>
-      </c>
-      <c r="M2" s="13">
-        <v>1129708865473567.2</v>
-      </c>
-      <c r="N2" s="13">
-        <v>1339596237688777</v>
-      </c>
-      <c r="O2" s="13">
-        <v>2427047908322861</v>
-      </c>
-      <c r="P2" s="13">
-        <v>2621326240834337</v>
-      </c>
-      <c r="Q2" s="13">
-        <v>1573713706255844.2</v>
-      </c>
-      <c r="R2" s="13">
-        <v>1201775417449594.5</v>
-      </c>
-      <c r="S2" s="13">
-        <v>852790016028065</v>
-      </c>
-      <c r="T2" s="13">
-        <v>963933618742378.88</v>
-      </c>
-      <c r="U2" s="13">
-        <v>342440028055332.06</v>
-      </c>
-      <c r="V2" s="13">
-        <v>277144032250903.78</v>
-      </c>
-      <c r="W2" s="13">
-        <v>324149965481829.88</v>
-      </c>
-      <c r="X2" s="13">
-        <v>172897475778987.47</v>
-      </c>
-      <c r="Y2" s="13">
-        <v>411276025337924.81</v>
-      </c>
-      <c r="Z2" s="13">
-        <v>259775337434062.5</v>
-      </c>
-      <c r="AA2" s="13">
-        <v>373263852526950.88</v>
-      </c>
-      <c r="AB2" s="13">
-        <v>436546377161111.81</v>
-      </c>
-      <c r="AC2" s="13">
-        <v>313282465310611.69</v>
-      </c>
-      <c r="AD2" s="13">
-        <v>362155719578151.5</v>
-      </c>
-      <c r="AE2" s="13">
-        <v>567067303185964</v>
-      </c>
-      <c r="AF2" s="13">
-        <v>665083900964468</v>
-      </c>
-      <c r="AG2" s="13">
-        <v>882477987272240.88</v>
-      </c>
-      <c r="AH2" s="13">
-        <v>805693940844518</v>
-      </c>
-      <c r="AI2" s="13">
-        <v>737554850928654.75</v>
-      </c>
-      <c r="AJ2" s="13">
-        <v>675178415215819.88</v>
-      </c>
-      <c r="AK2" s="13">
-        <v>618077274929946.75</v>
-      </c>
-      <c r="AL2" s="13">
-        <v>565805288166264.88</v>
-      </c>
-      <c r="AM2" s="13">
-        <v>517954044101029.88</v>
-      </c>
-      <c r="AN2" s="13">
-        <v>474149672001257.69</v>
-      </c>
-      <c r="AO2" s="13">
-        <v>434049920102657.31</v>
-      </c>
-      <c r="AP2" s="13">
-        <v>397341481532488.56</v>
-      </c>
-      <c r="AQ2" s="13">
-        <v>363737546384279.06</v>
-      </c>
-      <c r="AR2" s="13">
-        <v>332975560818302.44</v>
-      </c>
-      <c r="AS2" s="13">
-        <v>304815175679249.12</v>
-      </c>
-      <c r="AT2" s="13">
-        <v>279036368603255.31</v>
-      </c>
-      <c r="AU2" s="13">
-        <v>255437724941961.66</v>
-      </c>
-      <c r="AV2" s="13">
-        <v>233834864072138.25</v>
-      </c>
-      <c r="AW2" s="13">
-        <v>214058998795338.44</v>
-      </c>
-      <c r="AX2" s="13">
-        <v>195955616571901.84</v>
-      </c>
-      <c r="AY2" s="13">
-        <v>179383272285539.69</v>
-      </c>
-      <c r="AZ2" s="13">
-        <v>164212483106147.12</v>
-      </c>
-      <c r="BA2" s="13">
-        <v>150324716816197.78</v>
-      </c>
-      <c r="BB2" s="13">
-        <v>137611465696325.88</v>
-      </c>
-      <c r="BC2" s="13">
-        <v>125973398734189.95</v>
-      </c>
-      <c r="BD2" s="13">
-        <v>115319585532667.64</v>
-      </c>
-      <c r="BE2" s="13">
-        <v>105566785853630.58</v>
-      </c>
-      <c r="BF2" s="13">
-        <v>96638799246372.031</v>
-      </c>
-      <c r="BG2" s="13">
-        <v>88465869679212.312</v>
-      </c>
-      <c r="BH2" s="13">
-        <v>80984140522557.078</v>
-      </c>
-      <c r="BI2" s="13">
-        <v>74135155625089.281</v>
-      </c>
-      <c r="BJ2" s="13">
-        <v>67865402584909.328</v>
-      </c>
-    </row>
-    <row r="3" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="A3" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="22">
-        <v>837000000000000</v>
-      </c>
-      <c r="C3" s="22">
-        <v>840000000000000</v>
-      </c>
-      <c r="D3" s="22">
-        <v>1050000000000000</v>
-      </c>
-      <c r="E3" s="22">
-        <v>1160000000000000</v>
-      </c>
-      <c r="F3" s="22">
-        <v>1170000000000000</v>
-      </c>
-      <c r="G3" s="22">
-        <v>1230000000000000</v>
-      </c>
-      <c r="H3" s="22">
-        <v>1290000000000000</v>
-      </c>
-      <c r="I3" s="22">
-        <v>1130000000000000</v>
-      </c>
-      <c r="J3" s="22">
-        <v>1110000000000000</v>
-      </c>
-      <c r="K3" s="22">
-        <v>1190000000000000</v>
-      </c>
-      <c r="L3" s="22">
-        <v>1440000000000000</v>
-      </c>
-      <c r="M3" s="22">
-        <v>1740000000000000</v>
-      </c>
-      <c r="N3" s="22">
-        <v>1820000000000000</v>
-      </c>
-      <c r="O3" s="22">
-        <v>1830000000000000</v>
-      </c>
-      <c r="P3" s="22">
-        <v>1740000000000000</v>
-      </c>
-      <c r="Q3" s="22">
-        <v>1440000000000000</v>
-      </c>
-      <c r="R3" s="22">
-        <v>987000000000000</v>
-      </c>
-      <c r="S3" s="22">
-        <v>728000000000000</v>
-      </c>
-      <c r="T3" s="22">
-        <v>552000000000000</v>
-      </c>
-      <c r="U3" s="22">
-        <v>416000000000000</v>
-      </c>
-      <c r="V3" s="22">
-        <v>306000000000000</v>
-      </c>
-      <c r="W3" s="22">
-        <v>289000000000000</v>
-      </c>
-      <c r="X3" s="22">
-        <v>308000000000000</v>
-      </c>
-      <c r="Y3" s="22">
-        <v>331000000000000</v>
-      </c>
-      <c r="Z3" s="22">
-        <v>359000000000000</v>
-      </c>
-      <c r="AA3" s="22">
-        <v>349000000000000</v>
-      </c>
-      <c r="AB3" s="22">
-        <v>410000000000000</v>
-      </c>
-      <c r="AC3" s="22">
-        <v>469000000000000</v>
-      </c>
-      <c r="AD3" s="22">
-        <v>558000000000000</v>
-      </c>
-      <c r="AE3" s="22">
-        <v>556000000000000</v>
-      </c>
-      <c r="AF3" s="22">
-        <v>632000000000000</v>
-      </c>
-      <c r="AG3" s="22">
-        <v>853000000000000</v>
-      </c>
-      <c r="AH3" s="22">
-        <v>844000000000000</v>
-      </c>
-      <c r="AI3" s="22">
-        <v>780000000000000</v>
-      </c>
-      <c r="AJ3" s="22">
-        <v>623000000000000</v>
-      </c>
-      <c r="AK3" s="22">
-        <v>570000000000000</v>
-      </c>
-      <c r="AL3" s="22">
-        <v>522000000000000</v>
-      </c>
-      <c r="AM3" s="22">
-        <v>478000000000000</v>
-      </c>
-      <c r="AN3" s="22">
-        <v>437000000000000</v>
-      </c>
-      <c r="AO3" s="22">
-        <v>400000000000000</v>
-      </c>
-      <c r="AP3" s="22">
-        <v>367000000000000</v>
-      </c>
-      <c r="AQ3" s="22">
-        <v>336000000000000</v>
-      </c>
-      <c r="AR3" s="22">
-        <v>307000000000000</v>
-      </c>
-      <c r="AS3" s="22">
-        <v>281000000000000</v>
-      </c>
-      <c r="AT3" s="22">
-        <v>257000000000000</v>
-      </c>
-      <c r="AU3" s="22">
-        <v>236000000000000</v>
-      </c>
-      <c r="AV3" s="22">
-        <v>216000000000000</v>
-      </c>
-      <c r="AW3" s="22">
-        <v>197000000000000</v>
-      </c>
-      <c r="AX3" s="22">
-        <v>181000000000000</v>
-      </c>
-      <c r="AY3" s="22">
-        <v>165000000000000</v>
-      </c>
-      <c r="AZ3" s="22">
-        <v>152000000000000</v>
-      </c>
-      <c r="BA3" s="22">
-        <v>139000000000000</v>
-      </c>
-      <c r="BB3" s="22">
-        <v>127000000000000</v>
-      </c>
-      <c r="BC3" s="22">
-        <v>116000000000000</v>
-      </c>
-      <c r="BD3" s="22">
-        <v>106000000000000</v>
-      </c>
-      <c r="BE3" s="22">
-        <v>97400000000000</v>
-      </c>
-      <c r="BF3" s="22">
-        <v>89200000000000</v>
-      </c>
-      <c r="BG3" s="22">
-        <v>81600000000000</v>
-      </c>
-      <c r="BH3" s="22">
-        <v>77900000000000</v>
-      </c>
-      <c r="BI3" s="22">
-        <v>74300000000000</v>
-      </c>
-      <c r="BJ3" s="22">
-        <v>71000000000000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="A4" s="4"/>
-    </row>
-    <row r="5" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="A5" s="4"/>
-    </row>
-    <row r="6" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="A6" s="4"/>
-    </row>
-    <row r="7" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="A7" s="4"/>
-    </row>
-    <row r="8" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="A8" s="4"/>
-    </row>
-    <row r="9" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="A9" s="4"/>
-    </row>
-    <row r="10" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="A10" s="4"/>
-    </row>
-    <row r="11" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="A11" s="4"/>
-    </row>
-    <row r="12" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="A12" s="4"/>
-    </row>
-    <row r="13" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="A13" s="4"/>
-    </row>
-    <row r="14" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="A14" s="4"/>
-    </row>
-    <row r="15" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="A15" s="4"/>
-    </row>
-    <row r="16" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="A16" s="4"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" s="4"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" s="4"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" s="4"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20" s="4"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B20" s="23">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A22" s="4"/>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A23" s="4"/>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A24" s="4"/>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A25" s="4"/>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A26" s="4"/>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A27" s="4"/>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A22" s="21" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="21" t="str">
+        <f>A16</f>
+        <v>Year</v>
+      </c>
+      <c r="B23" s="17">
+        <f t="shared" ref="B23:AF23" si="7">B16</f>
+        <v>2020</v>
+      </c>
+      <c r="C23" s="17">
+        <f t="shared" si="7"/>
+        <v>2021</v>
+      </c>
+      <c r="D23" s="17">
+        <f t="shared" si="7"/>
+        <v>2022</v>
+      </c>
+      <c r="E23" s="17">
+        <f t="shared" si="7"/>
+        <v>2023</v>
+      </c>
+      <c r="F23" s="17">
+        <f t="shared" si="7"/>
+        <v>2024</v>
+      </c>
+      <c r="G23" s="17">
+        <f t="shared" si="7"/>
+        <v>2025</v>
+      </c>
+      <c r="H23" s="17">
+        <f t="shared" si="7"/>
+        <v>2026</v>
+      </c>
+      <c r="I23" s="17">
+        <f t="shared" si="7"/>
+        <v>2027</v>
+      </c>
+      <c r="J23" s="17">
+        <f t="shared" si="7"/>
+        <v>2028</v>
+      </c>
+      <c r="K23" s="17">
+        <f t="shared" si="7"/>
+        <v>2029</v>
+      </c>
+      <c r="L23" s="17">
+        <f t="shared" si="7"/>
+        <v>2030</v>
+      </c>
+      <c r="M23" s="17">
+        <f t="shared" si="7"/>
+        <v>2031</v>
+      </c>
+      <c r="N23" s="17">
+        <f t="shared" si="7"/>
+        <v>2032</v>
+      </c>
+      <c r="O23" s="17">
+        <f t="shared" si="7"/>
+        <v>2033</v>
+      </c>
+      <c r="P23" s="17">
+        <f t="shared" si="7"/>
+        <v>2034</v>
+      </c>
+      <c r="Q23" s="17">
+        <f t="shared" si="7"/>
+        <v>2035</v>
+      </c>
+      <c r="R23" s="17">
+        <f t="shared" si="7"/>
+        <v>2036</v>
+      </c>
+      <c r="S23" s="17">
+        <f t="shared" si="7"/>
+        <v>2037</v>
+      </c>
+      <c r="T23" s="17">
+        <f t="shared" si="7"/>
+        <v>2038</v>
+      </c>
+      <c r="U23" s="17">
+        <f t="shared" si="7"/>
+        <v>2039</v>
+      </c>
+      <c r="V23" s="17">
+        <f t="shared" si="7"/>
+        <v>2040</v>
+      </c>
+      <c r="W23" s="17">
+        <f t="shared" si="7"/>
+        <v>2041</v>
+      </c>
+      <c r="X23" s="17">
+        <f t="shared" si="7"/>
+        <v>2042</v>
+      </c>
+      <c r="Y23" s="17">
+        <f t="shared" si="7"/>
+        <v>2043</v>
+      </c>
+      <c r="Z23" s="17">
+        <f t="shared" si="7"/>
+        <v>2044</v>
+      </c>
+      <c r="AA23" s="17">
+        <f t="shared" si="7"/>
+        <v>2045</v>
+      </c>
+      <c r="AB23" s="17">
+        <f t="shared" si="7"/>
+        <v>2046</v>
+      </c>
+      <c r="AC23" s="17">
+        <f t="shared" si="7"/>
+        <v>2047</v>
+      </c>
+      <c r="AD23" s="17">
+        <f t="shared" si="7"/>
+        <v>2048</v>
+      </c>
+      <c r="AE23" s="17">
+        <f t="shared" si="7"/>
+        <v>2049</v>
+      </c>
+      <c r="AF23" s="17">
+        <f t="shared" si="7"/>
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="str">
+        <f>A17</f>
+        <v>Land use emissions (Mt CO2e)</v>
+      </c>
+      <c r="B24" s="13">
+        <f t="shared" ref="B24:AF24" si="8">B17</f>
+        <v>665.08399999999995</v>
+      </c>
+      <c r="C24" s="13">
+        <f t="shared" si="8"/>
+        <v>882.47799999999995</v>
+      </c>
+      <c r="D24" s="13">
+        <f t="shared" si="8"/>
+        <v>805.69399999999996</v>
+      </c>
+      <c r="E24" s="13">
+        <f t="shared" si="8"/>
+        <v>806.72664032959744</v>
+      </c>
+      <c r="F24" s="13">
+        <f t="shared" si="8"/>
+        <v>807.75928065919481</v>
+      </c>
+      <c r="G24" s="13">
+        <f t="shared" si="8"/>
+        <v>808.7919209887923</v>
+      </c>
+      <c r="H24" s="13">
+        <f t="shared" si="8"/>
+        <v>810.70294745777267</v>
+      </c>
+      <c r="I24" s="13">
+        <f t="shared" si="8"/>
+        <v>812.61397392675303</v>
+      </c>
+      <c r="J24" s="13">
+        <f t="shared" si="8"/>
+        <v>814.52500039573329</v>
+      </c>
+      <c r="K24" s="13">
+        <f t="shared" si="8"/>
+        <v>816.43602686471365</v>
+      </c>
+      <c r="L24" s="13">
+        <f t="shared" si="8"/>
+        <v>818.34705333369402</v>
+      </c>
+      <c r="M24" s="13">
+        <f t="shared" si="8"/>
+        <v>822.79303483134242</v>
+      </c>
+      <c r="N24" s="13">
+        <f t="shared" si="8"/>
+        <v>827.23901632899072</v>
+      </c>
+      <c r="O24" s="13">
+        <f t="shared" si="8"/>
+        <v>831.68499782663912</v>
+      </c>
+      <c r="P24" s="13">
+        <f t="shared" si="8"/>
+        <v>836.13097932428741</v>
+      </c>
+      <c r="Q24" s="13">
+        <f t="shared" si="8"/>
+        <v>840.57696082193581</v>
+      </c>
+      <c r="R24" s="13">
+        <f t="shared" si="8"/>
+        <v>846.18446970114098</v>
+      </c>
+      <c r="S24" s="13">
+        <f t="shared" si="8"/>
+        <v>851.79197858034615</v>
+      </c>
+      <c r="T24" s="13">
+        <f t="shared" si="8"/>
+        <v>857.39948745955144</v>
+      </c>
+      <c r="U24" s="13">
+        <f t="shared" si="8"/>
+        <v>863.00699633875661</v>
+      </c>
+      <c r="V24" s="13">
+        <f t="shared" si="8"/>
+        <v>868.61450521796178</v>
+      </c>
+      <c r="W24" s="13">
+        <f t="shared" si="8"/>
+        <v>868.77931653561507</v>
+      </c>
+      <c r="X24" s="13">
+        <f t="shared" si="8"/>
+        <v>868.94412785326847</v>
+      </c>
+      <c r="Y24" s="13">
+        <f t="shared" si="8"/>
+        <v>869.10893917092176</v>
+      </c>
+      <c r="Z24" s="13">
+        <f t="shared" si="8"/>
+        <v>869.27375048857516</v>
+      </c>
+      <c r="AA24" s="13">
+        <f t="shared" si="8"/>
+        <v>869.43856180622845</v>
+      </c>
+      <c r="AB24" s="13">
+        <f t="shared" si="8"/>
+        <v>873.42542606184247</v>
+      </c>
+      <c r="AC24" s="13">
+        <f t="shared" si="8"/>
+        <v>877.41229031745661</v>
+      </c>
+      <c r="AD24" s="13">
+        <f t="shared" si="8"/>
+        <v>881.39915457307063</v>
+      </c>
+      <c r="AE24" s="13">
+        <f t="shared" si="8"/>
+        <v>885.38601882868477</v>
+      </c>
+      <c r="AF24" s="13">
+        <f t="shared" si="8"/>
+        <v>889.37288308429879</v>
+      </c>
+    </row>
+    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B25">
+        <f>B24</f>
+        <v>665.08399999999995</v>
+      </c>
+      <c r="C25">
+        <f>$B$20*C24+(1-$B$20)*B25</f>
+        <v>730.30219999999986</v>
+      </c>
+      <c r="D25">
+        <f t="shared" ref="D25:AF25" si="9">$B$20*D24+(1-$B$20)*C25</f>
+        <v>752.91973999999982</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="9"/>
+        <v>769.06181009887905</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="9"/>
+        <v>780.67105126697368</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="9"/>
+        <v>789.10731218351918</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="9"/>
+        <v>795.58600276579523</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="9"/>
+        <v>800.69439411408257</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="9"/>
+        <v>804.84357599857765</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="9"/>
+        <v>808.3213112584184</v>
+      </c>
+      <c r="L25">
+        <f t="shared" si="9"/>
+        <v>811.32903388100101</v>
+      </c>
+      <c r="M25">
+        <f t="shared" si="9"/>
+        <v>814.76823416610341</v>
+      </c>
+      <c r="N25">
+        <f t="shared" si="9"/>
+        <v>818.50946881496952</v>
+      </c>
+      <c r="O25">
+        <f t="shared" si="9"/>
+        <v>822.46212751847042</v>
+      </c>
+      <c r="P25">
+        <f t="shared" si="9"/>
+        <v>826.56278306021545</v>
+      </c>
+      <c r="Q25">
+        <f t="shared" si="9"/>
+        <v>830.76703638873153</v>
+      </c>
+      <c r="R25">
+        <f t="shared" si="9"/>
+        <v>835.3922663824543</v>
+      </c>
+      <c r="S25">
+        <f t="shared" si="9"/>
+        <v>840.31218004182188</v>
+      </c>
+      <c r="T25">
+        <f t="shared" si="9"/>
+        <v>845.43837226714072</v>
+      </c>
+      <c r="U25">
+        <f t="shared" si="9"/>
+        <v>850.7089594886254</v>
+      </c>
+      <c r="V25">
+        <f t="shared" si="9"/>
+        <v>856.08062320742624</v>
+      </c>
+      <c r="W25">
+        <f t="shared" si="9"/>
+        <v>859.89023120588286</v>
+      </c>
+      <c r="X25">
+        <f t="shared" si="9"/>
+        <v>862.60640020009851</v>
+      </c>
+      <c r="Y25">
+        <f t="shared" si="9"/>
+        <v>864.55716189134546</v>
+      </c>
+      <c r="Z25">
+        <f t="shared" si="9"/>
+        <v>865.97213847051432</v>
+      </c>
+      <c r="AA25">
+        <f t="shared" si="9"/>
+        <v>867.01206547122842</v>
+      </c>
+      <c r="AB25">
+        <f t="shared" si="9"/>
+        <v>868.9360736484125</v>
+      </c>
+      <c r="AC25">
+        <f t="shared" si="9"/>
+        <v>871.47893864912567</v>
+      </c>
+      <c r="AD25">
+        <f t="shared" si="9"/>
+        <v>874.45500342630908</v>
+      </c>
+      <c r="AE25">
+        <f t="shared" si="9"/>
+        <v>877.73430804702184</v>
+      </c>
+      <c r="AF25">
+        <f t="shared" si="9"/>
+        <v>881.22588055820484</v>
+      </c>
+    </row>
+    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26">
+        <f>B25*$B$27</f>
+        <v>665084000000000</v>
+      </c>
+      <c r="C26">
+        <f t="shared" ref="C26:AF26" si="10">C25*$B$27</f>
+        <v>730302199999999.87</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="10"/>
+        <v>752919739999999.87</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="10"/>
+        <v>769061810098879</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="10"/>
+        <v>780671051266973.62</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="10"/>
+        <v>789107312183519.12</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="10"/>
+        <v>795586002765795.25</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="10"/>
+        <v>800694394114082.62</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="10"/>
+        <v>804843575998577.62</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="10"/>
+        <v>808321311258418.37</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="10"/>
+        <v>811329033881001</v>
+      </c>
+      <c r="M26">
+        <f t="shared" si="10"/>
+        <v>814768234166103.37</v>
+      </c>
+      <c r="N26">
+        <f t="shared" si="10"/>
+        <v>818509468814969.5</v>
+      </c>
+      <c r="O26">
+        <f t="shared" si="10"/>
+        <v>822462127518470.37</v>
+      </c>
+      <c r="P26">
+        <f t="shared" si="10"/>
+        <v>826562783060215.5</v>
+      </c>
+      <c r="Q26">
+        <f t="shared" si="10"/>
+        <v>830767036388731.5</v>
+      </c>
+      <c r="R26">
+        <f t="shared" si="10"/>
+        <v>835392266382454.25</v>
+      </c>
+      <c r="S26">
+        <f t="shared" si="10"/>
+        <v>840312180041821.87</v>
+      </c>
+      <c r="T26">
+        <f t="shared" si="10"/>
+        <v>845438372267140.75</v>
+      </c>
+      <c r="U26">
+        <f t="shared" si="10"/>
+        <v>850708959488625.37</v>
+      </c>
+      <c r="V26">
+        <f t="shared" si="10"/>
+        <v>856080623207426.25</v>
+      </c>
+      <c r="W26">
+        <f t="shared" si="10"/>
+        <v>859890231205882.87</v>
+      </c>
+      <c r="X26">
+        <f t="shared" si="10"/>
+        <v>862606400200098.5</v>
+      </c>
+      <c r="Y26">
+        <f t="shared" si="10"/>
+        <v>864557161891345.5</v>
+      </c>
+      <c r="Z26">
+        <f t="shared" si="10"/>
+        <v>865972138470514.37</v>
+      </c>
+      <c r="AA26">
+        <f t="shared" si="10"/>
+        <v>867012065471228.37</v>
+      </c>
+      <c r="AB26">
+        <f t="shared" si="10"/>
+        <v>868936073648412.5</v>
+      </c>
+      <c r="AC26">
+        <f t="shared" si="10"/>
+        <v>871478938649125.62</v>
+      </c>
+      <c r="AD26">
+        <f t="shared" si="10"/>
+        <v>874455003426309.12</v>
+      </c>
+      <c r="AE26">
+        <f t="shared" si="10"/>
+        <v>877734308047021.87</v>
+      </c>
+      <c r="AF26">
+        <f t="shared" si="10"/>
+        <v>881225880558204.87</v>
+      </c>
+    </row>
+    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A27" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="B27" s="25">
+        <v>1000000000000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A31" s="4"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A32" s="4"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A33" s="4"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A34" s="4"/>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A35" s="4"/>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A36" s="4"/>
-    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A19:B19"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC4E7FB-2748-A046-8AEB-50CFC4E5E4C4}">
-  <dimension ref="A1:BJ24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:BJ19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.5" customWidth="1"/>
-    <col min="2" max="11" width="14.1640625" customWidth="1"/>
-    <col min="12" max="12" width="12.1640625" customWidth="1"/>
-    <col min="13" max="13" width="10.83203125" customWidth="1"/>
-    <col min="14" max="17" width="14.1640625" customWidth="1"/>
-    <col min="18" max="18" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.42578125" customWidth="1"/>
+    <col min="2" max="11" width="14.140625" customWidth="1"/>
+    <col min="12" max="12" width="12.140625" customWidth="1"/>
+    <col min="13" max="13" width="10.85546875" customWidth="1"/>
+    <col min="14" max="17" width="14.140625" customWidth="1"/>
+    <col min="18" max="18" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="11" bestFit="1" customWidth="1"/>
-    <col min="20" max="31" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="31" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="11" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="15">
-        <v>1990</v>
-      </c>
-      <c r="C1" s="15">
-        <v>1991</v>
-      </c>
-      <c r="D1" s="15">
-        <v>1992</v>
-      </c>
-      <c r="E1" s="15">
-        <v>1993</v>
-      </c>
-      <c r="F1" s="15">
-        <v>1994</v>
-      </c>
-      <c r="G1" s="15">
-        <v>1995</v>
-      </c>
-      <c r="H1" s="15">
-        <v>1996</v>
-      </c>
-      <c r="I1" s="15">
-        <v>1997</v>
-      </c>
-      <c r="J1" s="15">
-        <v>1998</v>
-      </c>
-      <c r="K1" s="15">
-        <v>1999</v>
-      </c>
-      <c r="L1" s="15">
-        <v>2000</v>
-      </c>
-      <c r="M1" s="15">
-        <v>2001</v>
-      </c>
-      <c r="N1" s="15">
-        <v>2002</v>
-      </c>
-      <c r="O1" s="15">
-        <v>2003</v>
-      </c>
-      <c r="P1" s="15">
-        <v>2004</v>
-      </c>
-      <c r="Q1" s="15">
-        <v>2005</v>
-      </c>
-      <c r="R1" s="1">
-        <v>2006</v>
-      </c>
-      <c r="S1" s="1">
-        <v>2007</v>
-      </c>
-      <c r="T1" s="1">
-        <v>2008</v>
-      </c>
-      <c r="U1" s="1">
-        <v>2009</v>
-      </c>
-      <c r="V1" s="1">
-        <v>2010</v>
-      </c>
-      <c r="W1" s="1">
-        <v>2011</v>
-      </c>
-      <c r="X1" s="1">
-        <v>2012</v>
-      </c>
-      <c r="Y1" s="1">
-        <v>2013</v>
-      </c>
-      <c r="Z1" s="1">
-        <v>2014</v>
-      </c>
-      <c r="AA1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="AB1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="AC1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="AD1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="AE1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="AF1" s="1">
+      <c r="B1" s="17">
         <v>2020</v>
       </c>
-      <c r="AG1" s="1">
+      <c r="C1" s="17">
         <v>2021</v>
       </c>
-      <c r="AH1" s="1">
+      <c r="D1" s="17">
         <v>2022</v>
       </c>
-      <c r="AI1" s="1">
+      <c r="E1" s="17">
         <v>2023</v>
       </c>
-      <c r="AJ1" s="1">
+      <c r="F1" s="17">
         <v>2024</v>
       </c>
-      <c r="AK1" s="1">
+      <c r="G1" s="17">
         <v>2025</v>
       </c>
-      <c r="AL1" s="1">
+      <c r="H1" s="17">
         <v>2026</v>
       </c>
-      <c r="AM1" s="1">
+      <c r="I1" s="17">
         <v>2027</v>
       </c>
-      <c r="AN1" s="1">
+      <c r="J1" s="17">
         <v>2028</v>
       </c>
-      <c r="AO1" s="1">
+      <c r="K1" s="17">
         <v>2029</v>
       </c>
-      <c r="AP1" s="1">
+      <c r="L1" s="17">
         <v>2030</v>
       </c>
-      <c r="AQ1" s="1">
+      <c r="M1" s="17">
         <v>2031</v>
       </c>
-      <c r="AR1" s="1">
+      <c r="N1" s="17">
         <v>2032</v>
       </c>
-      <c r="AS1" s="1">
+      <c r="O1" s="17">
         <v>2033</v>
       </c>
-      <c r="AT1" s="1">
+      <c r="P1" s="17">
         <v>2034</v>
       </c>
-      <c r="AU1" s="1">
+      <c r="Q1" s="17">
         <v>2035</v>
       </c>
-      <c r="AV1" s="1">
+      <c r="R1" s="17">
         <v>2036</v>
       </c>
-      <c r="AW1" s="1">
+      <c r="S1" s="17">
         <v>2037</v>
       </c>
-      <c r="AX1" s="1">
+      <c r="T1" s="17">
         <v>2038</v>
       </c>
-      <c r="AY1" s="1">
+      <c r="U1" s="17">
         <v>2039</v>
       </c>
-      <c r="AZ1" s="1">
+      <c r="V1" s="17">
         <v>2040</v>
       </c>
-      <c r="BA1" s="1">
+      <c r="W1" s="17">
         <v>2041</v>
       </c>
-      <c r="BB1" s="1">
+      <c r="X1" s="17">
         <v>2042</v>
       </c>
-      <c r="BC1" s="1">
+      <c r="Y1" s="17">
         <v>2043</v>
       </c>
-      <c r="BD1" s="1">
+      <c r="Z1" s="17">
         <v>2044</v>
       </c>
-      <c r="BE1" s="1">
+      <c r="AA1" s="17">
         <v>2045</v>
       </c>
-      <c r="BF1" s="1">
+      <c r="AB1" s="17">
         <v>2046</v>
       </c>
-      <c r="BG1" s="1">
+      <c r="AC1" s="17">
         <v>2047</v>
       </c>
-      <c r="BH1" s="1">
+      <c r="AD1" s="17">
         <v>2048</v>
       </c>
-      <c r="BI1" s="1">
+      <c r="AE1" s="17">
         <v>2049</v>
       </c>
-      <c r="BJ1" s="1">
+      <c r="AF1" s="17">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" s="3">
+        <f>'EPE-Land use emissions'!B26</f>
+        <v>665084000000000</v>
+      </c>
+      <c r="C2" s="3">
+        <f>'EPE-Land use emissions'!C26</f>
+        <v>730302199999999.87</v>
+      </c>
+      <c r="D2" s="3">
+        <f>'EPE-Land use emissions'!D26</f>
+        <v>752919739999999.87</v>
+      </c>
+      <c r="E2" s="3">
+        <f>'EPE-Land use emissions'!E26</f>
+        <v>769061810098879</v>
+      </c>
+      <c r="F2" s="3">
+        <f>'EPE-Land use emissions'!F26</f>
+        <v>780671051266973.62</v>
+      </c>
+      <c r="G2" s="3">
+        <f>'EPE-Land use emissions'!G26</f>
+        <v>789107312183519.12</v>
+      </c>
+      <c r="H2" s="3">
+        <f>'EPE-Land use emissions'!H26</f>
+        <v>795586002765795.25</v>
+      </c>
+      <c r="I2" s="3">
+        <f>'EPE-Land use emissions'!I26</f>
+        <v>800694394114082.62</v>
+      </c>
+      <c r="J2" s="3">
+        <f>'EPE-Land use emissions'!J26</f>
+        <v>804843575998577.62</v>
+      </c>
+      <c r="K2" s="3">
+        <f>'EPE-Land use emissions'!K26</f>
+        <v>808321311258418.37</v>
+      </c>
+      <c r="L2" s="3">
+        <f>'EPE-Land use emissions'!L26</f>
+        <v>811329033881001</v>
+      </c>
+      <c r="M2" s="3">
+        <f>'EPE-Land use emissions'!M26</f>
+        <v>814768234166103.37</v>
+      </c>
+      <c r="N2" s="3">
+        <f>'EPE-Land use emissions'!N26</f>
+        <v>818509468814969.5</v>
+      </c>
+      <c r="O2" s="3">
+        <f>'EPE-Land use emissions'!O26</f>
+        <v>822462127518470.37</v>
+      </c>
+      <c r="P2" s="3">
+        <f>'EPE-Land use emissions'!P26</f>
+        <v>826562783060215.5</v>
+      </c>
+      <c r="Q2" s="3">
+        <f>'EPE-Land use emissions'!Q26</f>
+        <v>830767036388731.5</v>
+      </c>
+      <c r="R2" s="3">
+        <f>'EPE-Land use emissions'!R26</f>
+        <v>835392266382454.25</v>
+      </c>
+      <c r="S2" s="3">
+        <f>'EPE-Land use emissions'!S26</f>
+        <v>840312180041821.87</v>
+      </c>
+      <c r="T2" s="3">
+        <f>'EPE-Land use emissions'!T26</f>
+        <v>845438372267140.75</v>
+      </c>
+      <c r="U2" s="3">
+        <f>'EPE-Land use emissions'!U26</f>
+        <v>850708959488625.37</v>
+      </c>
+      <c r="V2" s="3">
+        <f>'EPE-Land use emissions'!V26</f>
+        <v>856080623207426.25</v>
+      </c>
+      <c r="W2" s="3">
+        <f>'EPE-Land use emissions'!W26</f>
+        <v>859890231205882.87</v>
+      </c>
+      <c r="X2" s="3">
+        <f>'EPE-Land use emissions'!X26</f>
+        <v>862606400200098.5</v>
+      </c>
+      <c r="Y2" s="3">
+        <f>'EPE-Land use emissions'!Y26</f>
+        <v>864557161891345.5</v>
+      </c>
+      <c r="Z2" s="3">
+        <f>'EPE-Land use emissions'!Z26</f>
+        <v>865972138470514.37</v>
+      </c>
+      <c r="AA2" s="3">
+        <f>'EPE-Land use emissions'!AA26</f>
+        <v>867012065471228.37</v>
+      </c>
+      <c r="AB2" s="3">
+        <f>'EPE-Land use emissions'!AB26</f>
+        <v>868936073648412.5</v>
+      </c>
+      <c r="AC2" s="3">
+        <f>'EPE-Land use emissions'!AC26</f>
+        <v>871478938649125.62</v>
+      </c>
+      <c r="AD2" s="3">
+        <f>'EPE-Land use emissions'!AD26</f>
+        <v>874455003426309.12</v>
+      </c>
+      <c r="AE2" s="3">
+        <f>'EPE-Land use emissions'!AE26</f>
+        <v>877734308047021.87</v>
+      </c>
+      <c r="AF2" s="3">
+        <f>'EPE-Land use emissions'!AF26</f>
+        <v>881225880558204.87</v>
+      </c>
+      <c r="AG2" s="3"/>
+      <c r="AH2" s="3"/>
+      <c r="AI2" s="3"/>
+      <c r="AJ2" s="3"/>
+      <c r="AK2" s="3"/>
+      <c r="AL2" s="3"/>
+      <c r="AM2" s="3"/>
+      <c r="AN2" s="3"/>
+      <c r="AO2" s="3"/>
+      <c r="AP2" s="3"/>
+      <c r="AQ2" s="3"/>
+      <c r="AR2" s="3"/>
+      <c r="AS2" s="3"/>
+      <c r="AT2" s="3"/>
+      <c r="AU2" s="3"/>
+      <c r="AV2" s="3"/>
+      <c r="AW2" s="3"/>
+      <c r="AX2" s="3"/>
+      <c r="AY2" s="3"/>
+      <c r="AZ2" s="3"/>
+      <c r="BA2" s="3"/>
+      <c r="BB2" s="3"/>
+      <c r="BC2" s="3"/>
+      <c r="BD2" s="3"/>
+      <c r="BE2" s="3"/>
+      <c r="BF2" s="3"/>
+      <c r="BG2" s="3"/>
+      <c r="BH2" s="3"/>
+      <c r="BI2" s="3"/>
+      <c r="BJ2" s="3"/>
+    </row>
+    <row r="3" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A3" s="15"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
+      <c r="AB3" s="3"/>
+      <c r="AC3" s="3"/>
+      <c r="AD3" s="3"/>
+      <c r="AE3" s="3"/>
+      <c r="AF3" s="3"/>
+      <c r="AG3" s="3"/>
+      <c r="AH3" s="3"/>
+      <c r="AI3" s="20"/>
+      <c r="AJ3" s="20"/>
+      <c r="AK3" s="20"/>
+      <c r="AL3" s="20"/>
+      <c r="AM3" s="20"/>
+      <c r="AN3" s="20"/>
+      <c r="AO3" s="20"/>
+      <c r="AP3" s="20"/>
+      <c r="AQ3" s="20"/>
+      <c r="AR3" s="20"/>
+      <c r="AS3" s="20"/>
+      <c r="AT3" s="20"/>
+      <c r="AU3" s="20"/>
+      <c r="AV3" s="20"/>
+      <c r="AW3" s="20"/>
+      <c r="AX3" s="20"/>
+      <c r="AY3" s="20"/>
+      <c r="AZ3" s="20"/>
+      <c r="BA3" s="20"/>
+      <c r="BB3" s="20"/>
+      <c r="BC3" s="20"/>
+      <c r="BD3" s="20"/>
+      <c r="BE3" s="20"/>
+      <c r="BF3" s="20"/>
+      <c r="BG3" s="20"/>
+      <c r="BH3" s="20"/>
+      <c r="BI3" s="20"/>
+      <c r="BJ3" s="20"/>
+    </row>
+    <row r="4" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="17">
+        <v>2020</v>
+      </c>
+      <c r="C4" s="17">
+        <v>2021</v>
+      </c>
+      <c r="D4" s="17">
+        <v>2022</v>
+      </c>
+      <c r="E4" s="17">
+        <v>2023</v>
+      </c>
+      <c r="F4" s="17">
+        <v>2024</v>
+      </c>
+      <c r="G4" s="17">
+        <v>2025</v>
+      </c>
+      <c r="H4" s="17">
+        <v>2026</v>
+      </c>
+      <c r="I4" s="17">
+        <v>2027</v>
+      </c>
+      <c r="J4" s="17">
+        <v>2028</v>
+      </c>
+      <c r="K4" s="17">
+        <v>2029</v>
+      </c>
+      <c r="L4" s="17">
+        <v>2030</v>
+      </c>
+      <c r="M4" s="17">
+        <v>2031</v>
+      </c>
+      <c r="N4" s="17">
+        <v>2032</v>
+      </c>
+      <c r="O4" s="17">
+        <v>2033</v>
+      </c>
+      <c r="P4" s="17">
+        <v>2034</v>
+      </c>
+      <c r="Q4" s="17">
+        <v>2035</v>
+      </c>
+      <c r="R4" s="17">
+        <v>2036</v>
+      </c>
+      <c r="S4" s="17">
+        <v>2037</v>
+      </c>
+      <c r="T4" s="17">
+        <v>2038</v>
+      </c>
+      <c r="U4" s="17">
+        <v>2039</v>
+      </c>
+      <c r="V4" s="17">
+        <v>2040</v>
+      </c>
+      <c r="W4" s="17">
+        <v>2041</v>
+      </c>
+      <c r="X4" s="17">
+        <v>2042</v>
+      </c>
+      <c r="Y4" s="17">
+        <v>2043</v>
+      </c>
+      <c r="Z4" s="17">
+        <v>2044</v>
+      </c>
+      <c r="AA4" s="17">
+        <v>2045</v>
+      </c>
+      <c r="AB4" s="17">
+        <v>2046</v>
+      </c>
+      <c r="AC4" s="17">
+        <v>2047</v>
+      </c>
+      <c r="AD4" s="17">
+        <v>2048</v>
+      </c>
+      <c r="AE4" s="17">
+        <v>2049</v>
+      </c>
+      <c r="AF4" s="17">
+        <v>2050</v>
+      </c>
+      <c r="AW4" s="17"/>
+      <c r="AX4" s="17"/>
+      <c r="AY4" s="17"/>
+      <c r="AZ4" s="17"/>
+      <c r="BA4" s="17"/>
+      <c r="BB4" s="17"/>
+      <c r="BC4" s="17"/>
+      <c r="BD4" s="17"/>
+      <c r="BE4" s="13"/>
+      <c r="BF4" s="13"/>
+      <c r="BG4" s="13"/>
+      <c r="BH4" s="13"/>
+      <c r="BI4" s="13"/>
+      <c r="BJ4" s="13"/>
+    </row>
+    <row r="5" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="21">
-        <v>908066.3323639452</v>
-      </c>
-      <c r="C2" s="21">
-        <v>726204.32267945854</v>
-      </c>
-      <c r="D2" s="21">
-        <v>839121.57903584931</v>
-      </c>
-      <c r="E2" s="21">
-        <v>874712.06977853761</v>
-      </c>
-      <c r="F2" s="21">
-        <v>854112.47920599568</v>
-      </c>
-      <c r="G2" s="21">
-        <v>1973225.0156548279</v>
-      </c>
-      <c r="H2" s="21">
-        <v>1245646.9467903182</v>
-      </c>
-      <c r="I2" s="21">
-        <v>915577.40985514433</v>
-      </c>
-      <c r="J2" s="21">
-        <v>1179953.4851826557</v>
-      </c>
-      <c r="K2" s="21">
-        <v>1132596.2442086905</v>
-      </c>
-      <c r="L2" s="21">
-        <v>1184463.676030746</v>
-      </c>
-      <c r="M2" s="21">
-        <v>1129708.8654735673</v>
-      </c>
-      <c r="N2" s="21">
-        <v>1339596.237688777</v>
-      </c>
-      <c r="O2" s="21">
-        <v>2427047.908322861</v>
-      </c>
-      <c r="P2" s="21">
-        <v>2621326.2408343372</v>
-      </c>
-      <c r="Q2" s="21">
-        <v>1573713.7062558443</v>
-      </c>
-      <c r="R2" s="21">
-        <v>1201775.4174495945</v>
-      </c>
-      <c r="S2" s="21">
-        <v>852790.016028065</v>
-      </c>
-      <c r="T2" s="21">
-        <v>963933.61874237889</v>
-      </c>
-      <c r="U2" s="21">
-        <v>342440.02805533208</v>
-      </c>
-      <c r="V2" s="21">
-        <v>277144.03225090378</v>
-      </c>
-      <c r="W2" s="21">
-        <v>324149.96548182989</v>
-      </c>
-      <c r="X2" s="21">
-        <v>172897.47577898746</v>
-      </c>
-      <c r="Y2" s="21">
-        <v>411276.02533792483</v>
-      </c>
-      <c r="Z2" s="21">
-        <v>259775.3374340625</v>
-      </c>
-      <c r="AA2" s="21">
-        <v>373263.85252695088</v>
-      </c>
-      <c r="AB2" s="21">
-        <v>436546.3771611118</v>
-      </c>
-      <c r="AC2" s="21">
-        <v>313282.4653106117</v>
-      </c>
-      <c r="AD2" s="21">
-        <v>362155.71957815147</v>
-      </c>
-      <c r="AE2" s="21">
-        <v>567067.303185964</v>
-      </c>
-      <c r="AF2" s="21">
-        <v>665083.90096446802</v>
-      </c>
-      <c r="AG2" s="21">
-        <v>882477.98727224092</v>
-      </c>
-      <c r="AH2" s="21">
-        <v>805693.94084451802</v>
-      </c>
-      <c r="AI2" s="22">
-        <f>AVERAGE(R2:AH2)</f>
-        <v>541867.85078841727</v>
-      </c>
-      <c r="AJ2" s="22">
-        <f t="shared" ref="AJ2:BJ2" si="0">AVERAGE(S2:AI2)</f>
-        <v>503049.7586318776</v>
-      </c>
-      <c r="AK2" s="22">
-        <f t="shared" si="0"/>
-        <v>482476.80231445475</v>
-      </c>
-      <c r="AL2" s="22">
-        <f t="shared" si="0"/>
-        <v>454155.81311281217</v>
-      </c>
-      <c r="AM2" s="22">
-        <f t="shared" si="0"/>
-        <v>460727.32988089928</v>
-      </c>
-      <c r="AN2" s="22">
-        <f t="shared" si="0"/>
-        <v>471526.34738854604</v>
-      </c>
-      <c r="AO2" s="22">
-        <f t="shared" si="0"/>
-        <v>480195.54632423527</v>
-      </c>
-      <c r="AP2" s="22">
-        <f t="shared" si="0"/>
-        <v>498271.9034151322</v>
-      </c>
-      <c r="AQ2" s="22">
-        <f t="shared" si="0"/>
-        <v>503389.3080079091</v>
-      </c>
-      <c r="AR2" s="22">
-        <f t="shared" si="0"/>
-        <v>517719.54157107649</v>
-      </c>
-      <c r="AS2" s="22">
-        <f t="shared" si="0"/>
-        <v>526216.93504426035</v>
-      </c>
-      <c r="AT2" s="22">
-        <f t="shared" si="0"/>
-        <v>531491.67374326917</v>
-      </c>
-      <c r="AU2" s="22">
-        <f t="shared" si="0"/>
-        <v>544327.50953342544</v>
-      </c>
-      <c r="AV2" s="22">
-        <f t="shared" si="0"/>
-        <v>555043.49717785325</v>
-      </c>
-      <c r="AW2" s="22">
-        <f t="shared" si="0"/>
-        <v>554336.21447149385</v>
-      </c>
-      <c r="AX2" s="22">
-        <f t="shared" si="0"/>
-        <v>547821.64467778953</v>
-      </c>
-      <c r="AY2" s="22">
-        <f t="shared" si="0"/>
-        <v>528135.97746635135</v>
-      </c>
-      <c r="AZ2" s="22">
-        <f t="shared" si="0"/>
-        <v>511809.03844410618</v>
-      </c>
-      <c r="BA2" s="22">
-        <f t="shared" si="0"/>
-        <v>510040.87301208777</v>
-      </c>
-      <c r="BB2" s="22">
-        <f t="shared" si="0"/>
-        <v>510452.11503445311</v>
-      </c>
-      <c r="BC2" s="22">
-        <f t="shared" si="0"/>
-        <v>512097.72166504129</v>
-      </c>
-      <c r="BD2" s="22">
-        <f t="shared" si="0"/>
-        <v>515506.06922693714</v>
-      </c>
-      <c r="BE2" s="22">
-        <f t="shared" si="0"/>
-        <v>518728.34801199811</v>
-      </c>
-      <c r="BF2" s="22">
-        <f t="shared" si="0"/>
-        <v>521504.936283966</v>
-      </c>
-      <c r="BG2" s="22">
-        <f t="shared" si="0"/>
-        <v>523934.90039924433</v>
-      </c>
-      <c r="BH2" s="22">
-        <f t="shared" si="0"/>
-        <v>525444.48845713306</v>
-      </c>
-      <c r="BI2" s="22">
-        <f t="shared" si="0"/>
-        <v>526741.85201296979</v>
-      </c>
-      <c r="BJ2" s="22">
-        <f t="shared" si="0"/>
-        <v>527272.57615661051</v>
-      </c>
-    </row>
-    <row r="3" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+      <c r="B5" s="20">
+        <f>B2*'Share of Pollutants'!$B$17</f>
+        <v>662106412018444.87</v>
+      </c>
+      <c r="C5" s="20">
+        <f>C2*'Share of Pollutants'!$B$17</f>
+        <v>727032629459101</v>
+      </c>
+      <c r="D5" s="20">
+        <f>D2*'Share of Pollutants'!$B$17</f>
+        <v>749548910497411.37</v>
+      </c>
+      <c r="E5" s="20">
+        <f>E2*'Share of Pollutants'!$B$17</f>
+        <v>765618712380660.87</v>
+      </c>
+      <c r="F5" s="20">
+        <f>F2*'Share of Pollutants'!$B$17</f>
+        <v>777175978855367.75</v>
+      </c>
+      <c r="G5" s="20">
+        <f>G2*'Share of Pollutants'!$B$17</f>
+        <v>785574470544094.87</v>
+      </c>
+      <c r="H5" s="20">
+        <f>H2*'Share of Pollutants'!$B$17</f>
+        <v>792024155961288</v>
+      </c>
+      <c r="I5" s="20">
+        <f>I2*'Share of Pollutants'!$B$17</f>
+        <v>797109676988407.37</v>
+      </c>
+      <c r="J5" s="20">
+        <f>J2*'Share of Pollutants'!$B$17</f>
+        <v>801240282942474.62</v>
+      </c>
+      <c r="K5" s="20">
+        <f>K2*'Share of Pollutants'!$B$17</f>
+        <v>804702448345406</v>
+      </c>
+      <c r="L5" s="20">
+        <f>L2*'Share of Pollutants'!$B$17</f>
+        <v>807696705362542</v>
+      </c>
+      <c r="M5" s="20">
+        <f>M2*'Share of Pollutants'!$B$17</f>
+        <v>811120508312217.5</v>
+      </c>
+      <c r="N5" s="20">
+        <f>N2*'Share of Pollutants'!$B$17</f>
+        <v>814844993414670.5</v>
+      </c>
+      <c r="O5" s="20">
+        <f>O2*'Share of Pollutants'!$B$17</f>
+        <v>818779956024067.87</v>
+      </c>
+      <c r="P5" s="20">
+        <f>P2*'Share of Pollutants'!$B$17</f>
+        <v>822862252888326.25</v>
+      </c>
+      <c r="Q5" s="20">
+        <f>Q2*'Share of Pollutants'!$B$17</f>
+        <v>827047683730987.25</v>
+      </c>
+      <c r="R5" s="20">
+        <f>R2*'Share of Pollutants'!$B$17</f>
+        <v>831652206521948.75</v>
+      </c>
+      <c r="S5" s="20">
+        <f>S2*'Share of Pollutants'!$B$17</f>
+        <v>836550093676720.87</v>
+      </c>
+      <c r="T5" s="20">
+        <f>T2*'Share of Pollutants'!$B$17</f>
+        <v>841653335886160.12</v>
+      </c>
+      <c r="U5" s="20">
+        <f>U2*'Share of Pollutants'!$B$17</f>
+        <v>846900326633866.37</v>
+      </c>
+      <c r="V5" s="20">
+        <f>V2*'Share of Pollutants'!$B$17</f>
+        <v>852247941358359.62</v>
+      </c>
+      <c r="W5" s="20">
+        <f>W2*'Share of Pollutants'!$B$17</f>
+        <v>856040493702206.25</v>
+      </c>
+      <c r="X5" s="20">
+        <f>X2*'Share of Pollutants'!$B$17</f>
+        <v>858744502379600.25</v>
+      </c>
+      <c r="Y5" s="20">
+        <f>Y2*'Share of Pollutants'!$B$17</f>
+        <v>860686530490477.25</v>
+      </c>
+      <c r="Z5" s="20">
+        <f>Z2*'Share of Pollutants'!$B$17</f>
+        <v>862095172204792.5</v>
+      </c>
+      <c r="AA5" s="20">
+        <f>AA2*'Share of Pollutants'!$B$17</f>
+        <v>863130443441514.25</v>
+      </c>
+      <c r="AB5" s="20">
+        <f>AB2*'Share of Pollutants'!$B$17</f>
+        <v>865045837814089.12</v>
+      </c>
+      <c r="AC5" s="20">
+        <f>AC2*'Share of Pollutants'!$B$17</f>
+        <v>867577318381760.87</v>
+      </c>
+      <c r="AD5" s="20">
+        <f>AD2*'Share of Pollutants'!$B$17</f>
+        <v>870540059286000.75</v>
+      </c>
+      <c r="AE5" s="20">
+        <f>AE2*'Share of Pollutants'!$B$17</f>
+        <v>873804682425838.12</v>
+      </c>
+      <c r="AF5" s="20">
+        <f>AF2*'Share of Pollutants'!$B$17</f>
+        <v>877280623130593.62</v>
+      </c>
+      <c r="AW5" s="13"/>
+      <c r="AX5" s="13"/>
+      <c r="AY5" s="13"/>
+      <c r="AZ5" s="13"/>
+      <c r="BA5" s="13"/>
+      <c r="BB5" s="13"/>
+      <c r="BC5" s="13"/>
+      <c r="BD5" s="13"/>
+      <c r="BE5" s="13"/>
+      <c r="BF5" s="13"/>
+      <c r="BG5" s="13"/>
+      <c r="BH5" s="13"/>
+      <c r="BI5" s="13"/>
+      <c r="BJ5" s="13"/>
+    </row>
+    <row r="6" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="22">
-        <v>1000000000</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
-      <c r="R3" s="22"/>
-      <c r="S3" s="22"/>
-      <c r="T3" s="22"/>
-      <c r="U3" s="22"/>
-      <c r="V3" s="22"/>
-      <c r="W3" s="22"/>
-      <c r="X3" s="22"/>
-      <c r="Y3" s="22"/>
-      <c r="Z3" s="22"/>
-      <c r="AA3" s="22"/>
-      <c r="AB3" s="22"/>
-      <c r="AC3" s="22"/>
-      <c r="AD3" s="22"/>
-      <c r="AE3" s="22"/>
-      <c r="AF3" s="22"/>
-      <c r="AG3" s="22"/>
-      <c r="AH3" s="22"/>
-      <c r="AI3" s="22"/>
-      <c r="AJ3" s="22"/>
-      <c r="AK3" s="22"/>
-      <c r="AL3" s="22"/>
-      <c r="AM3" s="22"/>
-      <c r="AN3" s="22"/>
-      <c r="AO3" s="22"/>
-      <c r="AP3" s="22"/>
-      <c r="AQ3" s="22"/>
-      <c r="AR3" s="22"/>
-      <c r="AS3" s="22"/>
-      <c r="AT3" s="22"/>
-      <c r="AU3" s="22"/>
-      <c r="AV3" s="22"/>
-      <c r="AW3" s="22"/>
-      <c r="AX3" s="22"/>
-      <c r="AY3" s="22"/>
-      <c r="AZ3" s="22"/>
-      <c r="BA3" s="22"/>
-      <c r="BB3" s="22"/>
-      <c r="BC3" s="22"/>
-      <c r="BD3" s="22"/>
-      <c r="BE3" s="22"/>
-      <c r="BF3" s="22"/>
-      <c r="BG3" s="22"/>
-      <c r="BH3" s="22"/>
-      <c r="BI3" s="22"/>
-      <c r="BJ3" s="22"/>
-    </row>
-    <row r="4" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="A4" s="15" t="s">
+      <c r="B6" s="20">
+        <f>B2*'Share of Pollutants'!$B$18</f>
+        <v>2889173126627.4751</v>
+      </c>
+      <c r="C6" s="20">
+        <f>C2*'Share of Pollutants'!$B$18</f>
+        <v>3172485716927.3706</v>
+      </c>
+      <c r="D6" s="20">
+        <f>D2*'Share of Pollutants'!$B$18</f>
+        <v>3270737950868.3794</v>
+      </c>
+      <c r="E6" s="20">
+        <f>E2*'Share of Pollutants'!$B$18</f>
+        <v>3340860273970.1504</v>
+      </c>
+      <c r="F6" s="20">
+        <f>F2*'Share of Pollutants'!$B$18</f>
+        <v>3391291659484.4561</v>
+      </c>
+      <c r="G6" s="20">
+        <f>G2*'Share of Pollutants'!$B$18</f>
+        <v>3427939388687.5356</v>
+      </c>
+      <c r="H6" s="20">
+        <f>H2*'Share of Pollutants'!$B$18</f>
+        <v>3456083290399.2695</v>
+      </c>
+      <c r="I6" s="20">
+        <f>I2*'Share of Pollutants'!$B$18</f>
+        <v>3478274512867.0601</v>
+      </c>
+      <c r="J6" s="20">
+        <f>J2*'Share of Pollutants'!$B$18</f>
+        <v>3496298859864.0898</v>
+      </c>
+      <c r="K6" s="20">
+        <f>K2*'Share of Pollutants'!$B$18</f>
+        <v>3511406394031.5884</v>
+      </c>
+      <c r="L6" s="20">
+        <f>L2*'Share of Pollutants'!$B$18</f>
+        <v>3524472159218.415</v>
+      </c>
+      <c r="M6" s="20">
+        <f>M2*'Share of Pollutants'!$B$18</f>
+        <v>3539412294661.167</v>
+      </c>
+      <c r="N6" s="20">
+        <f>N2*'Share of Pollutants'!$B$18</f>
+        <v>3555664489283.0669</v>
+      </c>
+      <c r="O6" s="20">
+        <f>O2*'Share of Pollutants'!$B$18</f>
+        <v>3572835125330.3706</v>
+      </c>
+      <c r="P6" s="20">
+        <f>P2*'Share of Pollutants'!$B$18</f>
+        <v>3590648670375.4565</v>
+      </c>
+      <c r="Q6" s="20">
+        <f>Q2*'Share of Pollutants'!$B$18</f>
+        <v>3608912251718.9897</v>
+      </c>
+      <c r="R6" s="20">
+        <f>R2*'Share of Pollutants'!$B$18</f>
+        <v>3629004586224.6089</v>
+      </c>
+      <c r="S6" s="20">
+        <f>S2*'Share of Pollutants'!$B$18</f>
+        <v>3650377047943.6885</v>
+      </c>
+      <c r="T6" s="20">
+        <f>T2*'Share of Pollutants'!$B$18</f>
+        <v>3672645598712.1899</v>
+      </c>
+      <c r="U6" s="20">
+        <f>U2*'Share of Pollutants'!$B$18</f>
+        <v>3695541411815.2861</v>
+      </c>
+      <c r="V6" s="20">
+        <f>V2*'Share of Pollutants'!$B$18</f>
+        <v>3718876308552.5996</v>
+      </c>
+      <c r="W6" s="20">
+        <f>W2*'Share of Pollutants'!$B$18</f>
+        <v>3735425521963.4258</v>
+      </c>
+      <c r="X6" s="20">
+        <f>X2*'Share of Pollutants'!$B$18</f>
+        <v>3747224757045.7109</v>
+      </c>
+      <c r="Y6" s="20">
+        <f>Y2*'Share of Pollutants'!$B$18</f>
+        <v>3755699007298.0176</v>
+      </c>
+      <c r="Z6" s="20">
+        <f>Z2*'Share of Pollutants'!$B$18</f>
+        <v>3761845768169.3389</v>
+      </c>
+      <c r="AA6" s="20">
+        <f>AA2*'Share of Pollutants'!$B$18</f>
+        <v>3766363286473.9702</v>
+      </c>
+      <c r="AB6" s="20">
+        <f>AB2*'Share of Pollutants'!$B$18</f>
+        <v>3774721317521.0737</v>
+      </c>
+      <c r="AC6" s="20">
+        <f>AC2*'Share of Pollutants'!$B$18</f>
+        <v>3785767707487.9077</v>
+      </c>
+      <c r="AD6" s="20">
+        <f>AD2*'Share of Pollutants'!$B$18</f>
+        <v>3798695948698.5537</v>
+      </c>
+      <c r="AE6" s="20">
+        <f>AE2*'Share of Pollutants'!$B$18</f>
+        <v>3812941485779.8677</v>
+      </c>
+      <c r="AF6" s="20">
+        <f>AF2*'Share of Pollutants'!$B$18</f>
+        <v>3828109129970.6484</v>
+      </c>
+      <c r="AW6" s="13"/>
+      <c r="AX6" s="13"/>
+      <c r="AY6" s="13"/>
+      <c r="AZ6" s="13"/>
+      <c r="BA6" s="13"/>
+      <c r="BB6" s="13"/>
+      <c r="BC6" s="13"/>
+      <c r="BD6" s="13"/>
+      <c r="BE6" s="13"/>
+      <c r="BF6" s="13"/>
+      <c r="BG6" s="13"/>
+      <c r="BH6" s="13"/>
+      <c r="BI6" s="13"/>
+      <c r="BJ6" s="13"/>
+    </row>
+    <row r="7" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="20">
-        <f>B6*$B$3</f>
-        <v>908066332363945.25</v>
-      </c>
-      <c r="C4" s="20">
-        <f t="shared" ref="C4:BJ4" si="1">C6*$B$3</f>
-        <v>726204322679458.5</v>
-      </c>
-      <c r="D4" s="20">
-        <f t="shared" si="1"/>
-        <v>839121579035849.25</v>
-      </c>
-      <c r="E4" s="20">
-        <f t="shared" si="1"/>
-        <v>874712069778537.62</v>
-      </c>
-      <c r="F4" s="20">
-        <f t="shared" si="1"/>
-        <v>854112479205995.62</v>
-      </c>
-      <c r="G4" s="20">
-        <f t="shared" si="1"/>
-        <v>1973225015654828</v>
-      </c>
-      <c r="H4" s="20">
-        <f t="shared" si="1"/>
-        <v>1245646946790318.2</v>
-      </c>
-      <c r="I4" s="20">
-        <f t="shared" si="1"/>
-        <v>915577409855144.38</v>
-      </c>
-      <c r="J4" s="20">
-        <f t="shared" si="1"/>
-        <v>1179953485182655.8</v>
-      </c>
-      <c r="K4" s="20">
-        <f t="shared" si="1"/>
-        <v>1132596244208690.5</v>
-      </c>
-      <c r="L4" s="20">
-        <f t="shared" si="1"/>
-        <v>1184463676030746</v>
-      </c>
-      <c r="M4" s="20">
-        <f t="shared" si="1"/>
-        <v>1129708865473567.2</v>
-      </c>
-      <c r="N4" s="20">
-        <f t="shared" si="1"/>
-        <v>1339596237688777</v>
-      </c>
-      <c r="O4" s="20">
-        <f t="shared" si="1"/>
-        <v>2427047908322861</v>
-      </c>
-      <c r="P4" s="20">
-        <f t="shared" si="1"/>
-        <v>2621326240834337</v>
-      </c>
-      <c r="Q4" s="20">
-        <f t="shared" si="1"/>
-        <v>1573713706255844.2</v>
-      </c>
-      <c r="R4" s="20">
-        <f t="shared" si="1"/>
-        <v>1201775417449594.5</v>
-      </c>
-      <c r="S4" s="20">
-        <f t="shared" si="1"/>
-        <v>852790016028065</v>
-      </c>
-      <c r="T4" s="20">
-        <f t="shared" si="1"/>
-        <v>963933618742378.88</v>
-      </c>
-      <c r="U4" s="20">
-        <f t="shared" si="1"/>
-        <v>342440028055332.06</v>
-      </c>
-      <c r="V4" s="20">
-        <f t="shared" si="1"/>
-        <v>277144032250903.78</v>
-      </c>
-      <c r="W4" s="20">
-        <f t="shared" si="1"/>
-        <v>324149965481829.88</v>
-      </c>
-      <c r="X4" s="20">
-        <f t="shared" si="1"/>
-        <v>172897475778987.47</v>
-      </c>
-      <c r="Y4" s="20">
-        <f t="shared" si="1"/>
-        <v>411276025337924.81</v>
-      </c>
-      <c r="Z4" s="20">
-        <f t="shared" si="1"/>
-        <v>259775337434062.5</v>
-      </c>
-      <c r="AA4" s="20">
-        <f t="shared" si="1"/>
-        <v>373263852526950.88</v>
-      </c>
-      <c r="AB4" s="20">
-        <f t="shared" si="1"/>
-        <v>436546377161111.81</v>
-      </c>
-      <c r="AC4" s="20">
-        <f t="shared" si="1"/>
-        <v>313282465310611.69</v>
-      </c>
-      <c r="AD4" s="20">
-        <f t="shared" si="1"/>
-        <v>362155719578151.5</v>
-      </c>
-      <c r="AE4" s="20">
-        <f t="shared" si="1"/>
-        <v>567067303185964</v>
-      </c>
-      <c r="AF4" s="20">
-        <f t="shared" si="1"/>
-        <v>665083900964468</v>
-      </c>
-      <c r="AG4" s="20">
-        <f t="shared" si="1"/>
-        <v>882477987272240.88</v>
-      </c>
-      <c r="AH4" s="20">
-        <f t="shared" si="1"/>
-        <v>805693940844518</v>
-      </c>
-      <c r="AI4" s="20">
-        <f t="shared" si="1"/>
-        <v>737554850928654.75</v>
-      </c>
-      <c r="AJ4" s="20">
-        <f t="shared" si="1"/>
-        <v>675178415215819.88</v>
-      </c>
-      <c r="AK4" s="20">
-        <f t="shared" si="1"/>
-        <v>618077274929946.75</v>
-      </c>
-      <c r="AL4" s="20">
-        <f t="shared" si="1"/>
-        <v>565805288166264.88</v>
-      </c>
-      <c r="AM4" s="20">
-        <f t="shared" si="1"/>
-        <v>517954044101029.88</v>
-      </c>
-      <c r="AN4" s="20">
-        <f t="shared" si="1"/>
-        <v>474149672001257.69</v>
-      </c>
-      <c r="AO4" s="20">
-        <f t="shared" si="1"/>
-        <v>434049920102657.31</v>
-      </c>
-      <c r="AP4" s="20">
-        <f t="shared" si="1"/>
-        <v>397341481532488.56</v>
-      </c>
-      <c r="AQ4" s="20">
-        <f t="shared" si="1"/>
-        <v>363737546384279.06</v>
-      </c>
-      <c r="AR4" s="20">
-        <f t="shared" si="1"/>
-        <v>332975560818302.44</v>
-      </c>
-      <c r="AS4" s="20">
-        <f t="shared" si="1"/>
-        <v>304815175679249.12</v>
-      </c>
-      <c r="AT4" s="20">
-        <f t="shared" si="1"/>
-        <v>279036368603255.31</v>
-      </c>
-      <c r="AU4" s="20">
-        <f t="shared" si="1"/>
-        <v>255437724941961.66</v>
-      </c>
-      <c r="AV4" s="20">
-        <f t="shared" si="1"/>
-        <v>233834864072138.25</v>
-      </c>
-      <c r="AW4" s="20">
-        <f t="shared" si="1"/>
-        <v>214058998795338.44</v>
-      </c>
-      <c r="AX4" s="20">
-        <f t="shared" si="1"/>
-        <v>195955616571901.84</v>
-      </c>
-      <c r="AY4" s="20">
-        <f t="shared" si="1"/>
-        <v>179383272285539.69</v>
-      </c>
-      <c r="AZ4" s="20">
-        <f t="shared" si="1"/>
-        <v>164212483106147.12</v>
-      </c>
-      <c r="BA4" s="20">
-        <f t="shared" si="1"/>
-        <v>150324716816197.78</v>
-      </c>
-      <c r="BB4" s="20">
-        <f t="shared" si="1"/>
-        <v>137611465696325.88</v>
-      </c>
-      <c r="BC4" s="20">
-        <f t="shared" si="1"/>
-        <v>125973398734189.95</v>
-      </c>
-      <c r="BD4" s="20">
-        <f t="shared" si="1"/>
-        <v>115319585532667.64</v>
-      </c>
-      <c r="BE4" s="20">
-        <f t="shared" si="1"/>
-        <v>105566785853630.58</v>
-      </c>
-      <c r="BF4" s="20">
-        <f t="shared" si="1"/>
-        <v>96638799246372.031</v>
-      </c>
-      <c r="BG4" s="20">
-        <f t="shared" si="1"/>
-        <v>88465869679212.312</v>
-      </c>
-      <c r="BH4" s="20">
-        <f t="shared" si="1"/>
-        <v>80984140522557.078</v>
-      </c>
-      <c r="BI4" s="20">
-        <f t="shared" si="1"/>
-        <v>74135155625089.281</v>
-      </c>
-      <c r="BJ4" s="20">
-        <f t="shared" si="1"/>
-        <v>67865402584909.328</v>
-      </c>
-    </row>
-    <row r="5" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B5" s="3">
-        <f>((AH2/B2)*EXP(1/32)-1)</f>
-        <v>-8.4571927951252457E-2</v>
-      </c>
-      <c r="R5" s="22"/>
-      <c r="S5" s="22"/>
-      <c r="T5" s="22"/>
-      <c r="U5" s="22"/>
-      <c r="V5" s="22"/>
-      <c r="W5" s="22"/>
-      <c r="X5" s="22"/>
-      <c r="Y5" s="22"/>
-      <c r="Z5" s="22"/>
-      <c r="AA5" s="22"/>
-      <c r="AB5" s="22"/>
-      <c r="AC5" s="22"/>
-      <c r="AD5" s="22"/>
-      <c r="AE5" s="22"/>
-      <c r="AF5" s="22"/>
-      <c r="AG5" s="22"/>
-      <c r="AH5" s="22"/>
-      <c r="AI5" s="22"/>
-      <c r="AJ5" s="22"/>
-      <c r="AK5" s="22"/>
-      <c r="AL5" s="22"/>
-      <c r="AM5" s="22"/>
-      <c r="AN5" s="22"/>
-      <c r="AO5" s="22"/>
-      <c r="AP5" s="22"/>
-      <c r="AQ5" s="22"/>
-      <c r="AR5" s="22"/>
-      <c r="AS5" s="22"/>
-      <c r="AT5" s="22"/>
-      <c r="AU5" s="22"/>
-      <c r="AV5" s="22"/>
-      <c r="AW5" s="22"/>
-      <c r="AX5" s="22"/>
-      <c r="AY5" s="22"/>
-      <c r="AZ5" s="22"/>
-      <c r="BA5" s="22"/>
-      <c r="BB5" s="22"/>
-      <c r="BC5" s="22"/>
-      <c r="BD5" s="22"/>
-      <c r="BE5" s="22"/>
-      <c r="BF5" s="22"/>
-      <c r="BG5" s="22"/>
-      <c r="BH5" s="22"/>
-      <c r="BI5" s="22"/>
-      <c r="BJ5" s="22"/>
-    </row>
-    <row r="6" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="A6" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" s="3">
-        <f>B2</f>
-        <v>908066.3323639452</v>
-      </c>
-      <c r="C6" s="3">
-        <f t="shared" ref="C6:AH6" si="2">C2</f>
-        <v>726204.32267945854</v>
-      </c>
-      <c r="D6" s="3">
-        <f t="shared" si="2"/>
-        <v>839121.57903584931</v>
-      </c>
-      <c r="E6" s="3">
-        <f t="shared" si="2"/>
-        <v>874712.06977853761</v>
-      </c>
-      <c r="F6" s="3">
-        <f t="shared" si="2"/>
-        <v>854112.47920599568</v>
-      </c>
-      <c r="G6" s="3">
-        <f t="shared" si="2"/>
-        <v>1973225.0156548279</v>
-      </c>
-      <c r="H6" s="3">
-        <f t="shared" si="2"/>
-        <v>1245646.9467903182</v>
-      </c>
-      <c r="I6" s="3">
-        <f t="shared" si="2"/>
-        <v>915577.40985514433</v>
-      </c>
-      <c r="J6" s="3">
-        <f t="shared" si="2"/>
-        <v>1179953.4851826557</v>
-      </c>
-      <c r="K6" s="3">
-        <f t="shared" si="2"/>
-        <v>1132596.2442086905</v>
-      </c>
-      <c r="L6" s="3">
-        <f t="shared" si="2"/>
-        <v>1184463.676030746</v>
-      </c>
-      <c r="M6" s="3">
-        <f t="shared" si="2"/>
-        <v>1129708.8654735673</v>
-      </c>
-      <c r="N6" s="3">
-        <f t="shared" si="2"/>
-        <v>1339596.237688777</v>
-      </c>
-      <c r="O6" s="3">
-        <f t="shared" si="2"/>
-        <v>2427047.908322861</v>
-      </c>
-      <c r="P6" s="3">
-        <f t="shared" si="2"/>
-        <v>2621326.2408343372</v>
-      </c>
-      <c r="Q6" s="3">
-        <f t="shared" si="2"/>
-        <v>1573713.7062558443</v>
-      </c>
-      <c r="R6" s="3">
-        <f t="shared" si="2"/>
-        <v>1201775.4174495945</v>
-      </c>
-      <c r="S6" s="3">
-        <f t="shared" si="2"/>
-        <v>852790.016028065</v>
-      </c>
-      <c r="T6" s="3">
-        <f t="shared" si="2"/>
-        <v>963933.61874237889</v>
-      </c>
-      <c r="U6" s="3">
-        <f t="shared" si="2"/>
-        <v>342440.02805533208</v>
-      </c>
-      <c r="V6" s="3">
-        <f t="shared" si="2"/>
-        <v>277144.03225090378</v>
-      </c>
-      <c r="W6" s="3">
-        <f t="shared" si="2"/>
-        <v>324149.96548182989</v>
-      </c>
-      <c r="X6" s="3">
-        <f t="shared" si="2"/>
-        <v>172897.47577898746</v>
-      </c>
-      <c r="Y6" s="3">
-        <f t="shared" si="2"/>
-        <v>411276.02533792483</v>
-      </c>
-      <c r="Z6" s="3">
-        <f t="shared" si="2"/>
-        <v>259775.3374340625</v>
-      </c>
-      <c r="AA6" s="3">
-        <f t="shared" si="2"/>
-        <v>373263.85252695088</v>
-      </c>
-      <c r="AB6" s="3">
-        <f t="shared" si="2"/>
-        <v>436546.3771611118</v>
-      </c>
-      <c r="AC6" s="3">
-        <f t="shared" si="2"/>
-        <v>313282.4653106117</v>
-      </c>
-      <c r="AD6" s="3">
-        <f t="shared" si="2"/>
-        <v>362155.71957815147</v>
-      </c>
-      <c r="AE6" s="3">
-        <f t="shared" si="2"/>
-        <v>567067.303185964</v>
-      </c>
-      <c r="AF6" s="3">
-        <f t="shared" si="2"/>
-        <v>665083.90096446802</v>
-      </c>
-      <c r="AG6" s="3">
-        <f t="shared" si="2"/>
-        <v>882477.98727224092</v>
-      </c>
-      <c r="AH6" s="3">
-        <f t="shared" si="2"/>
-        <v>805693.94084451802</v>
-      </c>
-      <c r="AI6" s="22">
-        <f>AH6+AH6*$B$5</f>
-        <v>737554.85092865478</v>
-      </c>
-      <c r="AJ6" s="22">
-        <f>AI6+AI6*$B$5</f>
-        <v>675178.41521581984</v>
-      </c>
-      <c r="AK6" s="22">
-        <f t="shared" ref="AK6:BJ6" si="3">AJ6+AJ6*$B$5</f>
-        <v>618077.27492994675</v>
-      </c>
-      <c r="AL6" s="22">
-        <f t="shared" si="3"/>
-        <v>565805.28816626489</v>
-      </c>
-      <c r="AM6" s="22">
-        <f t="shared" si="3"/>
-        <v>517954.04410102987</v>
-      </c>
-      <c r="AN6" s="22">
-        <f t="shared" si="3"/>
-        <v>474149.67200125771</v>
-      </c>
-      <c r="AO6" s="22">
-        <f t="shared" si="3"/>
-        <v>434049.92010265734</v>
-      </c>
-      <c r="AP6" s="22">
-        <f t="shared" si="3"/>
-        <v>397341.48153248854</v>
-      </c>
-      <c r="AQ6" s="22">
-        <f t="shared" si="3"/>
-        <v>363737.54638427903</v>
-      </c>
-      <c r="AR6" s="22">
-        <f t="shared" si="3"/>
-        <v>332975.56081830245</v>
-      </c>
-      <c r="AS6" s="22">
-        <f t="shared" si="3"/>
-        <v>304815.17567924911</v>
-      </c>
-      <c r="AT6" s="22">
-        <f t="shared" si="3"/>
-        <v>279036.36860325531</v>
-      </c>
-      <c r="AU6" s="22">
-        <f t="shared" si="3"/>
-        <v>255437.72494196167</v>
-      </c>
-      <c r="AV6" s="22">
-        <f t="shared" si="3"/>
-        <v>233834.86407213824</v>
-      </c>
-      <c r="AW6" s="22">
-        <f t="shared" si="3"/>
-        <v>214058.99879533844</v>
-      </c>
-      <c r="AX6" s="22">
-        <f t="shared" si="3"/>
-        <v>195955.61657190183</v>
-      </c>
-      <c r="AY6" s="22">
-        <f t="shared" si="3"/>
-        <v>179383.27228553969</v>
-      </c>
-      <c r="AZ6" s="22">
-        <f t="shared" si="3"/>
-        <v>164212.48310614712</v>
-      </c>
-      <c r="BA6" s="22">
-        <f t="shared" si="3"/>
-        <v>150324.71681619779</v>
-      </c>
-      <c r="BB6" s="22">
-        <f t="shared" si="3"/>
-        <v>137611.46569632587</v>
-      </c>
-      <c r="BC6" s="22">
-        <f t="shared" si="3"/>
-        <v>125973.39873418995</v>
-      </c>
-      <c r="BD6" s="22">
-        <f t="shared" si="3"/>
-        <v>115319.58553266764</v>
-      </c>
-      <c r="BE6" s="22">
-        <f t="shared" si="3"/>
-        <v>105566.78585363057</v>
-      </c>
-      <c r="BF6" s="22">
-        <f t="shared" si="3"/>
-        <v>96638.799246372029</v>
-      </c>
-      <c r="BG6" s="22">
-        <f t="shared" si="3"/>
-        <v>88465.869679212308</v>
-      </c>
-      <c r="BH6" s="22">
-        <f t="shared" si="3"/>
-        <v>80984.140522557078</v>
-      </c>
-      <c r="BI6" s="22">
-        <f t="shared" si="3"/>
-        <v>74135.155625089275</v>
-      </c>
-      <c r="BJ6" s="22">
-        <f t="shared" si="3"/>
-        <v>67865.40258490933</v>
-      </c>
-    </row>
-    <row r="7" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="A7" s="15" t="s">
-        <v>69</v>
-      </c>
       <c r="B7" s="3">
-        <f>'MA-Smoothing'!B3</f>
-        <v>837000000000000</v>
+        <f>B2*'Share of Pollutants'!$B$19</f>
+        <v>88414854927.522171</v>
       </c>
       <c r="C7" s="3">
-        <f>'MA-Smoothing'!C3</f>
-        <v>840000000000000</v>
+        <f>C2*'Share of Pollutants'!$B$19</f>
+        <v>97084823971.483719</v>
       </c>
       <c r="D7" s="3">
-        <f>'MA-Smoothing'!D3</f>
-        <v>1050000000000000</v>
+        <f>D2*'Share of Pollutants'!$B$19</f>
+        <v>100091551720.03491</v>
       </c>
       <c r="E7" s="3">
-        <f>'MA-Smoothing'!E3</f>
-        <v>1160000000000000</v>
+        <f>E2*'Share of Pollutants'!$B$19</f>
+        <v>102237444247.92958</v>
       </c>
       <c r="F7" s="3">
-        <f>'MA-Smoothing'!F3</f>
-        <v>1170000000000000</v>
+        <f>F2*'Share of Pollutants'!$B$19</f>
+        <v>103780752121.36467</v>
       </c>
       <c r="G7" s="3">
-        <f>'MA-Smoothing'!G3</f>
-        <v>1230000000000000</v>
+        <f>G2*'Share of Pollutants'!$B$19</f>
+        <v>104902250736.67807</v>
       </c>
       <c r="H7" s="3">
-        <f>'MA-Smoothing'!H3</f>
-        <v>1290000000000000</v>
+        <f>H2*'Share of Pollutants'!$B$19</f>
+        <v>105763514107.84959</v>
       </c>
       <c r="I7" s="3">
-        <f>'MA-Smoothing'!I3</f>
-        <v>1130000000000000</v>
+        <f>I2*'Share of Pollutants'!$B$19</f>
+        <v>106442612808.1218</v>
       </c>
       <c r="J7" s="3">
-        <f>'MA-Smoothing'!J3</f>
-        <v>1110000000000000</v>
+        <f>J2*'Share of Pollutants'!$B$19</f>
+        <v>106994196238.76443</v>
       </c>
       <c r="K7" s="3">
-        <f>'MA-Smoothing'!K3</f>
-        <v>1190000000000000</v>
+        <f>K2*'Share of Pollutants'!$B$19</f>
+        <v>107456518980.66644</v>
       </c>
       <c r="L7" s="3">
-        <f>'MA-Smoothing'!L3</f>
-        <v>1440000000000000</v>
+        <f>L2*'Share of Pollutants'!$B$19</f>
+        <v>107856359240.44997</v>
       </c>
       <c r="M7" s="3">
-        <f>'MA-Smoothing'!M3</f>
-        <v>1740000000000000</v>
+        <f>M2*'Share of Pollutants'!$B$19</f>
+        <v>108313559224.62343</v>
       </c>
       <c r="N7" s="3">
-        <f>'MA-Smoothing'!N3</f>
-        <v>1820000000000000</v>
+        <f>N2*'Share of Pollutants'!$B$19</f>
+        <v>108810911015.86983</v>
       </c>
       <c r="O7" s="3">
-        <f>'MA-Smoothing'!O3</f>
-        <v>1830000000000000</v>
+        <f>O2*'Share of Pollutants'!$B$19</f>
+        <v>109336369072.06729</v>
       </c>
       <c r="P7" s="3">
-        <f>'MA-Smoothing'!P3</f>
-        <v>1740000000000000</v>
+        <f>P2*'Share of Pollutants'!$B$19</f>
+        <v>109881501513.7305</v>
       </c>
       <c r="Q7" s="3">
-        <f>'MA-Smoothing'!Q3</f>
-        <v>1440000000000000</v>
+        <f>Q2*'Share of Pollutants'!$B$19</f>
+        <v>110440406025.21971</v>
       </c>
       <c r="R7" s="3">
-        <f>'MA-Smoothing'!R3</f>
-        <v>987000000000000</v>
+        <f>R2*'Share of Pollutants'!$B$19</f>
+        <v>111055274280.81062</v>
       </c>
       <c r="S7" s="3">
-        <f>'MA-Smoothing'!S3</f>
-        <v>728000000000000</v>
+        <f>S2*'Share of Pollutants'!$B$19</f>
+        <v>111709317157.27274</v>
       </c>
       <c r="T7" s="3">
-        <f>'MA-Smoothing'!T3</f>
-        <v>552000000000000</v>
+        <f>T2*'Share of Pollutants'!$B$19</f>
+        <v>112390782268.34465</v>
       </c>
       <c r="U7" s="3">
-        <f>'MA-Smoothing'!U3</f>
-        <v>416000000000000</v>
+        <f>U2*'Share of Pollutants'!$B$19</f>
+        <v>113091442943.64343</v>
       </c>
       <c r="V7" s="3">
-        <f>'MA-Smoothing'!V3</f>
-        <v>306000000000000</v>
+        <f>V2*'Share of Pollutants'!$B$19</f>
+        <v>113805540513.90105</v>
       </c>
       <c r="W7" s="3">
-        <f>'MA-Smoothing'!W3</f>
-        <v>289000000000000</v>
+        <f>W2*'Share of Pollutants'!$B$19</f>
+        <v>114311981713.0793</v>
       </c>
       <c r="X7" s="3">
-        <f>'MA-Smoothing'!X3</f>
-        <v>308000000000000</v>
+        <f>X2*'Share of Pollutants'!$B$19</f>
+        <v>114673063452.502</v>
       </c>
       <c r="Y7" s="3">
-        <f>'MA-Smoothing'!Y3</f>
-        <v>331000000000000</v>
+        <f>Y2*'Share of Pollutants'!$B$19</f>
+        <v>114932393570.09583</v>
       </c>
       <c r="Z7" s="3">
-        <f>'MA-Smoothing'!Z3</f>
-        <v>359000000000000</v>
+        <f>Z2*'Share of Pollutants'!$B$19</f>
+        <v>115120497552.40942</v>
       </c>
       <c r="AA7" s="3">
-        <f>'MA-Smoothing'!AA3</f>
-        <v>349000000000000</v>
+        <f>AA2*'Share of Pollutants'!$B$19</f>
+        <v>115258743240.02684</v>
       </c>
       <c r="AB7" s="3">
-        <f>'MA-Smoothing'!AB3</f>
-        <v>410000000000000</v>
+        <f>AB2*'Share of Pollutants'!$B$19</f>
+        <v>115514516802.26125</v>
       </c>
       <c r="AC7" s="3">
-        <f>'MA-Smoothing'!AC3</f>
-        <v>469000000000000</v>
+        <f>AC2*'Share of Pollutants'!$B$19</f>
+        <v>115852559876.72751</v>
       </c>
       <c r="AD7" s="3">
-        <f>'MA-Smoothing'!AD3</f>
-        <v>558000000000000</v>
+        <f>AD2*'Share of Pollutants'!$B$19</f>
+        <v>116248191609.7561</v>
       </c>
       <c r="AE7" s="3">
-        <f>'MA-Smoothing'!AE3</f>
-        <v>556000000000000</v>
+        <f>AE2*'Share of Pollutants'!$B$19</f>
+        <v>116684135403.77832</v>
       </c>
       <c r="AF7" s="3">
-        <f>'MA-Smoothing'!AF3</f>
-        <v>632000000000000</v>
-      </c>
-      <c r="AG7" s="3">
-        <f>'MA-Smoothing'!AG3</f>
-        <v>853000000000000</v>
-      </c>
-      <c r="AH7" s="3">
-        <f>'MA-Smoothing'!AH3</f>
-        <v>844000000000000</v>
-      </c>
-      <c r="AI7" s="3">
-        <f>'MA-Smoothing'!AI3</f>
-        <v>780000000000000</v>
-      </c>
-      <c r="AJ7" s="3">
-        <f>'MA-Smoothing'!AJ3</f>
-        <v>623000000000000</v>
-      </c>
-      <c r="AK7" s="3">
-        <f>'MA-Smoothing'!AK3</f>
-        <v>570000000000000</v>
-      </c>
-      <c r="AL7" s="3">
-        <f>'MA-Smoothing'!AL3</f>
-        <v>522000000000000</v>
-      </c>
-      <c r="AM7" s="3">
-        <f>'MA-Smoothing'!AM3</f>
-        <v>478000000000000</v>
-      </c>
-      <c r="AN7" s="3">
-        <f>'MA-Smoothing'!AN3</f>
-        <v>437000000000000</v>
-      </c>
-      <c r="AO7" s="3">
-        <f>'MA-Smoothing'!AO3</f>
-        <v>400000000000000</v>
-      </c>
-      <c r="AP7" s="3">
-        <f>'MA-Smoothing'!AP3</f>
-        <v>367000000000000</v>
-      </c>
-      <c r="AQ7" s="3">
-        <f>'MA-Smoothing'!AQ3</f>
-        <v>336000000000000</v>
-      </c>
-      <c r="AR7" s="3">
-        <f>'MA-Smoothing'!AR3</f>
-        <v>307000000000000</v>
-      </c>
-      <c r="AS7" s="3">
-        <f>'MA-Smoothing'!AS3</f>
-        <v>281000000000000</v>
-      </c>
-      <c r="AT7" s="3">
-        <f>'MA-Smoothing'!AT3</f>
-        <v>257000000000000</v>
-      </c>
-      <c r="AU7" s="3">
-        <f>'MA-Smoothing'!AU3</f>
-        <v>236000000000000</v>
-      </c>
-      <c r="AV7" s="3">
-        <f>'MA-Smoothing'!AV3</f>
-        <v>216000000000000</v>
-      </c>
-      <c r="AW7" s="3">
-        <f>'MA-Smoothing'!AW3</f>
-        <v>197000000000000</v>
-      </c>
-      <c r="AX7" s="3">
-        <f>'MA-Smoothing'!AX3</f>
-        <v>181000000000000</v>
-      </c>
-      <c r="AY7" s="3">
-        <f>'MA-Smoothing'!AY3</f>
-        <v>165000000000000</v>
-      </c>
-      <c r="AZ7" s="3">
-        <f>'MA-Smoothing'!AZ3</f>
-        <v>152000000000000</v>
-      </c>
-      <c r="BA7" s="3">
-        <f>'MA-Smoothing'!BA3</f>
-        <v>139000000000000</v>
-      </c>
-      <c r="BB7" s="3">
-        <f>'MA-Smoothing'!BB3</f>
-        <v>127000000000000</v>
-      </c>
-      <c r="BC7" s="3">
-        <f>'MA-Smoothing'!BC3</f>
-        <v>116000000000000</v>
-      </c>
-      <c r="BD7" s="3">
-        <f>'MA-Smoothing'!BD3</f>
-        <v>106000000000000</v>
-      </c>
-      <c r="BE7" s="3">
-        <f>'MA-Smoothing'!BE3</f>
-        <v>97400000000000</v>
-      </c>
-      <c r="BF7" s="3">
-        <f>'MA-Smoothing'!BF3</f>
-        <v>89200000000000</v>
-      </c>
-      <c r="BG7" s="3">
-        <f>'MA-Smoothing'!BG3</f>
-        <v>81600000000000</v>
-      </c>
-      <c r="BH7" s="3">
-        <f>'MA-Smoothing'!BH3</f>
-        <v>77900000000000</v>
-      </c>
-      <c r="BI7" s="3">
-        <f>'MA-Smoothing'!BI3</f>
-        <v>74300000000000</v>
-      </c>
-      <c r="BJ7" s="3">
-        <f>'MA-Smoothing'!BJ3</f>
-        <v>71000000000000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="A8" s="15"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
-      <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
-      <c r="Y8" s="3"/>
-      <c r="Z8" s="3"/>
-      <c r="AA8" s="3"/>
-      <c r="AB8" s="3"/>
-      <c r="AC8" s="3"/>
-      <c r="AD8" s="3"/>
-      <c r="AE8" s="3"/>
-      <c r="AF8" s="3"/>
-      <c r="AG8" s="3"/>
-      <c r="AH8" s="3"/>
-      <c r="AI8" s="22"/>
-      <c r="AJ8" s="22"/>
-      <c r="AK8" s="22"/>
-      <c r="AL8" s="22"/>
-      <c r="AM8" s="22"/>
-      <c r="AN8" s="22"/>
-      <c r="AO8" s="22"/>
-      <c r="AP8" s="22"/>
-      <c r="AQ8" s="22"/>
-      <c r="AR8" s="22"/>
-      <c r="AS8" s="22"/>
-      <c r="AT8" s="22"/>
-      <c r="AU8" s="22"/>
-      <c r="AV8" s="22"/>
-      <c r="AW8" s="22"/>
-      <c r="AX8" s="22"/>
-      <c r="AY8" s="22"/>
-      <c r="AZ8" s="22"/>
-      <c r="BA8" s="22"/>
-      <c r="BB8" s="22"/>
-      <c r="BC8" s="22"/>
-      <c r="BD8" s="22"/>
-      <c r="BE8" s="22"/>
-      <c r="BF8" s="22"/>
-      <c r="BG8" s="22"/>
-      <c r="BH8" s="22"/>
-      <c r="BI8" s="22"/>
-      <c r="BJ8" s="22"/>
-    </row>
-    <row r="9" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="17">
-        <v>2020</v>
-      </c>
-      <c r="C9" s="17">
-        <v>2021</v>
-      </c>
-      <c r="D9" s="17">
-        <v>2022</v>
-      </c>
-      <c r="E9" s="17">
-        <v>2023</v>
-      </c>
-      <c r="F9" s="17">
-        <v>2024</v>
-      </c>
-      <c r="G9" s="17">
-        <v>2025</v>
-      </c>
-      <c r="H9" s="17">
-        <v>2026</v>
-      </c>
-      <c r="I9" s="17">
-        <v>2027</v>
-      </c>
-      <c r="J9" s="17">
-        <v>2028</v>
-      </c>
-      <c r="K9" s="17">
-        <v>2029</v>
-      </c>
-      <c r="L9" s="17">
-        <v>2030</v>
-      </c>
-      <c r="M9" s="17">
-        <v>2031</v>
-      </c>
-      <c r="N9" s="17">
-        <v>2032</v>
-      </c>
-      <c r="O9" s="17">
-        <v>2033</v>
-      </c>
-      <c r="P9" s="17">
-        <v>2034</v>
-      </c>
-      <c r="Q9" s="17">
-        <v>2035</v>
-      </c>
-      <c r="R9" s="17">
-        <v>2036</v>
-      </c>
-      <c r="S9" s="17">
-        <v>2037</v>
-      </c>
-      <c r="T9" s="17">
-        <v>2038</v>
-      </c>
-      <c r="U9" s="17">
-        <v>2039</v>
-      </c>
-      <c r="V9" s="17">
-        <v>2040</v>
-      </c>
-      <c r="W9" s="17">
-        <v>2041</v>
-      </c>
-      <c r="X9" s="17">
-        <v>2042</v>
-      </c>
-      <c r="Y9" s="17">
-        <v>2043</v>
-      </c>
-      <c r="Z9" s="17">
-        <v>2044</v>
-      </c>
-      <c r="AA9" s="17">
-        <v>2045</v>
-      </c>
-      <c r="AB9" s="17">
-        <v>2046</v>
-      </c>
-      <c r="AC9" s="17">
-        <v>2047</v>
-      </c>
-      <c r="AD9" s="17">
-        <v>2048</v>
-      </c>
-      <c r="AE9" s="17">
-        <v>2049</v>
-      </c>
-      <c r="AF9" s="17">
-        <v>2050</v>
-      </c>
-      <c r="AW9" s="17"/>
-      <c r="AX9" s="17"/>
-      <c r="AY9" s="17"/>
-      <c r="AZ9" s="17"/>
-      <c r="BA9" s="17"/>
-      <c r="BB9" s="17"/>
-      <c r="BC9" s="17"/>
-      <c r="BD9" s="17"/>
-      <c r="BE9" s="13"/>
-      <c r="BF9" s="13"/>
-      <c r="BG9" s="13"/>
-      <c r="BH9" s="13"/>
-      <c r="BI9" s="13"/>
-      <c r="BJ9" s="13"/>
-    </row>
-    <row r="10" spans="1:62" x14ac:dyDescent="0.2">
+        <f>AF2*'Share of Pollutants'!$B$19</f>
+        <v>117148297640.49603</v>
+      </c>
+    </row>
+    <row r="10" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="22">
-        <f>AF7*'Share of Pollutants'!$B$17</f>
-        <v>629170529430353.5</v>
-      </c>
-      <c r="C10" s="22">
-        <f>AG7*'Share of Pollutants'!$B$17</f>
-        <v>849181110133056.12</v>
-      </c>
-      <c r="D10" s="22">
-        <f>AH7*'Share of Pollutants'!$B$17</f>
-        <v>840221403226611.25</v>
-      </c>
-      <c r="E10" s="22">
-        <f>AI7*'Share of Pollutants'!$B$17</f>
-        <v>776507931891891.88</v>
-      </c>
-      <c r="F10" s="22">
-        <f>AJ7*'Share of Pollutants'!$B$17</f>
-        <v>620210822523908.5</v>
-      </c>
-      <c r="G10" s="22">
-        <f>AK7*'Share of Pollutants'!$B$17</f>
-        <v>567448104074844.12</v>
-      </c>
-      <c r="H10" s="22">
-        <f>AL7*'Share of Pollutants'!$B$17</f>
-        <v>519663000573804.56</v>
-      </c>
-      <c r="I10" s="22">
-        <f>AM7*'Share of Pollutants'!$B$17</f>
-        <v>475859989031185.06</v>
-      </c>
-      <c r="J10" s="22">
-        <f>AN7*'Share of Pollutants'!$B$17</f>
-        <v>435043546457380.5</v>
-      </c>
-      <c r="K10" s="22">
-        <f>AO7*'Share of Pollutants'!$B$17</f>
-        <v>398209195841995.88</v>
-      </c>
-      <c r="L10" s="22">
-        <f>AP7*'Share of Pollutants'!$B$17</f>
-        <v>365356937185031.19</v>
-      </c>
-      <c r="M10" s="22">
-        <f>AQ7*'Share of Pollutants'!$B$17</f>
-        <v>334495724507276.5</v>
-      </c>
-      <c r="N10" s="22">
-        <f>AR7*'Share of Pollutants'!$B$17</f>
-        <v>305625557808731.81</v>
-      </c>
-      <c r="O10" s="22">
-        <f>AS7*'Share of Pollutants'!$B$17</f>
-        <v>279741960079002.09</v>
-      </c>
-      <c r="P10" s="22">
-        <f>AT7*'Share of Pollutants'!$B$17</f>
-        <v>255849408328482.34</v>
-      </c>
-      <c r="Q10" s="22">
-        <f>AU7*'Share of Pollutants'!$B$17</f>
-        <v>234943425546777.56</v>
-      </c>
-      <c r="R10" s="22">
-        <f>AV7*'Share of Pollutants'!$B$17</f>
-        <v>215032965754677.75</v>
-      </c>
-      <c r="S10" s="22">
-        <f>AW7*'Share of Pollutants'!$B$17</f>
-        <v>196118028952182.97</v>
-      </c>
-      <c r="T10" s="22">
-        <f>AX7*'Share of Pollutants'!$B$17</f>
-        <v>180189661118503.12</v>
-      </c>
-      <c r="U10" s="22">
-        <f>AY7*'Share of Pollutants'!$B$17</f>
-        <v>164261293284823.28</v>
-      </c>
-      <c r="V10" s="22">
-        <f>AZ7*'Share of Pollutants'!$B$17</f>
-        <v>151319494419958.44</v>
-      </c>
-      <c r="W10" s="22">
-        <f>BA7*'Share of Pollutants'!$B$17</f>
-        <v>138377695555093.56</v>
-      </c>
-      <c r="X10" s="22">
-        <f>BB7*'Share of Pollutants'!$B$17</f>
-        <v>126431419679833.69</v>
-      </c>
-      <c r="Y10" s="22">
-        <f>BC7*'Share of Pollutants'!$B$17</f>
-        <v>115480666794178.8</v>
-      </c>
-      <c r="Z10" s="22">
-        <f>BD7*'Share of Pollutants'!$B$17</f>
-        <v>105525436898128.91</v>
-      </c>
-      <c r="AA10" s="22">
-        <f>BE7*'Share of Pollutants'!$B$17</f>
-        <v>96963939187525.984</v>
-      </c>
-      <c r="AB10" s="22">
-        <f>BF7*'Share of Pollutants'!$B$17</f>
-        <v>88800650672765.078</v>
-      </c>
-      <c r="AC10" s="22">
-        <f>BG7*'Share of Pollutants'!$B$17</f>
-        <v>81234675951767.156</v>
-      </c>
-      <c r="AD10" s="22">
-        <f>BH7*'Share of Pollutants'!$B$17</f>
-        <v>77551240890228.688</v>
-      </c>
-      <c r="AE10" s="22">
-        <f>BI7*'Share of Pollutants'!$B$17</f>
-        <v>73967358127650.734</v>
-      </c>
-      <c r="AF10" s="22">
-        <f>BJ7*'Share of Pollutants'!$B$17</f>
-        <v>70682132261954.266</v>
-      </c>
-      <c r="AW10" s="13"/>
-      <c r="AX10" s="13"/>
-      <c r="AY10" s="13"/>
-      <c r="AZ10" s="13"/>
-      <c r="BA10" s="13"/>
-      <c r="BB10" s="13"/>
-      <c r="BC10" s="13"/>
-      <c r="BD10" s="13"/>
-      <c r="BE10" s="13"/>
-      <c r="BF10" s="13"/>
-      <c r="BG10" s="13"/>
-      <c r="BH10" s="13"/>
-      <c r="BI10" s="13"/>
-      <c r="BJ10" s="13"/>
-    </row>
-    <row r="11" spans="1:62" x14ac:dyDescent="0.2">
+      <c r="B10" s="17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="B11" s="22">
-        <f>AF7*'Share of Pollutants'!$B$18</f>
-        <v>2745453831438.6816</v>
-      </c>
-      <c r="C11" s="22">
-        <f>AG7*'Share of Pollutants'!$B$18</f>
-        <v>3705493857938.6006</v>
-      </c>
-      <c r="D11" s="22">
-        <f>AH7*'Share of Pollutants'!$B$18</f>
-        <v>3666397205275.708</v>
-      </c>
-      <c r="E11" s="22">
-        <f>AI7*'Share of Pollutants'!$B$18</f>
-        <v>3388376564117.3604</v>
-      </c>
-      <c r="F11" s="22">
-        <f>AJ7*'Share of Pollutants'!$B$18</f>
-        <v>2706357178775.7891</v>
-      </c>
-      <c r="G11" s="22">
-        <f>AK7*'Share of Pollutants'!$B$18</f>
-        <v>2476121335316.5327</v>
-      </c>
-      <c r="H11" s="22">
-        <f>AL7*'Share of Pollutants'!$B$18</f>
-        <v>2267605854447.772</v>
-      </c>
-      <c r="I11" s="22">
-        <f>AM7*'Share of Pollutants'!$B$18</f>
-        <v>2076466663651.408</v>
-      </c>
-      <c r="J11" s="22">
-        <f>AN7*'Share of Pollutants'!$B$18</f>
-        <v>1898359690409.3416</v>
-      </c>
-      <c r="K11" s="22">
-        <f>AO7*'Share of Pollutants'!$B$18</f>
-        <v>1737629007239.6719</v>
-      </c>
-      <c r="L11" s="22">
-        <f>AP7*'Share of Pollutants'!$B$18</f>
-        <v>1594274614142.3989</v>
-      </c>
-      <c r="M11" s="22">
-        <f>AQ7*'Share of Pollutants'!$B$18</f>
-        <v>1459608366081.3245</v>
-      </c>
-      <c r="N11" s="22">
-        <f>AR7*'Share of Pollutants'!$B$18</f>
-        <v>1333630263056.4482</v>
-      </c>
-      <c r="O11" s="22">
-        <f>AS7*'Share of Pollutants'!$B$18</f>
-        <v>1220684377585.8696</v>
-      </c>
-      <c r="P11" s="22">
-        <f>AT7*'Share of Pollutants'!$B$18</f>
-        <v>1116426637151.4893</v>
-      </c>
-      <c r="Q11" s="22">
-        <f>AU7*'Share of Pollutants'!$B$18</f>
-        <v>1025201114271.4065</v>
-      </c>
-      <c r="R11" s="22">
-        <f>AV7*'Share of Pollutants'!$B$18</f>
-        <v>938319663909.42285</v>
-      </c>
-      <c r="S11" s="22">
-        <f>AW7*'Share of Pollutants'!$B$18</f>
-        <v>855782286065.53845</v>
-      </c>
-      <c r="T11" s="22">
-        <f>AX7*'Share of Pollutants'!$B$18</f>
-        <v>786277125775.95154</v>
-      </c>
-      <c r="U11" s="22">
-        <f>AY7*'Share of Pollutants'!$B$18</f>
-        <v>716771965486.36475</v>
-      </c>
-      <c r="V11" s="22">
-        <f>AZ7*'Share of Pollutants'!$B$18</f>
-        <v>660299022751.07532</v>
-      </c>
-      <c r="W11" s="22">
-        <f>BA7*'Share of Pollutants'!$B$18</f>
-        <v>603826080015.78601</v>
-      </c>
-      <c r="X11" s="22">
-        <f>BB7*'Share of Pollutants'!$B$18</f>
-        <v>551697209798.59583</v>
-      </c>
-      <c r="Y11" s="22">
-        <f>BC7*'Share of Pollutants'!$B$18</f>
-        <v>503912412099.50488</v>
-      </c>
-      <c r="Z11" s="22">
-        <f>BD7*'Share of Pollutants'!$B$18</f>
-        <v>460471686918.51306</v>
-      </c>
-      <c r="AA11" s="22">
-        <f>BE7*'Share of Pollutants'!$B$18</f>
-        <v>423112663262.86011</v>
-      </c>
-      <c r="AB11" s="22">
-        <f>BF7*'Share of Pollutants'!$B$18</f>
-        <v>387491268614.44684</v>
-      </c>
-      <c r="AC11" s="22">
-        <f>BG7*'Share of Pollutants'!$B$18</f>
-        <v>354476317476.89307</v>
-      </c>
-      <c r="AD11" s="22">
-        <f>BH7*'Share of Pollutants'!$B$18</f>
-        <v>338403249159.92609</v>
-      </c>
-      <c r="AE11" s="22">
-        <f>BI7*'Share of Pollutants'!$B$18</f>
-        <v>322764588094.76904</v>
-      </c>
-      <c r="AF11" s="22">
-        <f>BJ7*'Share of Pollutants'!$B$18</f>
-        <v>308429148785.04175</v>
-      </c>
-      <c r="AW11" s="13"/>
-      <c r="AX11" s="13"/>
-      <c r="AY11" s="13"/>
-      <c r="AZ11" s="13"/>
-      <c r="BA11" s="13"/>
-      <c r="BB11" s="13"/>
-      <c r="BC11" s="13"/>
-      <c r="BD11" s="13"/>
-      <c r="BE11" s="13"/>
-      <c r="BF11" s="13"/>
-      <c r="BG11" s="13"/>
-      <c r="BH11" s="13"/>
-      <c r="BI11" s="13"/>
-      <c r="BJ11" s="13"/>
-    </row>
-    <row r="12" spans="1:62" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+      <c r="B11" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="13">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A13" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="13">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="16" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="17">
+        <v>2020</v>
+      </c>
+      <c r="C16" s="17">
+        <v>2021</v>
+      </c>
+      <c r="D16" s="17">
+        <v>2022</v>
+      </c>
+      <c r="E16" s="17">
+        <v>2023</v>
+      </c>
+      <c r="F16" s="17">
+        <v>2024</v>
+      </c>
+      <c r="G16" s="17">
+        <v>2025</v>
+      </c>
+      <c r="H16" s="17">
+        <v>2026</v>
+      </c>
+      <c r="I16" s="17">
+        <v>2027</v>
+      </c>
+      <c r="J16" s="17">
+        <v>2028</v>
+      </c>
+      <c r="K16" s="17">
+        <v>2029</v>
+      </c>
+      <c r="L16" s="17">
+        <v>2030</v>
+      </c>
+      <c r="M16" s="17">
+        <v>2031</v>
+      </c>
+      <c r="N16" s="17">
+        <v>2032</v>
+      </c>
+      <c r="O16" s="17">
+        <v>2033</v>
+      </c>
+      <c r="P16" s="17">
+        <v>2034</v>
+      </c>
+      <c r="Q16" s="17">
+        <v>2035</v>
+      </c>
+      <c r="R16" s="17">
+        <v>2036</v>
+      </c>
+      <c r="S16" s="17">
+        <v>2037</v>
+      </c>
+      <c r="T16" s="17">
+        <v>2038</v>
+      </c>
+      <c r="U16" s="17">
+        <v>2039</v>
+      </c>
+      <c r="V16" s="17">
+        <v>2040</v>
+      </c>
+      <c r="W16" s="17">
+        <v>2041</v>
+      </c>
+      <c r="X16" s="17">
+        <v>2042</v>
+      </c>
+      <c r="Y16" s="17">
+        <v>2043</v>
+      </c>
+      <c r="Z16" s="17">
+        <v>2044</v>
+      </c>
+      <c r="AA16" s="17">
+        <v>2045</v>
+      </c>
+      <c r="AB16" s="17">
+        <v>2046</v>
+      </c>
+      <c r="AC16" s="17">
+        <v>2047</v>
+      </c>
+      <c r="AD16" s="17">
+        <v>2048</v>
+      </c>
+      <c r="AE16" s="17">
+        <v>2049</v>
+      </c>
+      <c r="AF16" s="17">
+        <v>2050</v>
+      </c>
+      <c r="AW16" s="17"/>
+      <c r="AX16" s="17"/>
+      <c r="AY16" s="17"/>
+      <c r="AZ16" s="17"/>
+      <c r="BA16" s="17"/>
+      <c r="BB16" s="17"/>
+      <c r="BC16" s="17"/>
+      <c r="BD16" s="17"/>
+      <c r="BE16" s="13"/>
+      <c r="BF16" s="13"/>
+      <c r="BG16" s="13"/>
+      <c r="BH16" s="13"/>
+      <c r="BI16" s="13"/>
+      <c r="BJ16" s="13"/>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A17" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="3">
-        <f>AF7*'Share of Pollutants'!$B$19</f>
-        <v>84016738207.796326</v>
-      </c>
-      <c r="C12" s="3">
-        <f>AG7*'Share of Pollutants'!$B$19</f>
-        <v>113396009005.14284</v>
-      </c>
-      <c r="D12" s="3">
-        <f>AH7*'Share of Pollutants'!$B$19</f>
-        <v>112199568112.94321</v>
-      </c>
-      <c r="E12" s="3">
-        <f>AI7*'Share of Pollutants'!$B$19</f>
-        <v>103691543990.6347</v>
-      </c>
-      <c r="F12" s="3">
-        <f>AJ7*'Share of Pollutants'!$B$19</f>
-        <v>82820297315.596695</v>
-      </c>
-      <c r="G12" s="3">
-        <f>AK7*'Share of Pollutants'!$B$19</f>
-        <v>75774589839.309982</v>
-      </c>
-      <c r="H12" s="3">
-        <f>AL7*'Share of Pollutants'!$B$19</f>
-        <v>69393571747.578613</v>
-      </c>
-      <c r="I12" s="3">
-        <f>AM7*'Share of Pollutants'!$B$19</f>
-        <v>63544305163.491531</v>
-      </c>
-      <c r="J12" s="3">
-        <f>AN7*'Share of Pollutants'!$B$19</f>
-        <v>58093852210.13765</v>
-      </c>
-      <c r="K12" s="3">
-        <f>AO7*'Share of Pollutants'!$B$19</f>
-        <v>53175150764.428055</v>
-      </c>
-      <c r="L12" s="3">
-        <f>AP7*'Share of Pollutants'!$B$19</f>
-        <v>48788200826.36274</v>
-      </c>
-      <c r="M12" s="3">
-        <f>AQ7*'Share of Pollutants'!$B$19</f>
-        <v>44667126642.119568</v>
-      </c>
-      <c r="N12" s="3">
-        <f>AR7*'Share of Pollutants'!$B$19</f>
-        <v>40811928211.698532</v>
-      </c>
-      <c r="O12" s="3">
-        <f>AS7*'Share of Pollutants'!$B$19</f>
-        <v>37355543412.010712</v>
-      </c>
-      <c r="P12" s="3">
-        <f>AT7*'Share of Pollutants'!$B$19</f>
-        <v>34165034366.145027</v>
-      </c>
-      <c r="Q12" s="3">
-        <f>AU7*'Share of Pollutants'!$B$19</f>
-        <v>31373338951.012554</v>
-      </c>
-      <c r="R12" s="3">
-        <f>AV7*'Share of Pollutants'!$B$19</f>
-        <v>28714581412.791149</v>
-      </c>
-      <c r="S12" s="3">
-        <f>AW7*'Share of Pollutants'!$B$19</f>
-        <v>26188761751.48082</v>
-      </c>
-      <c r="T12" s="3">
-        <f>AX7*'Share of Pollutants'!$B$19</f>
-        <v>24061755720.903694</v>
-      </c>
-      <c r="U12" s="3">
-        <f>AY7*'Share of Pollutants'!$B$19</f>
-        <v>21934749690.326572</v>
-      </c>
-      <c r="V12" s="3">
-        <f>AZ7*'Share of Pollutants'!$B$19</f>
-        <v>20206557290.482662</v>
-      </c>
-      <c r="W12" s="3">
-        <f>BA7*'Share of Pollutants'!$B$19</f>
-        <v>18478364890.638748</v>
-      </c>
-      <c r="X12" s="3">
-        <f>BB7*'Share of Pollutants'!$B$19</f>
-        <v>16883110367.705908</v>
-      </c>
-      <c r="Y12" s="3">
-        <f>BC7*'Share of Pollutants'!$B$19</f>
-        <v>15420793721.684137</v>
-      </c>
-      <c r="Z12" s="3">
-        <f>BD7*'Share of Pollutants'!$B$19</f>
-        <v>14091414952.573435</v>
-      </c>
-      <c r="AA12" s="3">
-        <f>BE7*'Share of Pollutants'!$B$19</f>
-        <v>12948149211.138231</v>
-      </c>
-      <c r="AB12" s="3">
-        <f>BF7*'Share of Pollutants'!$B$19</f>
-        <v>11858058620.467457</v>
-      </c>
-      <c r="AC12" s="3">
-        <f>BG7*'Share of Pollutants'!$B$19</f>
-        <v>10847730755.943323</v>
-      </c>
-      <c r="AD12" s="3">
-        <f>BH7*'Share of Pollutants'!$B$19</f>
-        <v>10355860611.372364</v>
-      </c>
-      <c r="AE12" s="3">
-        <f>BI7*'Share of Pollutants'!$B$19</f>
-        <v>9877284254.4925117</v>
-      </c>
-      <c r="AF12" s="3">
-        <f>BJ7*'Share of Pollutants'!$B$19</f>
-        <v>9438589260.6859798</v>
-      </c>
-    </row>
-    <row r="15" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="A15" s="15" t="s">
+      <c r="B17" s="3">
+        <f t="shared" ref="B17:AF17" si="0">B5/$B$11</f>
+        <v>662106412018444.87</v>
+      </c>
+      <c r="C17" s="3">
+        <f t="shared" si="0"/>
+        <v>727032629459101</v>
+      </c>
+      <c r="D17" s="3">
+        <f t="shared" si="0"/>
+        <v>749548910497411.37</v>
+      </c>
+      <c r="E17" s="3">
+        <f t="shared" si="0"/>
+        <v>765618712380660.87</v>
+      </c>
+      <c r="F17" s="3">
+        <f t="shared" si="0"/>
+        <v>777175978855367.75</v>
+      </c>
+      <c r="G17" s="3">
+        <f t="shared" si="0"/>
+        <v>785574470544094.87</v>
+      </c>
+      <c r="H17" s="3">
+        <f t="shared" si="0"/>
+        <v>792024155961288</v>
+      </c>
+      <c r="I17" s="3">
+        <f t="shared" si="0"/>
+        <v>797109676988407.37</v>
+      </c>
+      <c r="J17" s="3">
+        <f t="shared" si="0"/>
+        <v>801240282942474.62</v>
+      </c>
+      <c r="K17" s="3">
+        <f t="shared" si="0"/>
+        <v>804702448345406</v>
+      </c>
+      <c r="L17" s="3">
+        <f t="shared" si="0"/>
+        <v>807696705362542</v>
+      </c>
+      <c r="M17" s="3">
+        <f t="shared" si="0"/>
+        <v>811120508312217.5</v>
+      </c>
+      <c r="N17" s="3">
+        <f t="shared" si="0"/>
+        <v>814844993414670.5</v>
+      </c>
+      <c r="O17" s="3">
+        <f t="shared" si="0"/>
+        <v>818779956024067.87</v>
+      </c>
+      <c r="P17" s="3">
+        <f t="shared" si="0"/>
+        <v>822862252888326.25</v>
+      </c>
+      <c r="Q17" s="3">
+        <f t="shared" si="0"/>
+        <v>827047683730987.25</v>
+      </c>
+      <c r="R17" s="3">
+        <f t="shared" si="0"/>
+        <v>831652206521948.75</v>
+      </c>
+      <c r="S17" s="3">
+        <f t="shared" si="0"/>
+        <v>836550093676720.87</v>
+      </c>
+      <c r="T17" s="3">
+        <f t="shared" si="0"/>
+        <v>841653335886160.12</v>
+      </c>
+      <c r="U17" s="3">
+        <f t="shared" si="0"/>
+        <v>846900326633866.37</v>
+      </c>
+      <c r="V17" s="3">
+        <f t="shared" si="0"/>
+        <v>852247941358359.62</v>
+      </c>
+      <c r="W17" s="3">
+        <f t="shared" si="0"/>
+        <v>856040493702206.25</v>
+      </c>
+      <c r="X17" s="3">
+        <f t="shared" si="0"/>
+        <v>858744502379600.25</v>
+      </c>
+      <c r="Y17" s="3">
+        <f t="shared" si="0"/>
+        <v>860686530490477.25</v>
+      </c>
+      <c r="Z17" s="3">
+        <f t="shared" si="0"/>
+        <v>862095172204792.5</v>
+      </c>
+      <c r="AA17" s="3">
+        <f t="shared" si="0"/>
+        <v>863130443441514.25</v>
+      </c>
+      <c r="AB17" s="3">
+        <f t="shared" si="0"/>
+        <v>865045837814089.12</v>
+      </c>
+      <c r="AC17" s="3">
+        <f t="shared" si="0"/>
+        <v>867577318381760.87</v>
+      </c>
+      <c r="AD17" s="3">
+        <f t="shared" si="0"/>
+        <v>870540059286000.75</v>
+      </c>
+      <c r="AE17" s="3">
+        <f t="shared" si="0"/>
+        <v>873804682425838.12</v>
+      </c>
+      <c r="AF17" s="3">
+        <f t="shared" si="0"/>
+        <v>877280623130593.62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A18" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B18" s="3">
+        <f t="shared" ref="B18:AF18" si="1">B6/$B$12</f>
+        <v>103184754522.40982</v>
+      </c>
+      <c r="C18" s="3">
+        <f t="shared" si="1"/>
+        <v>113303061318.83467</v>
+      </c>
+      <c r="D18" s="3">
+        <f t="shared" si="1"/>
+        <v>116812069673.8707</v>
+      </c>
+      <c r="E18" s="3">
+        <f t="shared" si="1"/>
+        <v>119316438356.0768</v>
+      </c>
+      <c r="F18" s="3">
+        <f t="shared" si="1"/>
+        <v>121117559267.302</v>
+      </c>
+      <c r="G18" s="3">
+        <f t="shared" si="1"/>
+        <v>122426406738.84056</v>
+      </c>
+      <c r="H18" s="3">
+        <f t="shared" si="1"/>
+        <v>123431546085.6882</v>
+      </c>
+      <c r="I18" s="3">
+        <f t="shared" si="1"/>
+        <v>124224089745.25215</v>
+      </c>
+      <c r="J18" s="3">
+        <f t="shared" si="1"/>
+        <v>124867816423.7175</v>
+      </c>
+      <c r="K18" s="3">
+        <f t="shared" si="1"/>
+        <v>125407371215.41386</v>
+      </c>
+      <c r="L18" s="3">
+        <f t="shared" si="1"/>
+        <v>125874005686.37196</v>
+      </c>
+      <c r="M18" s="3">
+        <f t="shared" si="1"/>
+        <v>126407581952.18454</v>
+      </c>
+      <c r="N18" s="3">
+        <f t="shared" si="1"/>
+        <v>126988017474.39525</v>
+      </c>
+      <c r="O18" s="3">
+        <f t="shared" si="1"/>
+        <v>127601254476.08467</v>
+      </c>
+      <c r="P18" s="3">
+        <f t="shared" si="1"/>
+        <v>128237452513.40916</v>
+      </c>
+      <c r="Q18" s="3">
+        <f t="shared" si="1"/>
+        <v>128889723275.67821</v>
+      </c>
+      <c r="R18" s="3">
+        <f t="shared" si="1"/>
+        <v>129607306650.87889</v>
+      </c>
+      <c r="S18" s="3">
+        <f t="shared" si="1"/>
+        <v>130370608855.13173</v>
+      </c>
+      <c r="T18" s="3">
+        <f t="shared" si="1"/>
+        <v>131165914239.72107</v>
+      </c>
+      <c r="U18" s="3">
+        <f t="shared" si="1"/>
+        <v>131983621850.54593</v>
+      </c>
+      <c r="V18" s="3">
+        <f t="shared" si="1"/>
+        <v>132817011019.7357</v>
+      </c>
+      <c r="W18" s="3">
+        <f t="shared" si="1"/>
+        <v>133408054355.83664</v>
+      </c>
+      <c r="X18" s="3">
+        <f t="shared" si="1"/>
+        <v>133829455608.77539</v>
+      </c>
+      <c r="Y18" s="3">
+        <f t="shared" si="1"/>
+        <v>134132107403.50063</v>
+      </c>
+      <c r="Z18" s="3">
+        <f t="shared" si="1"/>
+        <v>134351634577.47639</v>
+      </c>
+      <c r="AA18" s="3">
+        <f t="shared" si="1"/>
+        <v>134512974516.92751</v>
+      </c>
+      <c r="AB18" s="3">
+        <f t="shared" si="1"/>
+        <v>134811475625.75264</v>
+      </c>
+      <c r="AC18" s="3">
+        <f t="shared" si="1"/>
+        <v>135205989553.13956</v>
+      </c>
+      <c r="AD18" s="3">
+        <f t="shared" si="1"/>
+        <v>135667712453.51978</v>
+      </c>
+      <c r="AE18" s="3">
+        <f t="shared" si="1"/>
+        <v>136176481634.99527</v>
+      </c>
+      <c r="AF18" s="3">
+        <f t="shared" si="1"/>
+        <v>136718183213.23744</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A19" s="16" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="16" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="A16" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="A17" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="13">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="A18" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="13">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="21" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B21" s="17">
-        <v>2020</v>
-      </c>
-      <c r="C21" s="17">
-        <v>2021</v>
-      </c>
-      <c r="D21" s="17">
-        <v>2022</v>
-      </c>
-      <c r="E21" s="17">
-        <v>2023</v>
-      </c>
-      <c r="F21" s="17">
-        <v>2024</v>
-      </c>
-      <c r="G21" s="17">
-        <v>2025</v>
-      </c>
-      <c r="H21" s="17">
-        <v>2026</v>
-      </c>
-      <c r="I21" s="17">
-        <v>2027</v>
-      </c>
-      <c r="J21" s="17">
-        <v>2028</v>
-      </c>
-      <c r="K21" s="17">
-        <v>2029</v>
-      </c>
-      <c r="L21" s="17">
-        <v>2030</v>
-      </c>
-      <c r="M21" s="17">
-        <v>2031</v>
-      </c>
-      <c r="N21" s="17">
-        <v>2032</v>
-      </c>
-      <c r="O21" s="17">
-        <v>2033</v>
-      </c>
-      <c r="P21" s="17">
-        <v>2034</v>
-      </c>
-      <c r="Q21" s="17">
-        <v>2035</v>
-      </c>
-      <c r="R21" s="17">
-        <v>2036</v>
-      </c>
-      <c r="S21" s="17">
-        <v>2037</v>
-      </c>
-      <c r="T21" s="17">
-        <v>2038</v>
-      </c>
-      <c r="U21" s="17">
-        <v>2039</v>
-      </c>
-      <c r="V21" s="17">
-        <v>2040</v>
-      </c>
-      <c r="W21" s="17">
-        <v>2041</v>
-      </c>
-      <c r="X21" s="17">
-        <v>2042</v>
-      </c>
-      <c r="Y21" s="17">
-        <v>2043</v>
-      </c>
-      <c r="Z21" s="17">
-        <v>2044</v>
-      </c>
-      <c r="AA21" s="17">
-        <v>2045</v>
-      </c>
-      <c r="AB21" s="17">
-        <v>2046</v>
-      </c>
-      <c r="AC21" s="17">
-        <v>2047</v>
-      </c>
-      <c r="AD21" s="17">
-        <v>2048</v>
-      </c>
-      <c r="AE21" s="17">
-        <v>2049</v>
-      </c>
-      <c r="AF21" s="17">
-        <v>2050</v>
-      </c>
-      <c r="AW21" s="17"/>
-      <c r="AX21" s="17"/>
-      <c r="AY21" s="17"/>
-      <c r="AZ21" s="17"/>
-      <c r="BA21" s="17"/>
-      <c r="BB21" s="17"/>
-      <c r="BC21" s="17"/>
-      <c r="BD21" s="17"/>
-      <c r="BE21" s="13"/>
-      <c r="BF21" s="13"/>
-      <c r="BG21" s="13"/>
-      <c r="BH21" s="13"/>
-      <c r="BI21" s="13"/>
-      <c r="BJ21" s="13"/>
-    </row>
-    <row r="22" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="A22" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="B22" s="3">
-        <f t="shared" ref="B22:AF22" si="4">B10/$B$16</f>
-        <v>629170529430353.5</v>
-      </c>
-      <c r="C22" s="3">
-        <f t="shared" si="4"/>
-        <v>849181110133056.12</v>
-      </c>
-      <c r="D22" s="3">
-        <f t="shared" si="4"/>
-        <v>840221403226611.25</v>
-      </c>
-      <c r="E22" s="3">
-        <f t="shared" si="4"/>
-        <v>776507931891891.88</v>
-      </c>
-      <c r="F22" s="3">
-        <f t="shared" si="4"/>
-        <v>620210822523908.5</v>
-      </c>
-      <c r="G22" s="3">
-        <f t="shared" si="4"/>
-        <v>567448104074844.12</v>
-      </c>
-      <c r="H22" s="3">
-        <f t="shared" si="4"/>
-        <v>519663000573804.56</v>
-      </c>
-      <c r="I22" s="3">
-        <f t="shared" si="4"/>
-        <v>475859989031185.06</v>
-      </c>
-      <c r="J22" s="3">
-        <f t="shared" si="4"/>
-        <v>435043546457380.5</v>
-      </c>
-      <c r="K22" s="3">
-        <f t="shared" si="4"/>
-        <v>398209195841995.88</v>
-      </c>
-      <c r="L22" s="3">
-        <f t="shared" si="4"/>
-        <v>365356937185031.19</v>
-      </c>
-      <c r="M22" s="3">
-        <f t="shared" si="4"/>
-        <v>334495724507276.5</v>
-      </c>
-      <c r="N22" s="3">
-        <f t="shared" si="4"/>
-        <v>305625557808731.81</v>
-      </c>
-      <c r="O22" s="3">
-        <f t="shared" si="4"/>
-        <v>279741960079002.09</v>
-      </c>
-      <c r="P22" s="3">
-        <f t="shared" si="4"/>
-        <v>255849408328482.34</v>
-      </c>
-      <c r="Q22" s="3">
-        <f t="shared" si="4"/>
-        <v>234943425546777.56</v>
-      </c>
-      <c r="R22" s="3">
-        <f t="shared" si="4"/>
-        <v>215032965754677.75</v>
-      </c>
-      <c r="S22" s="3">
-        <f t="shared" si="4"/>
-        <v>196118028952182.97</v>
-      </c>
-      <c r="T22" s="3">
-        <f t="shared" si="4"/>
-        <v>180189661118503.12</v>
-      </c>
-      <c r="U22" s="3">
-        <f t="shared" si="4"/>
-        <v>164261293284823.28</v>
-      </c>
-      <c r="V22" s="3">
-        <f t="shared" si="4"/>
-        <v>151319494419958.44</v>
-      </c>
-      <c r="W22" s="3">
-        <f t="shared" si="4"/>
-        <v>138377695555093.56</v>
-      </c>
-      <c r="X22" s="3">
-        <f t="shared" si="4"/>
-        <v>126431419679833.69</v>
-      </c>
-      <c r="Y22" s="3">
-        <f t="shared" si="4"/>
-        <v>115480666794178.8</v>
-      </c>
-      <c r="Z22" s="3">
-        <f t="shared" si="4"/>
-        <v>105525436898128.91</v>
-      </c>
-      <c r="AA22" s="3">
-        <f t="shared" si="4"/>
-        <v>96963939187525.984</v>
-      </c>
-      <c r="AB22" s="3">
-        <f t="shared" si="4"/>
-        <v>88800650672765.078</v>
-      </c>
-      <c r="AC22" s="3">
-        <f t="shared" si="4"/>
-        <v>81234675951767.156</v>
-      </c>
-      <c r="AD22" s="3">
-        <f t="shared" si="4"/>
-        <v>77551240890228.688</v>
-      </c>
-      <c r="AE22" s="3">
-        <f t="shared" si="4"/>
-        <v>73967358127650.734</v>
-      </c>
-      <c r="AF22" s="3">
-        <f t="shared" si="4"/>
-        <v>70682132261954.266</v>
-      </c>
-    </row>
-    <row r="23" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="A23" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="B23" s="3">
-        <f t="shared" ref="B23:AF23" si="5">B11/$B$17</f>
-        <v>98051922551.381485</v>
-      </c>
-      <c r="C23" s="3">
-        <f t="shared" si="5"/>
-        <v>132339066354.95003</v>
-      </c>
-      <c r="D23" s="3">
-        <f t="shared" si="5"/>
-        <v>130942757331.27528</v>
-      </c>
-      <c r="E23" s="3">
-        <f t="shared" si="5"/>
-        <v>121013448718.47716</v>
-      </c>
-      <c r="F23" s="3">
-        <f t="shared" si="5"/>
-        <v>96655613527.706757</v>
-      </c>
-      <c r="G23" s="3">
-        <f t="shared" si="5"/>
-        <v>88432904832.733307</v>
-      </c>
-      <c r="H23" s="3">
-        <f t="shared" si="5"/>
-        <v>80985923373.13472</v>
-      </c>
-      <c r="I23" s="3">
-        <f t="shared" si="5"/>
-        <v>74159523701.835999</v>
-      </c>
-      <c r="J23" s="3">
-        <f t="shared" si="5"/>
-        <v>67798560371.762199</v>
-      </c>
-      <c r="K23" s="3">
-        <f t="shared" si="5"/>
-        <v>62058178829.988281</v>
-      </c>
-      <c r="L23" s="3">
-        <f t="shared" si="5"/>
-        <v>56938379076.514244</v>
-      </c>
-      <c r="M23" s="3">
-        <f t="shared" si="5"/>
-        <v>52128870217.190163</v>
-      </c>
-      <c r="N23" s="3">
-        <f t="shared" si="5"/>
-        <v>47629652252.016006</v>
-      </c>
-      <c r="O23" s="3">
-        <f t="shared" si="5"/>
-        <v>43595870628.066772</v>
-      </c>
-      <c r="P23" s="3">
-        <f t="shared" si="5"/>
-        <v>39872379898.267471</v>
-      </c>
-      <c r="Q23" s="3">
-        <f t="shared" si="5"/>
-        <v>36614325509.693092</v>
-      </c>
-      <c r="R23" s="3">
-        <f t="shared" si="5"/>
-        <v>33511416568.193672</v>
-      </c>
-      <c r="S23" s="3">
-        <f t="shared" si="5"/>
-        <v>30563653073.76923</v>
-      </c>
-      <c r="T23" s="3">
-        <f t="shared" si="5"/>
-        <v>28081325920.569698</v>
-      </c>
-      <c r="U23" s="3">
-        <f t="shared" si="5"/>
-        <v>25598998767.370171</v>
-      </c>
-      <c r="V23" s="3">
-        <f t="shared" si="5"/>
-        <v>23582107955.395546</v>
-      </c>
-      <c r="W23" s="3">
-        <f t="shared" si="5"/>
-        <v>21565217143.420929</v>
-      </c>
-      <c r="X23" s="3">
-        <f t="shared" si="5"/>
-        <v>19703471778.521278</v>
-      </c>
-      <c r="Y23" s="3">
-        <f t="shared" si="5"/>
-        <v>17996871860.696602</v>
-      </c>
-      <c r="Z23" s="3">
-        <f t="shared" si="5"/>
-        <v>16445417389.946896</v>
-      </c>
-      <c r="AA23" s="3">
-        <f t="shared" si="5"/>
-        <v>15111166545.102146</v>
-      </c>
-      <c r="AB23" s="3">
-        <f t="shared" si="5"/>
-        <v>13838973879.087387</v>
-      </c>
-      <c r="AC23" s="3">
-        <f t="shared" si="5"/>
-        <v>12659868481.31761</v>
-      </c>
-      <c r="AD23" s="3">
-        <f t="shared" si="5"/>
-        <v>12085830327.140217</v>
-      </c>
-      <c r="AE23" s="3">
-        <f t="shared" si="5"/>
-        <v>11527306717.670322</v>
-      </c>
-      <c r="AF23" s="3">
-        <f t="shared" si="5"/>
-        <v>11015326742.32292</v>
-      </c>
-    </row>
-    <row r="24" spans="1:62" x14ac:dyDescent="0.2">
-      <c r="A24" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="B24" s="3">
-        <f t="shared" ref="B24:AF24" si="6">B12/$B$18</f>
-        <v>317044295.12375975</v>
-      </c>
-      <c r="C24" s="3">
-        <f t="shared" si="6"/>
-        <v>427909467.94393522</v>
-      </c>
-      <c r="D24" s="3">
-        <f t="shared" si="6"/>
-        <v>423394596.65261585</v>
-      </c>
-      <c r="E24" s="3">
-        <f t="shared" si="6"/>
-        <v>391288845.2476781</v>
-      </c>
-      <c r="F24" s="3">
-        <f t="shared" si="6"/>
-        <v>312529423.83244038</v>
-      </c>
-      <c r="G24" s="3">
-        <f t="shared" si="6"/>
-        <v>285941848.45022637</v>
-      </c>
-      <c r="H24" s="3">
-        <f t="shared" si="6"/>
-        <v>261862534.89652306</v>
-      </c>
-      <c r="I24" s="3">
-        <f t="shared" si="6"/>
-        <v>239789830.80562842</v>
-      </c>
-      <c r="J24" s="3">
-        <f t="shared" si="6"/>
-        <v>219222083.81184018</v>
-      </c>
-      <c r="K24" s="3">
-        <f t="shared" si="6"/>
-        <v>200660946.28086057</v>
-      </c>
-      <c r="L24" s="3">
-        <f t="shared" si="6"/>
-        <v>184106418.21268958</v>
-      </c>
-      <c r="M24" s="3">
-        <f t="shared" si="6"/>
-        <v>168555194.87592289</v>
-      </c>
-      <c r="N24" s="3">
-        <f t="shared" si="6"/>
-        <v>154007276.2705605</v>
-      </c>
-      <c r="O24" s="3">
-        <f t="shared" si="6"/>
-        <v>140964314.76230457</v>
-      </c>
-      <c r="P24" s="3">
-        <f t="shared" si="6"/>
-        <v>128924657.98545294</v>
-      </c>
-      <c r="Q24" s="3">
-        <f t="shared" si="6"/>
-        <v>118389958.30570775</v>
-      </c>
-      <c r="R24" s="3">
-        <f t="shared" si="6"/>
-        <v>108356910.99166471</v>
-      </c>
-      <c r="S24" s="3">
-        <f t="shared" si="6"/>
-        <v>98825516.043323845</v>
-      </c>
-      <c r="T24" s="3">
-        <f t="shared" si="6"/>
-        <v>90799078.192089409</v>
-      </c>
-      <c r="U24" s="3">
-        <f t="shared" si="6"/>
-        <v>82772640.340854988</v>
-      </c>
-      <c r="V24" s="3">
-        <f t="shared" si="6"/>
-        <v>76251159.586727023</v>
-      </c>
-      <c r="W24" s="3">
-        <f t="shared" si="6"/>
-        <v>69729678.832599044</v>
-      </c>
-      <c r="X24" s="3">
-        <f t="shared" si="6"/>
-        <v>63709850.444173239</v>
-      </c>
-      <c r="Y24" s="3">
-        <f t="shared" si="6"/>
-        <v>58191674.421449572</v>
-      </c>
-      <c r="Z24" s="3">
-        <f t="shared" si="6"/>
-        <v>53175150.764428057</v>
-      </c>
-      <c r="AA24" s="3">
-        <f t="shared" si="6"/>
-        <v>48860940.419389553</v>
-      </c>
-      <c r="AB24" s="3">
-        <f t="shared" si="6"/>
-        <v>44747391.020631909</v>
-      </c>
-      <c r="AC24" s="3">
-        <f t="shared" si="6"/>
-        <v>40934833.041295558</v>
-      </c>
-      <c r="AD24" s="3">
-        <f t="shared" si="6"/>
-        <v>39078719.288197599</v>
-      </c>
-      <c r="AE24" s="3">
-        <f t="shared" si="6"/>
-        <v>37272770.771669857</v>
-      </c>
-      <c r="AF24" s="3">
-        <f t="shared" si="6"/>
-        <v>35617317.964852758</v>
+      <c r="B19" s="3">
+        <f t="shared" ref="B19:AF19" si="2">B7/$B$13</f>
+        <v>333640961.9906497</v>
+      </c>
+      <c r="C19" s="3">
+        <f t="shared" si="2"/>
+        <v>366357826.30748576</v>
+      </c>
+      <c r="D19" s="3">
+        <f t="shared" si="2"/>
+        <v>377703968.75484872</v>
+      </c>
+      <c r="E19" s="3">
+        <f t="shared" si="2"/>
+        <v>385801676.40728146</v>
+      </c>
+      <c r="F19" s="3">
+        <f t="shared" si="2"/>
+        <v>391625479.70326293</v>
+      </c>
+      <c r="G19" s="3">
+        <f t="shared" si="2"/>
+        <v>395857549.94972855</v>
+      </c>
+      <c r="H19" s="3">
+        <f t="shared" si="2"/>
+        <v>399107600.40697962</v>
+      </c>
+      <c r="I19" s="3">
+        <f t="shared" si="2"/>
+        <v>401670237.01178038</v>
+      </c>
+      <c r="J19" s="3">
+        <f t="shared" si="2"/>
+        <v>403751683.91986579</v>
+      </c>
+      <c r="K19" s="3">
+        <f t="shared" si="2"/>
+        <v>405496298.04025072</v>
+      </c>
+      <c r="L19" s="3">
+        <f t="shared" si="2"/>
+        <v>407005129.20924515</v>
+      </c>
+      <c r="M19" s="3">
+        <f t="shared" si="2"/>
+        <v>408730412.16839027</v>
+      </c>
+      <c r="N19" s="3">
+        <f t="shared" si="2"/>
+        <v>410607211.38064086</v>
+      </c>
+      <c r="O19" s="3">
+        <f t="shared" si="2"/>
+        <v>412590071.97006524</v>
+      </c>
+      <c r="P19" s="3">
+        <f t="shared" si="2"/>
+        <v>414647175.52351129</v>
+      </c>
+      <c r="Q19" s="3">
+        <f t="shared" si="2"/>
+        <v>416756249.1517725</v>
+      </c>
+      <c r="R19" s="3">
+        <f t="shared" si="2"/>
+        <v>419076506.72004008</v>
+      </c>
+      <c r="S19" s="3">
+        <f t="shared" si="2"/>
+        <v>421544593.04631221</v>
+      </c>
+      <c r="T19" s="3">
+        <f t="shared" si="2"/>
+        <v>424116159.50318736</v>
+      </c>
+      <c r="U19" s="3">
+        <f t="shared" si="2"/>
+        <v>426760162.05148464</v>
+      </c>
+      <c r="V19" s="3">
+        <f t="shared" si="2"/>
+        <v>429454869.86377752</v>
+      </c>
+      <c r="W19" s="3">
+        <f t="shared" si="2"/>
+        <v>431365968.72860116</v>
+      </c>
+      <c r="X19" s="3">
+        <f t="shared" si="2"/>
+        <v>432728541.3301962</v>
+      </c>
+      <c r="Y19" s="3">
+        <f t="shared" si="2"/>
+        <v>433707145.54753143</v>
+      </c>
+      <c r="Z19" s="3">
+        <f t="shared" si="2"/>
+        <v>434416971.89588463</v>
+      </c>
+      <c r="AA19" s="3">
+        <f t="shared" si="2"/>
+        <v>434938653.73595035</v>
+      </c>
+      <c r="AB19" s="3">
+        <f t="shared" si="2"/>
+        <v>435903836.98966509</v>
+      </c>
+      <c r="AC19" s="3">
+        <f t="shared" si="2"/>
+        <v>437179471.232934</v>
+      </c>
+      <c r="AD19" s="3">
+        <f t="shared" si="2"/>
+        <v>438672421.16889095</v>
+      </c>
+      <c r="AE19" s="3">
+        <f t="shared" si="2"/>
+        <v>440317492.08972949</v>
+      </c>
+      <c r="AF19" s="3">
+        <f t="shared" si="2"/>
+        <v>442069047.69998503</v>
       </c>
     </row>
   </sheetData>
@@ -7907,14 +7119,14 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE593CF6-1A61-ED4A-A755-362718C8F2D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
   <dimension ref="A1:AF13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>1</v>
       </c>
@@ -8012,136 +7224,136 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="3">
-        <f>'Government Data'!B22</f>
-        <v>629170529430353.5</v>
+        <f>'Emissions by Pollutants'!B17</f>
+        <v>662106412018444.87</v>
       </c>
       <c r="C2" s="3">
-        <f>'Government Data'!C22</f>
-        <v>849181110133056.12</v>
+        <f>'Emissions by Pollutants'!C17</f>
+        <v>727032629459101</v>
       </c>
       <c r="D2" s="3">
-        <f>'Government Data'!D22</f>
-        <v>840221403226611.25</v>
+        <f>'Emissions by Pollutants'!D17</f>
+        <v>749548910497411.37</v>
       </c>
       <c r="E2" s="3">
-        <f>'Government Data'!E22</f>
-        <v>776507931891891.88</v>
+        <f>'Emissions by Pollutants'!E17</f>
+        <v>765618712380660.87</v>
       </c>
       <c r="F2" s="3">
-        <f>'Government Data'!F22</f>
-        <v>620210822523908.5</v>
+        <f>'Emissions by Pollutants'!F17</f>
+        <v>777175978855367.75</v>
       </c>
       <c r="G2" s="3">
-        <f>'Government Data'!G22</f>
-        <v>567448104074844.12</v>
+        <f>'Emissions by Pollutants'!G17</f>
+        <v>785574470544094.87</v>
       </c>
       <c r="H2" s="3">
-        <f>'Government Data'!H22</f>
-        <v>519663000573804.56</v>
+        <f>'Emissions by Pollutants'!H17</f>
+        <v>792024155961288</v>
       </c>
       <c r="I2" s="3">
-        <f>'Government Data'!I22</f>
-        <v>475859989031185.06</v>
+        <f>'Emissions by Pollutants'!I17</f>
+        <v>797109676988407.37</v>
       </c>
       <c r="J2" s="3">
-        <f>'Government Data'!J22</f>
-        <v>435043546457380.5</v>
+        <f>'Emissions by Pollutants'!J17</f>
+        <v>801240282942474.62</v>
       </c>
       <c r="K2" s="3">
-        <f>'Government Data'!K22</f>
-        <v>398209195841995.88</v>
+        <f>'Emissions by Pollutants'!K17</f>
+        <v>804702448345406</v>
       </c>
       <c r="L2" s="3">
-        <f>'Government Data'!L22</f>
-        <v>365356937185031.19</v>
+        <f>'Emissions by Pollutants'!L17</f>
+        <v>807696705362542</v>
       </c>
       <c r="M2" s="3">
-        <f>'Government Data'!M22</f>
-        <v>334495724507276.5</v>
+        <f>'Emissions by Pollutants'!M17</f>
+        <v>811120508312217.5</v>
       </c>
       <c r="N2" s="3">
-        <f>'Government Data'!N22</f>
-        <v>305625557808731.81</v>
+        <f>'Emissions by Pollutants'!N17</f>
+        <v>814844993414670.5</v>
       </c>
       <c r="O2" s="3">
-        <f>'Government Data'!O22</f>
-        <v>279741960079002.09</v>
+        <f>'Emissions by Pollutants'!O17</f>
+        <v>818779956024067.87</v>
       </c>
       <c r="P2" s="3">
-        <f>'Government Data'!P22</f>
-        <v>255849408328482.34</v>
+        <f>'Emissions by Pollutants'!P17</f>
+        <v>822862252888326.25</v>
       </c>
       <c r="Q2" s="3">
-        <f>'Government Data'!Q22</f>
-        <v>234943425546777.56</v>
+        <f>'Emissions by Pollutants'!Q17</f>
+        <v>827047683730987.25</v>
       </c>
       <c r="R2" s="3">
-        <f>'Government Data'!R22</f>
-        <v>215032965754677.75</v>
+        <f>'Emissions by Pollutants'!R17</f>
+        <v>831652206521948.75</v>
       </c>
       <c r="S2" s="3">
-        <f>'Government Data'!S22</f>
-        <v>196118028952182.97</v>
+        <f>'Emissions by Pollutants'!S17</f>
+        <v>836550093676720.87</v>
       </c>
       <c r="T2" s="3">
-        <f>'Government Data'!T22</f>
-        <v>180189661118503.12</v>
+        <f>'Emissions by Pollutants'!T17</f>
+        <v>841653335886160.12</v>
       </c>
       <c r="U2" s="3">
-        <f>'Government Data'!U22</f>
-        <v>164261293284823.28</v>
+        <f>'Emissions by Pollutants'!U17</f>
+        <v>846900326633866.37</v>
       </c>
       <c r="V2" s="3">
-        <f>'Government Data'!V22</f>
-        <v>151319494419958.44</v>
+        <f>'Emissions by Pollutants'!V17</f>
+        <v>852247941358359.62</v>
       </c>
       <c r="W2" s="3">
-        <f>'Government Data'!W22</f>
-        <v>138377695555093.56</v>
+        <f>'Emissions by Pollutants'!W17</f>
+        <v>856040493702206.25</v>
       </c>
       <c r="X2" s="3">
-        <f>'Government Data'!X22</f>
-        <v>126431419679833.69</v>
+        <f>'Emissions by Pollutants'!X17</f>
+        <v>858744502379600.25</v>
       </c>
       <c r="Y2" s="3">
-        <f>'Government Data'!Y22</f>
-        <v>115480666794178.8</v>
+        <f>'Emissions by Pollutants'!Y17</f>
+        <v>860686530490477.25</v>
       </c>
       <c r="Z2" s="3">
-        <f>'Government Data'!Z22</f>
-        <v>105525436898128.91</v>
+        <f>'Emissions by Pollutants'!Z17</f>
+        <v>862095172204792.5</v>
       </c>
       <c r="AA2" s="3">
-        <f>'Government Data'!AA22</f>
-        <v>96963939187525.984</v>
+        <f>'Emissions by Pollutants'!AA17</f>
+        <v>863130443441514.25</v>
       </c>
       <c r="AB2" s="3">
-        <f>'Government Data'!AB22</f>
-        <v>88800650672765.078</v>
+        <f>'Emissions by Pollutants'!AB17</f>
+        <v>865045837814089.12</v>
       </c>
       <c r="AC2" s="3">
-        <f>'Government Data'!AC22</f>
-        <v>81234675951767.156</v>
+        <f>'Emissions by Pollutants'!AC17</f>
+        <v>867577318381760.87</v>
       </c>
       <c r="AD2" s="3">
-        <f>'Government Data'!AD22</f>
-        <v>77551240890228.688</v>
+        <f>'Emissions by Pollutants'!AD17</f>
+        <v>870540059286000.75</v>
       </c>
       <c r="AE2" s="3">
-        <f>'Government Data'!AE22</f>
-        <v>73967358127650.734</v>
+        <f>'Emissions by Pollutants'!AE17</f>
+        <v>873804682425838.12</v>
       </c>
       <c r="AF2" s="3">
-        <f>'Government Data'!AF22</f>
-        <v>70682132261954.266</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+        <f>'Emissions by Pollutants'!AF17</f>
+        <v>877280623130593.62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
         <v>6</v>
       </c>
@@ -8239,7 +7451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
         <v>7</v>
       </c>
@@ -8337,7 +7549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
         <v>8</v>
       </c>
@@ -8435,7 +7647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
         <v>9</v>
       </c>
@@ -8533,7 +7745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
         <v>10</v>
       </c>
@@ -8631,7 +7843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
         <v>11</v>
       </c>
@@ -8729,7 +7941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>12</v>
       </c>
@@ -8827,7 +8039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>13</v>
       </c>
@@ -8925,265 +8137,265 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="3">
-        <f>'Government Data'!B23</f>
-        <v>98051922551.381485</v>
+        <f>'Emissions by Pollutants'!B18</f>
+        <v>103184754522.40982</v>
       </c>
       <c r="C11" s="3">
-        <f>'Government Data'!C23</f>
-        <v>132339066354.95003</v>
+        <f>'Emissions by Pollutants'!C18</f>
+        <v>113303061318.83467</v>
       </c>
       <c r="D11" s="3">
-        <f>'Government Data'!D23</f>
-        <v>130942757331.27528</v>
+        <f>'Emissions by Pollutants'!D18</f>
+        <v>116812069673.8707</v>
       </c>
       <c r="E11" s="3">
-        <f>'Government Data'!E23</f>
-        <v>121013448718.47716</v>
+        <f>'Emissions by Pollutants'!E18</f>
+        <v>119316438356.0768</v>
       </c>
       <c r="F11" s="3">
-        <f>'Government Data'!F23</f>
-        <v>96655613527.706757</v>
+        <f>'Emissions by Pollutants'!F18</f>
+        <v>121117559267.302</v>
       </c>
       <c r="G11" s="3">
-        <f>'Government Data'!G23</f>
-        <v>88432904832.733307</v>
+        <f>'Emissions by Pollutants'!G18</f>
+        <v>122426406738.84056</v>
       </c>
       <c r="H11" s="3">
-        <f>'Government Data'!H23</f>
-        <v>80985923373.13472</v>
+        <f>'Emissions by Pollutants'!H18</f>
+        <v>123431546085.6882</v>
       </c>
       <c r="I11" s="3">
-        <f>'Government Data'!I23</f>
-        <v>74159523701.835999</v>
+        <f>'Emissions by Pollutants'!I18</f>
+        <v>124224089745.25215</v>
       </c>
       <c r="J11" s="3">
-        <f>'Government Data'!J23</f>
-        <v>67798560371.762199</v>
+        <f>'Emissions by Pollutants'!J18</f>
+        <v>124867816423.7175</v>
       </c>
       <c r="K11" s="3">
-        <f>'Government Data'!K23</f>
-        <v>62058178829.988281</v>
+        <f>'Emissions by Pollutants'!K18</f>
+        <v>125407371215.41386</v>
       </c>
       <c r="L11" s="3">
-        <f>'Government Data'!L23</f>
-        <v>56938379076.514244</v>
+        <f>'Emissions by Pollutants'!L18</f>
+        <v>125874005686.37196</v>
       </c>
       <c r="M11" s="3">
-        <f>'Government Data'!M23</f>
-        <v>52128870217.190163</v>
+        <f>'Emissions by Pollutants'!M18</f>
+        <v>126407581952.18454</v>
       </c>
       <c r="N11" s="3">
-        <f>'Government Data'!N23</f>
-        <v>47629652252.016006</v>
+        <f>'Emissions by Pollutants'!N18</f>
+        <v>126988017474.39525</v>
       </c>
       <c r="O11" s="3">
-        <f>'Government Data'!O23</f>
-        <v>43595870628.066772</v>
+        <f>'Emissions by Pollutants'!O18</f>
+        <v>127601254476.08467</v>
       </c>
       <c r="P11" s="3">
-        <f>'Government Data'!P23</f>
-        <v>39872379898.267471</v>
+        <f>'Emissions by Pollutants'!P18</f>
+        <v>128237452513.40916</v>
       </c>
       <c r="Q11" s="3">
-        <f>'Government Data'!Q23</f>
-        <v>36614325509.693092</v>
+        <f>'Emissions by Pollutants'!Q18</f>
+        <v>128889723275.67821</v>
       </c>
       <c r="R11" s="3">
-        <f>'Government Data'!R23</f>
-        <v>33511416568.193672</v>
+        <f>'Emissions by Pollutants'!R18</f>
+        <v>129607306650.87889</v>
       </c>
       <c r="S11" s="3">
-        <f>'Government Data'!S23</f>
-        <v>30563653073.76923</v>
+        <f>'Emissions by Pollutants'!S18</f>
+        <v>130370608855.13173</v>
       </c>
       <c r="T11" s="3">
-        <f>'Government Data'!T23</f>
-        <v>28081325920.569698</v>
+        <f>'Emissions by Pollutants'!T18</f>
+        <v>131165914239.72107</v>
       </c>
       <c r="U11" s="3">
-        <f>'Government Data'!U23</f>
-        <v>25598998767.370171</v>
+        <f>'Emissions by Pollutants'!U18</f>
+        <v>131983621850.54593</v>
       </c>
       <c r="V11" s="3">
-        <f>'Government Data'!V23</f>
-        <v>23582107955.395546</v>
+        <f>'Emissions by Pollutants'!V18</f>
+        <v>132817011019.7357</v>
       </c>
       <c r="W11" s="3">
-        <f>'Government Data'!W23</f>
-        <v>21565217143.420929</v>
+        <f>'Emissions by Pollutants'!W18</f>
+        <v>133408054355.83664</v>
       </c>
       <c r="X11" s="3">
-        <f>'Government Data'!X23</f>
-        <v>19703471778.521278</v>
+        <f>'Emissions by Pollutants'!X18</f>
+        <v>133829455608.77539</v>
       </c>
       <c r="Y11" s="3">
-        <f>'Government Data'!Y23</f>
-        <v>17996871860.696602</v>
+        <f>'Emissions by Pollutants'!Y18</f>
+        <v>134132107403.50063</v>
       </c>
       <c r="Z11" s="3">
-        <f>'Government Data'!Z23</f>
-        <v>16445417389.946896</v>
+        <f>'Emissions by Pollutants'!Z18</f>
+        <v>134351634577.47639</v>
       </c>
       <c r="AA11" s="3">
-        <f>'Government Data'!AA23</f>
-        <v>15111166545.102146</v>
+        <f>'Emissions by Pollutants'!AA18</f>
+        <v>134512974516.92751</v>
       </c>
       <c r="AB11" s="3">
-        <f>'Government Data'!AB23</f>
-        <v>13838973879.087387</v>
+        <f>'Emissions by Pollutants'!AB18</f>
+        <v>134811475625.75264</v>
       </c>
       <c r="AC11" s="3">
-        <f>'Government Data'!AC23</f>
-        <v>12659868481.31761</v>
+        <f>'Emissions by Pollutants'!AC18</f>
+        <v>135205989553.13956</v>
       </c>
       <c r="AD11" s="3">
-        <f>'Government Data'!AD23</f>
-        <v>12085830327.140217</v>
+        <f>'Emissions by Pollutants'!AD18</f>
+        <v>135667712453.51978</v>
       </c>
       <c r="AE11" s="3">
-        <f>'Government Data'!AE23</f>
-        <v>11527306717.670322</v>
+        <f>'Emissions by Pollutants'!AE18</f>
+        <v>136176481634.99527</v>
       </c>
       <c r="AF11" s="3">
-        <f>'Government Data'!AF23</f>
-        <v>11015326742.32292</v>
-      </c>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+        <f>'Emissions by Pollutants'!AF18</f>
+        <v>136718183213.23744</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="3">
-        <f>'Government Data'!B24</f>
-        <v>317044295.12375975</v>
+        <f>'Emissions by Pollutants'!B19</f>
+        <v>333640961.9906497</v>
       </c>
       <c r="C12" s="3">
-        <f>'Government Data'!C24</f>
-        <v>427909467.94393522</v>
+        <f>'Emissions by Pollutants'!C19</f>
+        <v>366357826.30748576</v>
       </c>
       <c r="D12" s="3">
-        <f>'Government Data'!D24</f>
-        <v>423394596.65261585</v>
+        <f>'Emissions by Pollutants'!D19</f>
+        <v>377703968.75484872</v>
       </c>
       <c r="E12" s="3">
-        <f>'Government Data'!E24</f>
-        <v>391288845.2476781</v>
+        <f>'Emissions by Pollutants'!E19</f>
+        <v>385801676.40728146</v>
       </c>
       <c r="F12" s="3">
-        <f>'Government Data'!F24</f>
-        <v>312529423.83244038</v>
+        <f>'Emissions by Pollutants'!F19</f>
+        <v>391625479.70326293</v>
       </c>
       <c r="G12" s="3">
-        <f>'Government Data'!G24</f>
-        <v>285941848.45022637</v>
+        <f>'Emissions by Pollutants'!G19</f>
+        <v>395857549.94972855</v>
       </c>
       <c r="H12" s="3">
-        <f>'Government Data'!H24</f>
-        <v>261862534.89652306</v>
+        <f>'Emissions by Pollutants'!H19</f>
+        <v>399107600.40697962</v>
       </c>
       <c r="I12" s="3">
-        <f>'Government Data'!I24</f>
-        <v>239789830.80562842</v>
+        <f>'Emissions by Pollutants'!I19</f>
+        <v>401670237.01178038</v>
       </c>
       <c r="J12" s="3">
-        <f>'Government Data'!J24</f>
-        <v>219222083.81184018</v>
+        <f>'Emissions by Pollutants'!J19</f>
+        <v>403751683.91986579</v>
       </c>
       <c r="K12" s="3">
-        <f>'Government Data'!K24</f>
-        <v>200660946.28086057</v>
+        <f>'Emissions by Pollutants'!K19</f>
+        <v>405496298.04025072</v>
       </c>
       <c r="L12" s="3">
-        <f>'Government Data'!L24</f>
-        <v>184106418.21268958</v>
+        <f>'Emissions by Pollutants'!L19</f>
+        <v>407005129.20924515</v>
       </c>
       <c r="M12" s="3">
-        <f>'Government Data'!M24</f>
-        <v>168555194.87592289</v>
+        <f>'Emissions by Pollutants'!M19</f>
+        <v>408730412.16839027</v>
       </c>
       <c r="N12" s="3">
-        <f>'Government Data'!N24</f>
-        <v>154007276.2705605</v>
+        <f>'Emissions by Pollutants'!N19</f>
+        <v>410607211.38064086</v>
       </c>
       <c r="O12" s="3">
-        <f>'Government Data'!O24</f>
-        <v>140964314.76230457</v>
+        <f>'Emissions by Pollutants'!O19</f>
+        <v>412590071.97006524</v>
       </c>
       <c r="P12" s="3">
-        <f>'Government Data'!P24</f>
-        <v>128924657.98545294</v>
+        <f>'Emissions by Pollutants'!P19</f>
+        <v>414647175.52351129</v>
       </c>
       <c r="Q12" s="3">
-        <f>'Government Data'!Q24</f>
-        <v>118389958.30570775</v>
+        <f>'Emissions by Pollutants'!Q19</f>
+        <v>416756249.1517725</v>
       </c>
       <c r="R12" s="3">
-        <f>'Government Data'!R24</f>
-        <v>108356910.99166471</v>
+        <f>'Emissions by Pollutants'!R19</f>
+        <v>419076506.72004008</v>
       </c>
       <c r="S12" s="3">
-        <f>'Government Data'!S24</f>
-        <v>98825516.043323845</v>
+        <f>'Emissions by Pollutants'!S19</f>
+        <v>421544593.04631221</v>
       </c>
       <c r="T12" s="3">
-        <f>'Government Data'!T24</f>
-        <v>90799078.192089409</v>
+        <f>'Emissions by Pollutants'!T19</f>
+        <v>424116159.50318736</v>
       </c>
       <c r="U12" s="3">
-        <f>'Government Data'!U24</f>
-        <v>82772640.340854988</v>
+        <f>'Emissions by Pollutants'!U19</f>
+        <v>426760162.05148464</v>
       </c>
       <c r="V12" s="3">
-        <f>'Government Data'!V24</f>
-        <v>76251159.586727023</v>
+        <f>'Emissions by Pollutants'!V19</f>
+        <v>429454869.86377752</v>
       </c>
       <c r="W12" s="3">
-        <f>'Government Data'!W24</f>
-        <v>69729678.832599044</v>
+        <f>'Emissions by Pollutants'!W19</f>
+        <v>431365968.72860116</v>
       </c>
       <c r="X12" s="3">
-        <f>'Government Data'!X24</f>
-        <v>63709850.444173239</v>
+        <f>'Emissions by Pollutants'!X19</f>
+        <v>432728541.3301962</v>
       </c>
       <c r="Y12" s="3">
-        <f>'Government Data'!Y24</f>
-        <v>58191674.421449572</v>
+        <f>'Emissions by Pollutants'!Y19</f>
+        <v>433707145.54753143</v>
       </c>
       <c r="Z12" s="3">
-        <f>'Government Data'!Z24</f>
-        <v>53175150.764428057</v>
+        <f>'Emissions by Pollutants'!Z19</f>
+        <v>434416971.89588463</v>
       </c>
       <c r="AA12" s="3">
-        <f>'Government Data'!AA24</f>
-        <v>48860940.419389553</v>
+        <f>'Emissions by Pollutants'!AA19</f>
+        <v>434938653.73595035</v>
       </c>
       <c r="AB12" s="3">
-        <f>'Government Data'!AB24</f>
-        <v>44747391.020631909</v>
+        <f>'Emissions by Pollutants'!AB19</f>
+        <v>435903836.98966509</v>
       </c>
       <c r="AC12" s="3">
-        <f>'Government Data'!AC24</f>
-        <v>40934833.041295558</v>
+        <f>'Emissions by Pollutants'!AC19</f>
+        <v>437179471.232934</v>
       </c>
       <c r="AD12" s="3">
-        <f>'Government Data'!AD24</f>
-        <v>39078719.288197599</v>
+        <f>'Emissions by Pollutants'!AD19</f>
+        <v>438672421.16889095</v>
       </c>
       <c r="AE12" s="3">
-        <f>'Government Data'!AE24</f>
-        <v>37272770.771669857</v>
+        <f>'Emissions by Pollutants'!AE19</f>
+        <v>440317492.08972949</v>
       </c>
       <c r="AF12" s="3">
-        <f>'Government Data'!AF24</f>
-        <v>35617317.964852758</v>
-      </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+        <f>'Emissions by Pollutants'!AF19</f>
+        <v>442069047.69998503</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>4</v>
       </c>
